--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C24F96-1402-401E-BC6C-749DCE094419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB84B255-05BE-4FEE-B734-D65908C900B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="197">
   <si>
     <t>STT</t>
   </si>
@@ -610,13 +610,22 @@
   </si>
   <si>
     <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Khách đã lắp, lỗi không sáng đèn led, gửi lại X-Force bảo hành (01/07/2026)</t>
+  </si>
+  <si>
+    <t>Gửi lại X-Force bảo hành (01/07/2026)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -648,8 +657,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -659,6 +674,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -730,6 +751,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1066,7 +1102,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G198"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1074,6 +1109,7 @@
     <col min="2" max="2" width="27.42578125" style="12" customWidth="1"/>
     <col min="3" max="3" width="15" style="12" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" style="15" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
@@ -1091,6 +1127,9 @@
       <c r="D1" s="7" t="s">
         <v>102</v>
       </c>
+      <c r="E1" s="17" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
@@ -1105,6 +1144,7 @@
       <c r="D2" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E2" s="16"/>
       <c r="F2" s="13"/>
       <c r="G2" s="9"/>
     </row>
@@ -1121,6 +1161,7 @@
       <c r="D3" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E3" s="16"/>
       <c r="F3" s="13"/>
       <c r="G3" s="9"/>
     </row>
@@ -1137,6 +1178,7 @@
       <c r="D4" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E4" s="16"/>
       <c r="F4" s="13"/>
       <c r="G4" s="9"/>
     </row>
@@ -1153,6 +1195,7 @@
       <c r="D5" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E5" s="16"/>
       <c r="F5" s="13"/>
       <c r="G5" s="9"/>
     </row>
@@ -1169,6 +1212,7 @@
       <c r="D6" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E6" s="16"/>
       <c r="F6" s="13"/>
       <c r="G6" s="9"/>
     </row>
@@ -1185,6 +1229,7 @@
       <c r="D7" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E7" s="16"/>
       <c r="F7" s="13"/>
       <c r="G7" s="9"/>
     </row>
@@ -1201,6 +1246,7 @@
       <c r="D8" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E8" s="16"/>
       <c r="F8" s="13"/>
       <c r="G8" s="9"/>
     </row>
@@ -1217,6 +1263,7 @@
       <c r="D9" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E9" s="16"/>
       <c r="F9" s="13"/>
       <c r="G9" s="9"/>
     </row>
@@ -1233,6 +1280,7 @@
       <c r="D10" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E10" s="16"/>
       <c r="F10" s="13"/>
       <c r="G10" s="9"/>
     </row>
@@ -1249,6 +1297,7 @@
       <c r="D11" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E11" s="16"/>
       <c r="F11" s="13"/>
       <c r="G11" s="9"/>
     </row>
@@ -1265,6 +1314,7 @@
       <c r="D12" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E12" s="16"/>
       <c r="F12" s="13"/>
       <c r="G12" s="9"/>
     </row>
@@ -1281,10 +1331,11 @@
       <c r="D13" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E13" s="16"/>
       <c r="F13" s="13"/>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -1296,6 +1347,9 @@
       </c>
       <c r="D14" s="4" t="s">
         <v>103</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>195</v>
       </c>
       <c r="F14" s="13"/>
       <c r="G14" s="9"/>
@@ -1313,6 +1367,7 @@
       <c r="D15" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E15" s="16"/>
       <c r="F15" s="13"/>
       <c r="G15" s="9"/>
     </row>
@@ -1329,6 +1384,7 @@
       <c r="D16" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E16" s="16"/>
       <c r="F16" s="13"/>
       <c r="G16" s="9"/>
     </row>
@@ -1345,6 +1401,7 @@
       <c r="D17" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E17" s="16"/>
       <c r="F17" s="13"/>
       <c r="G17" s="9"/>
     </row>
@@ -1361,6 +1418,7 @@
       <c r="D18" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E18" s="16"/>
       <c r="F18" s="13"/>
       <c r="G18" s="9"/>
     </row>
@@ -1377,6 +1435,7 @@
       <c r="D19" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E19" s="16"/>
       <c r="F19" s="13"/>
       <c r="G19" s="9"/>
     </row>
@@ -1393,6 +1452,7 @@
       <c r="D20" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E20" s="16"/>
       <c r="F20" s="13"/>
       <c r="G20" s="9"/>
     </row>
@@ -1409,6 +1469,7 @@
       <c r="D21" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E21" s="16"/>
       <c r="F21" s="13"/>
       <c r="G21" s="9"/>
     </row>
@@ -1425,6 +1486,7 @@
       <c r="D22" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E22" s="16"/>
       <c r="F22" s="13"/>
       <c r="G22" s="9"/>
     </row>
@@ -1441,6 +1503,7 @@
       <c r="D23" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E23" s="16"/>
       <c r="F23" s="13"/>
       <c r="G23" s="9"/>
     </row>
@@ -1457,6 +1520,7 @@
       <c r="D24" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E24" s="16"/>
       <c r="F24" s="13"/>
       <c r="G24" s="10"/>
     </row>
@@ -1473,6 +1537,7 @@
       <c r="D25" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E25" s="16"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1488,6 +1553,7 @@
       <c r="D26" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E26" s="16"/>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1503,6 +1569,7 @@
       <c r="D27" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E27" s="16"/>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1518,6 +1585,7 @@
       <c r="D28" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E28" s="16"/>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1533,6 +1601,7 @@
       <c r="D29" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E29" s="16"/>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1548,6 +1617,7 @@
       <c r="D30" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E30" s="16"/>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,6 +1633,7 @@
       <c r="D31" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E31" s="16"/>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1578,9 +1649,10 @@
       <c r="D32" s="4" t="s">
         <v>103</v>
       </c>
+      <c r="E32" s="16"/>
       <c r="G32" s="10"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -1593,8 +1665,9 @@
       <c r="D33" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="16"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -1607,8 +1680,9 @@
       <c r="D34" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="16"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -1621,8 +1695,9 @@
       <c r="D35" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="16"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -1635,8 +1710,9 @@
       <c r="D36" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="16"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -1649,8 +1725,9 @@
       <c r="D37" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="16"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -1663,8 +1740,9 @@
       <c r="D38" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="16"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -1677,8 +1755,9 @@
       <c r="D39" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="16"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -1691,8 +1770,9 @@
       <c r="D40" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="16"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -1705,8 +1785,9 @@
       <c r="D41" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="16"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -1719,8 +1800,9 @@
       <c r="D42" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="16"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -1733,8 +1815,9 @@
       <c r="D43" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="16"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -1747,8 +1830,9 @@
       <c r="D44" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="16"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -1761,8 +1845,9 @@
       <c r="D45" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="16"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -1775,8 +1860,9 @@
       <c r="D46" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="16"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -1789,8 +1875,9 @@
       <c r="D47" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="16"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -1803,8 +1890,9 @@
       <c r="D48" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="16"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -1817,8 +1905,9 @@
       <c r="D49" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="16"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -1831,8 +1920,9 @@
       <c r="D50" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="16"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -1845,8 +1935,9 @@
       <c r="D51" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="16"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -1859,8 +1950,9 @@
       <c r="D52" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="16"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -1873,8 +1965,9 @@
       <c r="D53" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="16"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -1887,8 +1980,9 @@
       <c r="D54" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="16"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -1901,8 +1995,9 @@
       <c r="D55" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" s="16"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -1915,8 +2010,9 @@
       <c r="D56" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="16"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -1929,8 +2025,9 @@
       <c r="D57" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="16"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -1943,8 +2040,9 @@
       <c r="D58" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="16"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -1957,8 +2055,9 @@
       <c r="D59" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="16"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -1971,8 +2070,9 @@
       <c r="D60" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="16"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -1985,8 +2085,9 @@
       <c r="D61" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="16"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -1999,8 +2100,9 @@
       <c r="D62" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="16"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -2013,8 +2115,9 @@
       <c r="D63" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" s="16"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -2027,8 +2130,9 @@
       <c r="D64" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="16"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -2041,8 +2145,9 @@
       <c r="D65" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="16"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -2055,8 +2160,9 @@
       <c r="D66" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="16"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -2069,8 +2175,9 @@
       <c r="D67" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="16"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -2083,8 +2190,9 @@
       <c r="D68" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" s="16"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -2097,8 +2205,9 @@
       <c r="D69" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="16"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -2111,8 +2220,9 @@
       <c r="D70" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" s="16"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -2125,8 +2235,9 @@
       <c r="D71" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" s="16"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -2139,8 +2250,9 @@
       <c r="D72" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="16"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -2153,8 +2265,9 @@
       <c r="D73" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="16"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -2167,8 +2280,9 @@
       <c r="D74" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" s="16"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -2181,8 +2295,9 @@
       <c r="D75" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" s="16"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -2195,8 +2310,9 @@
       <c r="D76" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="16"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -2209,8 +2325,9 @@
       <c r="D77" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="16"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -2223,8 +2340,9 @@
       <c r="D78" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" s="16"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -2237,8 +2355,9 @@
       <c r="D79" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="16"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -2251,8 +2370,9 @@
       <c r="D80" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="16"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -2265,8 +2385,9 @@
       <c r="D81" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="16"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -2279,8 +2400,9 @@
       <c r="D82" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" s="16"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -2293,8 +2415,9 @@
       <c r="D83" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" s="16"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -2307,8 +2430,9 @@
       <c r="D84" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" s="16"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -2321,8 +2445,9 @@
       <c r="D85" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="16"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -2335,8 +2460,9 @@
       <c r="D86" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="16"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -2349,8 +2475,9 @@
       <c r="D87" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" s="16"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -2363,8 +2490,9 @@
       <c r="D88" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="16"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -2377,8 +2505,9 @@
       <c r="D89" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="16"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -2391,8 +2520,9 @@
       <c r="D90" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" s="16"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -2405,8 +2535,9 @@
       <c r="D91" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E91" s="16"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -2419,8 +2550,9 @@
       <c r="D92" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E92" s="16"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -2433,8 +2565,9 @@
       <c r="D93" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="16"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -2447,8 +2580,9 @@
       <c r="D94" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" s="16"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -2461,8 +2595,9 @@
       <c r="D95" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" s="16"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -2475,8 +2610,9 @@
       <c r="D96" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" s="16"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -2489,8 +2625,9 @@
       <c r="D97" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" s="16"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -2503,8 +2640,9 @@
       <c r="D98" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" s="16"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -2517,8 +2655,9 @@
       <c r="D99" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" s="16"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -2531,8 +2670,9 @@
       <c r="D100" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" s="16"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -2545,8 +2685,9 @@
       <c r="D101" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E101" s="16"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -2559,8 +2700,9 @@
       <c r="D102" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E102" s="16"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -2573,8 +2715,9 @@
       <c r="D103" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E103" s="16"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -2587,8 +2730,9 @@
       <c r="D104" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E104" s="16"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -2601,8 +2745,9 @@
       <c r="D105" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E105" s="16"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -2615,8 +2760,9 @@
       <c r="D106" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E106" s="16"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -2629,8 +2775,9 @@
       <c r="D107" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E107" s="16"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -2643,8 +2790,9 @@
       <c r="D108" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E108" s="16"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -2657,8 +2805,9 @@
       <c r="D109" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E109" s="16"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -2671,8 +2820,9 @@
       <c r="D110" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E110" s="16"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -2685,8 +2835,9 @@
       <c r="D111" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E111" s="16"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -2699,8 +2850,9 @@
       <c r="D112" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E112" s="16"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -2713,8 +2865,9 @@
       <c r="D113" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E113" s="16"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -2727,8 +2880,9 @@
       <c r="D114" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E114" s="16"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -2741,8 +2895,9 @@
       <c r="D115" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E115" s="16"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -2755,8 +2910,9 @@
       <c r="D116" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E116" s="16"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -2769,8 +2925,9 @@
       <c r="D117" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E117" s="16"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -2783,8 +2940,9 @@
       <c r="D118" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E118" s="16"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -2797,8 +2955,9 @@
       <c r="D119" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E119" s="16"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -2811,8 +2970,9 @@
       <c r="D120" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E120" s="16"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -2825,8 +2985,9 @@
       <c r="D121" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E121" s="16"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -2839,8 +3000,9 @@
       <c r="D122" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E122" s="16"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -2853,8 +3015,9 @@
       <c r="D123" s="4" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E123" s="16"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -2867,8 +3030,9 @@
       <c r="D124" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E124" s="16"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -2878,11 +3042,12 @@
       <c r="C125" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D125" s="4" t="s">
+      <c r="D125" s="20" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E125" s="16"/>
+    </row>
+    <row r="126" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -2892,11 +3057,14 @@
       <c r="C126" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D126" s="4" t="s">
+      <c r="D126" s="14" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E126" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -2909,8 +3077,9 @@
       <c r="D127" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E127" s="16"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -2923,8 +3092,9 @@
       <c r="D128" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E128" s="16"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -2937,8 +3107,9 @@
       <c r="D129" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E129" s="16"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -2951,8 +3122,9 @@
       <c r="D130" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E130" s="16"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -2965,8 +3137,9 @@
       <c r="D131" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E131" s="16"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -2979,8 +3152,9 @@
       <c r="D132" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E132" s="16"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -2993,8 +3167,9 @@
       <c r="D133" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E133" s="16"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -3007,8 +3182,9 @@
       <c r="D134" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E134" s="16"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -3021,8 +3197,9 @@
       <c r="D135" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E135" s="16"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -3035,8 +3212,9 @@
       <c r="D136" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E136" s="16"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -3049,8 +3227,9 @@
       <c r="D137" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E137" s="16"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -3063,8 +3242,9 @@
       <c r="D138" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E138" s="16"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -3077,8 +3257,9 @@
       <c r="D139" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E139" s="16"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -3091,8 +3272,9 @@
       <c r="D140" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E140" s="16"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -3105,8 +3287,9 @@
       <c r="D141" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E141" s="16"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -3119,8 +3302,9 @@
       <c r="D142" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E142" s="16"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -3133,8 +3317,9 @@
       <c r="D143" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E143" s="16"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -3147,8 +3332,9 @@
       <c r="D144" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E144" s="16"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -3161,8 +3347,9 @@
       <c r="D145" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E145" s="16"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -3175,8 +3362,9 @@
       <c r="D146" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E146" s="16"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -3189,8 +3377,9 @@
       <c r="D147" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E147" s="16"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -3203,8 +3392,9 @@
       <c r="D148" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E148" s="16"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -3217,8 +3407,9 @@
       <c r="D149" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E149" s="16"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -3231,8 +3422,9 @@
       <c r="D150" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E150" s="16"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -3245,8 +3437,9 @@
       <c r="D151" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E151" s="16"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -3259,8 +3452,9 @@
       <c r="D152" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E152" s="16"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -3273,8 +3467,9 @@
       <c r="D153" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E153" s="16"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -3287,8 +3482,9 @@
       <c r="D154" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E154" s="16"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -3301,8 +3497,9 @@
       <c r="D155" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E155" s="16"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -3315,8 +3512,9 @@
       <c r="D156" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E156" s="16"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -3329,8 +3527,9 @@
       <c r="D157" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E157" s="16"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -3343,8 +3542,9 @@
       <c r="D158" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E158" s="16"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -3357,8 +3557,9 @@
       <c r="D159" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E159" s="16"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -3371,8 +3572,9 @@
       <c r="D160" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E160" s="16"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -3385,8 +3587,9 @@
       <c r="D161" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E161" s="16"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -3399,8 +3602,9 @@
       <c r="D162" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E162" s="16"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -3413,8 +3617,9 @@
       <c r="D163" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E163" s="16"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -3427,8 +3632,9 @@
       <c r="D164" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E164" s="16"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -3441,8 +3647,9 @@
       <c r="D165" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E165" s="16"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -3455,8 +3662,9 @@
       <c r="D166" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E166" s="16"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -3469,8 +3677,9 @@
       <c r="D167" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E167" s="16"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -3483,8 +3692,9 @@
       <c r="D168" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E168" s="16"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -3497,8 +3707,9 @@
       <c r="D169" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E169" s="16"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -3511,8 +3722,9 @@
       <c r="D170" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E170" s="16"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -3525,8 +3737,9 @@
       <c r="D171" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E171" s="16"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -3539,8 +3752,9 @@
       <c r="D172" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E172" s="16"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -3553,8 +3767,9 @@
       <c r="D173" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E173" s="16"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -3567,8 +3782,9 @@
       <c r="D174" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E174" s="16"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -3581,8 +3797,9 @@
       <c r="D175" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E175" s="16"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -3595,8 +3812,9 @@
       <c r="D176" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E176" s="16"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -3609,8 +3827,9 @@
       <c r="D177" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E177" s="16"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -3623,8 +3842,9 @@
       <c r="D178" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E178" s="16"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -3637,8 +3857,9 @@
       <c r="D179" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E179" s="16"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -3651,8 +3872,9 @@
       <c r="D180" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E180" s="16"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -3665,8 +3887,9 @@
       <c r="D181" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E181" s="16"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -3679,91 +3902,85 @@
       <c r="D182" s="4" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="E182" s="16"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="11">
         <v>183</v>
       </c>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="11">
         <v>184</v>
       </c>
     </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="11">
         <v>185</v>
       </c>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="11">
         <v>186</v>
       </c>
     </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="11">
         <v>187</v>
       </c>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="11">
         <v>188</v>
       </c>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="11">
         <v>189</v>
       </c>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="11">
         <v>190</v>
       </c>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="11">
         <v>191</v>
       </c>
     </row>
-    <row r="193" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="11">
         <v>192</v>
       </c>
     </row>
-    <row r="194" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="11">
         <v>193</v>
       </c>
     </row>
-    <row r="195" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="11">
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="11">
         <v>195</v>
       </c>
     </row>
-    <row r="197" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="11">
         <v>196</v>
       </c>
     </row>
-    <row r="198" spans="1:1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="11">
         <v>197</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D198" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Đã nhập kho"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D198" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
   <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB84B255-05BE-4FEE-B734-D65908C900B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92351AD8-913C-40FF-8C73-46DE3B4510E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ID_VNSH03" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$D$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$D$262</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="277">
   <si>
     <t>STT</t>
   </si>
@@ -585,9 +585,6 @@
     <t>VNET861385071527587</t>
   </si>
   <si>
-    <t>Đang chờ test</t>
-  </si>
-  <si>
     <t>Không có nguồn RFID</t>
   </si>
   <si>
@@ -619,6 +616,249 @@
   </si>
   <si>
     <t>Gửi lại X-Force bảo hành (01/07/2026)</t>
+  </si>
+  <si>
+    <t>VNET861385071518677</t>
+  </si>
+  <si>
+    <t>VNET861385071455722</t>
+  </si>
+  <si>
+    <t>VNET861385071527298</t>
+  </si>
+  <si>
+    <t>VNET861385071448511</t>
+  </si>
+  <si>
+    <t>VNET861385071456373</t>
+  </si>
+  <si>
+    <t>VNET861385071531522</t>
+  </si>
+  <si>
+    <t>VNET861385071476181</t>
+  </si>
+  <si>
+    <t>VNET861385071516382</t>
+  </si>
+  <si>
+    <t>VNET861385071448693</t>
+  </si>
+  <si>
+    <t>VNET861385071461423</t>
+  </si>
+  <si>
+    <t>VNET861385070649796</t>
+  </si>
+  <si>
+    <t>VNET861385071455235</t>
+  </si>
+  <si>
+    <t>VNET861385071455854</t>
+  </si>
+  <si>
+    <t>VNET861385071448552</t>
+  </si>
+  <si>
+    <t>VNET861385071449352</t>
+  </si>
+  <si>
+    <t>VNET861385071455839</t>
+  </si>
+  <si>
+    <t>VNET861385071476173</t>
+  </si>
+  <si>
+    <t>VNET861385071518818</t>
+  </si>
+  <si>
+    <t>VNET861385071455706</t>
+  </si>
+  <si>
+    <t>VNET861385071517638</t>
+  </si>
+  <si>
+    <t>VNET861385071518511</t>
+  </si>
+  <si>
+    <t>VNET861385071455284</t>
+  </si>
+  <si>
+    <t>VNET861385071455045</t>
+  </si>
+  <si>
+    <t>VNET861385071455243</t>
+  </si>
+  <si>
+    <t>VNET861385071448883</t>
+  </si>
+  <si>
+    <t>VNET861385071460193</t>
+  </si>
+  <si>
+    <t>VNET861385071455631</t>
+  </si>
+  <si>
+    <t>VNET861385071526951</t>
+  </si>
+  <si>
+    <t>VNET861385071531282</t>
+  </si>
+  <si>
+    <t>VNET861385071534625</t>
+  </si>
+  <si>
+    <t>VNET861385071455060</t>
+  </si>
+  <si>
+    <t>VNET861385071516523</t>
+  </si>
+  <si>
+    <t>VNET861385071531506</t>
+  </si>
+  <si>
+    <t>VNET861385071455961</t>
+  </si>
+  <si>
+    <t>VNET861385071457595</t>
+  </si>
+  <si>
+    <t>VNET861385071455276</t>
+  </si>
+  <si>
+    <t>VNET861385071517695</t>
+  </si>
+  <si>
+    <t>VNET861385071449410</t>
+  </si>
+  <si>
+    <t>VNET861385071455821</t>
+  </si>
+  <si>
+    <t>VNET861385071486826</t>
+  </si>
+  <si>
+    <t>VNET861385071531829</t>
+  </si>
+  <si>
+    <t>VNET861385071455847</t>
+  </si>
+  <si>
+    <t>VNET861385071449444</t>
+  </si>
+  <si>
+    <t>VNET861385071448719</t>
+  </si>
+  <si>
+    <t>VNET861385071486701</t>
+  </si>
+  <si>
+    <t>VNET861385071447059</t>
+  </si>
+  <si>
+    <t>VNET861385071461431</t>
+  </si>
+  <si>
+    <t>VNET861385071461308</t>
+  </si>
+  <si>
+    <t>VNET861385071486735</t>
+  </si>
+  <si>
+    <t>VNET861385071448438</t>
+  </si>
+  <si>
+    <t>VNET861385071448891</t>
+  </si>
+  <si>
+    <t>VNET861385071455490</t>
+  </si>
+  <si>
+    <t>VNET861385071447034</t>
+  </si>
+  <si>
+    <t>VNET861385071461399</t>
+  </si>
+  <si>
+    <t>VNET861385071456340</t>
+  </si>
+  <si>
+    <t>VNET861385071448479</t>
+  </si>
+  <si>
+    <t>VNET861385071482577</t>
+  </si>
+  <si>
+    <t>VNET861385071534195</t>
+  </si>
+  <si>
+    <t>VNET861385071446960</t>
+  </si>
+  <si>
+    <t>VNET861385071456779</t>
+  </si>
+  <si>
+    <t>VNET861385071455508</t>
+  </si>
+  <si>
+    <t>VNET861385071455342</t>
+  </si>
+  <si>
+    <t>VNET861385071455557</t>
+  </si>
+  <si>
+    <t>VNET861385071448701</t>
+  </si>
+  <si>
+    <t>VNET861385071448602</t>
+  </si>
+  <si>
+    <t>VNET861385070620805</t>
+  </si>
+  <si>
+    <t>VNET861385071457660</t>
+  </si>
+  <si>
+    <t>VNET861385071455607</t>
+  </si>
+  <si>
+    <t>VNET861385071448594</t>
+  </si>
+  <si>
+    <t>VNET861385071476140</t>
+  </si>
+  <si>
+    <t>VNET861385071531753</t>
+  </si>
+  <si>
+    <t>VNET861385071517588</t>
+  </si>
+  <si>
+    <t>VNET861385071518859</t>
+  </si>
+  <si>
+    <t>VNET861385071455680</t>
+  </si>
+  <si>
+    <t>VNET861385071448347</t>
+  </si>
+  <si>
+    <t>VNET861385071534229</t>
+  </si>
+  <si>
+    <t>VNET861385071455649</t>
+  </si>
+  <si>
+    <t>VNET861385071455094</t>
+  </si>
+  <si>
+    <t>VNET861385071527249</t>
+  </si>
+  <si>
+    <t>VNET861385071455763</t>
+  </si>
+  <si>
+    <t>02/07/2026</t>
   </si>
 </sst>
 </file>
@@ -749,15 +989,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -767,6 +1003,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1102,15 +1340,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="11" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" style="12" customWidth="1"/>
     <col min="3" max="3" width="15" style="12" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" style="11" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" style="15" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" customWidth="1"/>
     <col min="7" max="7" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1122,13 +1360,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>194</v>
+      <c r="E1" s="19" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1139,13 +1377,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="16"/>
-      <c r="F2" s="13"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1156,13 +1394,13 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="13"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="5"/>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1173,13 +1411,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="13"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1190,13 +1428,13 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="13"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1207,13 +1445,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="13"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1224,13 +1462,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="13"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="5"/>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1241,13 +1479,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="13"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="5"/>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1258,13 +1496,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="13"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="5"/>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1275,13 +1513,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="13"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1292,13 +1530,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="13"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1309,13 +1547,13 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="13"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1326,13 +1564,13 @@
         <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="13"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -1343,15 +1581,15 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="F14" s="13"/>
+      <c r="E14" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="F14" s="5"/>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1362,13 +1600,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="16"/>
-      <c r="F15" s="13"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1379,13 +1617,13 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="13"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1396,13 +1634,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="13"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="5"/>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1413,13 +1651,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="13"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="5"/>
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1430,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="13"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="5"/>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1447,13 +1685,13 @@
         <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="13"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="5"/>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1464,13 +1702,13 @@
         <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="13"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1481,13 +1719,13 @@
         <v>22</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="16"/>
-      <c r="F22" s="13"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="5"/>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1498,13 +1736,13 @@
         <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="16"/>
-      <c r="F23" s="13"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="5"/>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1515,13 +1753,13 @@
         <v>24</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="16"/>
-      <c r="F24" s="13"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="5"/>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1532,12 +1770,13 @@
         <v>25</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="16"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="5"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1548,12 +1787,13 @@
         <v>26</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="16"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="5"/>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1564,12 +1804,13 @@
         <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="16"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="5"/>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1580,12 +1821,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="16"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="5"/>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1596,12 +1838,13 @@
         <v>29</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="16"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="5"/>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1612,12 +1855,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="16"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="5"/>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1628,12 +1872,13 @@
         <v>31</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="5"/>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1644,15 +1889,16 @@
         <v>32</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="16"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="5"/>
       <c r="G32" s="10"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>32</v>
       </c>
@@ -1660,14 +1906,15 @@
         <v>33</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="16"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E33" s="15"/>
+      <c r="F33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>33</v>
       </c>
@@ -1675,14 +1922,15 @@
         <v>34</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="16"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E34" s="15"/>
+      <c r="F34" s="5"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>34</v>
       </c>
@@ -1690,14 +1938,15 @@
         <v>35</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E35" s="16"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E35" s="15"/>
+      <c r="F35" s="5"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -1705,14 +1954,15 @@
         <v>36</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="16"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E36" s="15"/>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -1720,14 +1970,15 @@
         <v>37</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E37" s="16"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E37" s="15"/>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -1735,14 +1986,15 @@
         <v>38</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="16"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E38" s="15"/>
+      <c r="F38" s="5"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -1750,14 +2002,15 @@
         <v>39</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E39" s="16"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E39" s="15"/>
+      <c r="F39" s="5"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -1765,14 +2018,15 @@
         <v>40</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E40" s="16"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="15"/>
+      <c r="F40" s="5"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -1780,14 +2034,15 @@
         <v>41</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E41" s="16"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E41" s="15"/>
+      <c r="F41" s="5"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -1795,14 +2050,15 @@
         <v>42</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="16"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" s="15"/>
+      <c r="F42" s="20"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -1810,14 +2066,15 @@
         <v>43</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E43" s="16"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E43" s="15"/>
+      <c r="F43" s="20"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -1825,14 +2082,15 @@
         <v>44</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="16"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E44" s="15"/>
+      <c r="F44" s="20"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -1840,14 +2098,15 @@
         <v>45</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="16"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E45" s="15"/>
+      <c r="F45" s="20"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -1855,14 +2114,15 @@
         <v>46</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E46" s="16"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E46" s="15"/>
+      <c r="F46" s="20"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -1870,14 +2130,15 @@
         <v>47</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="16"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E47" s="15"/>
+      <c r="F47" s="20"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -1885,14 +2146,15 @@
         <v>48</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E48" s="16"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E48" s="15"/>
+      <c r="F48" s="20"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -1900,14 +2162,15 @@
         <v>49</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E49" s="16"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E49" s="15"/>
+      <c r="F49" s="20"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -1915,14 +2178,15 @@
         <v>50</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="16"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E50" s="15"/>
+      <c r="F50" s="20"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -1930,14 +2194,15 @@
         <v>51</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E51" s="16"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E51" s="15"/>
+      <c r="F51" s="20"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -1945,14 +2210,15 @@
         <v>52</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E52" s="16"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E52" s="15"/>
+      <c r="F52" s="20"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -1960,14 +2226,15 @@
         <v>53</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E53" s="16"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E53" s="15"/>
+      <c r="F53" s="20"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -1975,14 +2242,15 @@
         <v>54</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="16"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E54" s="15"/>
+      <c r="F54" s="20"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -1990,14 +2258,15 @@
         <v>55</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E55" s="16"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E55" s="15"/>
+      <c r="F55" s="20"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -2005,14 +2274,15 @@
         <v>56</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="16"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E56" s="15"/>
+      <c r="F56" s="20"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -2020,14 +2290,15 @@
         <v>57</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E57" s="16"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E57" s="15"/>
+      <c r="F57" s="20"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -2035,14 +2306,15 @@
         <v>58</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E58" s="16"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E58" s="15"/>
+      <c r="F58" s="20"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -2050,14 +2322,15 @@
         <v>59</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E59" s="16"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E59" s="15"/>
+      <c r="F59" s="20"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -2065,14 +2338,15 @@
         <v>60</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E60" s="16"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E60" s="15"/>
+      <c r="F60" s="20"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -2080,14 +2354,15 @@
         <v>61</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E61" s="16"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E61" s="15"/>
+      <c r="F61" s="20"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -2095,14 +2370,15 @@
         <v>62</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E62" s="16"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E62" s="15"/>
+      <c r="F62" s="20"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -2110,14 +2386,15 @@
         <v>63</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E63" s="16"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E63" s="15"/>
+      <c r="F63" s="20"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -2125,14 +2402,15 @@
         <v>64</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E64" s="16"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E64" s="15"/>
+      <c r="F64" s="20"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -2140,14 +2418,15 @@
         <v>65</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E65" s="16"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E65" s="15"/>
+      <c r="F65" s="20"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -2155,14 +2434,15 @@
         <v>66</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E66" s="16"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E66" s="15"/>
+      <c r="F66" s="20"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -2170,14 +2450,15 @@
         <v>67</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E67" s="16"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E67" s="15"/>
+      <c r="F67" s="20"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -2185,14 +2466,15 @@
         <v>68</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E68" s="16"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E68" s="15"/>
+      <c r="F68" s="20"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -2200,14 +2482,15 @@
         <v>69</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="16"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E69" s="15"/>
+      <c r="F69" s="20"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -2215,14 +2498,15 @@
         <v>70</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E70" s="16"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E70" s="15"/>
+      <c r="F70" s="20"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -2230,14 +2514,15 @@
         <v>71</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E71" s="16"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E71" s="15"/>
+      <c r="F71" s="20"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -2245,14 +2530,15 @@
         <v>72</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E72" s="16"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="15"/>
+      <c r="F72" s="20"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -2260,14 +2546,15 @@
         <v>73</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E73" s="16"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E73" s="15"/>
+      <c r="F73" s="20"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -2275,14 +2562,15 @@
         <v>74</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E74" s="16"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E74" s="15"/>
+      <c r="F74" s="20"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -2290,14 +2578,15 @@
         <v>75</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E75" s="16"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E75" s="15"/>
+      <c r="F75" s="20"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -2305,14 +2594,15 @@
         <v>76</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E76" s="16"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E76" s="15"/>
+      <c r="F76" s="20"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -2320,14 +2610,15 @@
         <v>77</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E77" s="16"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E77" s="15"/>
+      <c r="F77" s="20"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -2335,14 +2626,15 @@
         <v>78</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E78" s="16"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E78" s="15"/>
+      <c r="F78" s="20"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -2350,14 +2642,15 @@
         <v>79</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E79" s="16"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E79" s="15"/>
+      <c r="F79" s="20"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -2365,14 +2658,15 @@
         <v>80</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E80" s="16"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E80" s="15"/>
+      <c r="F80" s="20"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
         <v>80</v>
       </c>
@@ -2380,14 +2674,15 @@
         <v>81</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E81" s="16"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E81" s="15"/>
+      <c r="F81" s="20"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
         <v>81</v>
       </c>
@@ -2395,14 +2690,15 @@
         <v>82</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E82" s="16"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E82" s="15"/>
+      <c r="F82" s="20"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>82</v>
       </c>
@@ -2410,14 +2706,15 @@
         <v>83</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E83" s="16"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E83" s="15"/>
+      <c r="F83" s="20"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -2425,14 +2722,15 @@
         <v>84</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E84" s="16"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E84" s="15"/>
+      <c r="F84" s="20"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -2440,14 +2738,15 @@
         <v>85</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E85" s="16"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E85" s="15"/>
+      <c r="F85" s="20"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -2455,14 +2754,15 @@
         <v>86</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E86" s="16"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E86" s="15"/>
+      <c r="F86" s="20"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -2470,14 +2770,15 @@
         <v>87</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E87" s="16"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E87" s="15"/>
+      <c r="F87" s="20"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -2485,14 +2786,15 @@
         <v>88</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E88" s="16"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E88" s="15"/>
+      <c r="F88" s="20"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
@@ -2500,14 +2802,15 @@
         <v>89</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E89" s="16"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E89" s="15"/>
+      <c r="F89" s="20"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>89</v>
       </c>
@@ -2515,14 +2818,15 @@
         <v>90</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E90" s="16"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E90" s="15"/>
+      <c r="F90" s="20"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>90</v>
       </c>
@@ -2530,14 +2834,15 @@
         <v>91</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E91" s="16"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E91" s="15"/>
+      <c r="F91" s="20"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>91</v>
       </c>
@@ -2545,14 +2850,15 @@
         <v>92</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E92" s="16"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E92" s="15"/>
+      <c r="F92" s="20"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>92</v>
       </c>
@@ -2560,14 +2866,15 @@
         <v>93</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E93" s="16"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E93" s="15"/>
+      <c r="F93" s="20"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>93</v>
       </c>
@@ -2575,14 +2882,15 @@
         <v>94</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E94" s="16"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E94" s="15"/>
+      <c r="F94" s="20"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>94</v>
       </c>
@@ -2590,14 +2898,15 @@
         <v>95</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E95" s="16"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E95" s="15"/>
+      <c r="F95" s="20"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>95</v>
       </c>
@@ -2605,14 +2914,15 @@
         <v>96</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E96" s="16"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E96" s="15"/>
+      <c r="F96" s="20"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>96</v>
       </c>
@@ -2620,14 +2930,15 @@
         <v>97</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E97" s="16"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="15"/>
+      <c r="F97" s="20"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>97</v>
       </c>
@@ -2635,14 +2946,15 @@
         <v>98</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E98" s="16"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E98" s="15"/>
+      <c r="F98" s="20"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>98</v>
       </c>
@@ -2650,14 +2962,15 @@
         <v>99</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E99" s="16"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E99" s="15"/>
+      <c r="F99" s="20"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>99</v>
       </c>
@@ -2665,14 +2978,15 @@
         <v>100</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E100" s="16"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E100" s="15"/>
+      <c r="F100" s="20"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -2680,14 +2994,15 @@
         <v>101</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E101" s="16"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E101" s="15"/>
+      <c r="F101" s="20"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>101</v>
       </c>
@@ -2695,14 +3010,15 @@
         <v>104</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E102" s="16"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E102" s="15"/>
+      <c r="F102" s="20"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>102</v>
       </c>
@@ -2710,14 +3026,15 @@
         <v>105</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E103" s="16"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E103" s="15"/>
+      <c r="F103" s="20"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>103</v>
       </c>
@@ -2725,14 +3042,15 @@
         <v>106</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E104" s="16"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E104" s="15"/>
+      <c r="F104" s="20"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>104</v>
       </c>
@@ -2740,14 +3058,15 @@
         <v>107</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E105" s="16"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E105" s="15"/>
+      <c r="F105" s="20"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>105</v>
       </c>
@@ -2755,14 +3074,15 @@
         <v>108</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E106" s="16"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E106" s="15"/>
+      <c r="F106" s="20"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>106</v>
       </c>
@@ -2770,14 +3090,15 @@
         <v>109</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E107" s="16"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E107" s="15"/>
+      <c r="F107" s="20"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>107</v>
       </c>
@@ -2785,14 +3106,15 @@
         <v>110</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E108" s="16"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E108" s="15"/>
+      <c r="F108" s="20"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>108</v>
       </c>
@@ -2800,14 +3122,15 @@
         <v>111</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E109" s="16"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E109" s="15"/>
+      <c r="F109" s="20"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>109</v>
       </c>
@@ -2815,14 +3138,15 @@
         <v>112</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E110" s="16"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E110" s="15"/>
+      <c r="F110" s="20"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>110</v>
       </c>
@@ -2830,14 +3154,15 @@
         <v>113</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E111" s="16"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E111" s="15"/>
+      <c r="F111" s="20"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>111</v>
       </c>
@@ -2845,14 +3170,15 @@
         <v>114</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E112" s="16"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E112" s="15"/>
+      <c r="F112" s="20"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>112</v>
       </c>
@@ -2860,14 +3186,15 @@
         <v>115</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E113" s="16"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E113" s="15"/>
+      <c r="F113" s="20"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>113</v>
       </c>
@@ -2875,14 +3202,15 @@
         <v>116</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E114" s="16"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E114" s="15"/>
+      <c r="F114" s="20"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>114</v>
       </c>
@@ -2890,14 +3218,15 @@
         <v>117</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E115" s="16"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E115" s="15"/>
+      <c r="F115" s="20"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>115</v>
       </c>
@@ -2905,14 +3234,15 @@
         <v>118</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E116" s="16"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E116" s="15"/>
+      <c r="F116" s="20"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>116</v>
       </c>
@@ -2920,14 +3250,15 @@
         <v>119</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E117" s="16"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E117" s="15"/>
+      <c r="F117" s="20"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>117</v>
       </c>
@@ -2935,14 +3266,15 @@
         <v>120</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E118" s="16"/>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E118" s="15"/>
+      <c r="F118" s="20"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>118</v>
       </c>
@@ -2950,14 +3282,15 @@
         <v>121</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E119" s="16"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E119" s="15"/>
+      <c r="F119" s="20"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>119</v>
       </c>
@@ -2965,14 +3298,15 @@
         <v>122</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E120" s="16"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E120" s="15"/>
+      <c r="F120" s="20"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>120</v>
       </c>
@@ -2980,14 +3314,15 @@
         <v>123</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E121" s="16"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E121" s="15"/>
+      <c r="F121" s="20"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>121</v>
       </c>
@@ -2995,14 +3330,15 @@
         <v>124</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E122" s="16"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E122" s="15"/>
+      <c r="F122" s="20"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>122</v>
       </c>
@@ -3010,14 +3346,15 @@
         <v>125</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E123" s="16"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E123" s="15"/>
+      <c r="F123" s="20"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>123</v>
       </c>
@@ -3025,14 +3362,15 @@
         <v>126</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E124" s="16"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E124" s="15"/>
+      <c r="F124" s="20"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>124</v>
       </c>
@@ -3040,14 +3378,15 @@
         <v>127</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D125" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="E125" s="16"/>
-    </row>
-    <row r="126" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="E125" s="15"/>
+      <c r="F125" s="20"/>
+    </row>
+    <row r="126" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -3055,16 +3394,17 @@
         <v>128</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D126" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="E126" s="19" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="E126" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="F126" s="20"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>126</v>
       </c>
@@ -3072,14 +3412,15 @@
         <v>129</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E127" s="16"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E127" s="15"/>
+      <c r="F127" s="20"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>127</v>
       </c>
@@ -3087,14 +3428,15 @@
         <v>130</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E128" s="16"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E128" s="15"/>
+      <c r="F128" s="20"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>128</v>
       </c>
@@ -3102,14 +3444,15 @@
         <v>131</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E129" s="16"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E129" s="15"/>
+      <c r="F129" s="20"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>129</v>
       </c>
@@ -3117,14 +3460,15 @@
         <v>132</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E130" s="16"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E130" s="15"/>
+      <c r="F130" s="20"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
@@ -3132,14 +3476,15 @@
         <v>133</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E131" s="16"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E131" s="15"/>
+      <c r="F131" s="20"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>131</v>
       </c>
@@ -3147,14 +3492,13 @@
         <v>134</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E132" s="16"/>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D132" s="4"/>
+      <c r="E132" s="15"/>
+      <c r="F132" s="20"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>132</v>
       </c>
@@ -3162,14 +3506,15 @@
         <v>135</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E133" s="16"/>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E133" s="15"/>
+      <c r="F133" s="20"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>133</v>
       </c>
@@ -3177,14 +3522,13 @@
         <v>136</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E134" s="16"/>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D134" s="4"/>
+      <c r="E134" s="15"/>
+      <c r="F134" s="20"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
@@ -3192,14 +3536,13 @@
         <v>137</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E135" s="16"/>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D135" s="4"/>
+      <c r="E135" s="15"/>
+      <c r="F135" s="20"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>135</v>
       </c>
@@ -3207,14 +3550,15 @@
         <v>138</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E136" s="16"/>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E136" s="15"/>
+      <c r="F136" s="20"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>136</v>
       </c>
@@ -3222,14 +3566,15 @@
         <v>139</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E137" s="16"/>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E137" s="15"/>
+      <c r="F137" s="20"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>137</v>
       </c>
@@ -3237,14 +3582,13 @@
         <v>140</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D138" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E138" s="16"/>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D138" s="4"/>
+      <c r="E138" s="15"/>
+      <c r="F138" s="20"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
         <v>138</v>
       </c>
@@ -3252,14 +3596,15 @@
         <v>141</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E139" s="16"/>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E139" s="15"/>
+      <c r="F139" s="20"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
         <v>139</v>
       </c>
@@ -3267,14 +3612,15 @@
         <v>142</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E140" s="16"/>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E140" s="15"/>
+      <c r="F140" s="20"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
         <v>140</v>
       </c>
@@ -3282,14 +3628,15 @@
         <v>143</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E141" s="16"/>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E141" s="15"/>
+      <c r="F141" s="20"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
         <v>141</v>
       </c>
@@ -3297,14 +3644,13 @@
         <v>144</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D142" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E142" s="16"/>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D142" s="4"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="20"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
         <v>142</v>
       </c>
@@ -3312,14 +3658,13 @@
         <v>145</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D143" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E143" s="16"/>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D143" s="4"/>
+      <c r="E143" s="15"/>
+      <c r="F143" s="20"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
         <v>143</v>
       </c>
@@ -3327,14 +3672,15 @@
         <v>146</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E144" s="16"/>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E144" s="15"/>
+      <c r="F144" s="20"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
         <v>144</v>
       </c>
@@ -3342,14 +3688,15 @@
         <v>147</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E145" s="16"/>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E145" s="15"/>
+      <c r="F145" s="20"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
         <v>145</v>
       </c>
@@ -3357,14 +3704,15 @@
         <v>148</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E146" s="16"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E146" s="15"/>
+      <c r="F146" s="20"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>146</v>
       </c>
@@ -3372,14 +3720,13 @@
         <v>149</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D147" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E147" s="16"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D147" s="4"/>
+      <c r="E147" s="15"/>
+      <c r="F147" s="20"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>147</v>
       </c>
@@ -3387,14 +3734,13 @@
         <v>150</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D148" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E148" s="16"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D148" s="4"/>
+      <c r="E148" s="15"/>
+      <c r="F148" s="20"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>148</v>
       </c>
@@ -3402,14 +3748,13 @@
         <v>151</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D149" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E149" s="16"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D149" s="4"/>
+      <c r="E149" s="15"/>
+      <c r="F149" s="20"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>149</v>
       </c>
@@ -3417,14 +3762,15 @@
         <v>152</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E150" s="16"/>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E150" s="15"/>
+      <c r="F150" s="20"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>150</v>
       </c>
@@ -3432,14 +3778,15 @@
         <v>153</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E151" s="16"/>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E151" s="15"/>
+      <c r="F151" s="20"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>151</v>
       </c>
@@ -3447,14 +3794,15 @@
         <v>154</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E152" s="16"/>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E152" s="15"/>
+      <c r="F152" s="20"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
         <v>152</v>
       </c>
@@ -3462,14 +3810,15 @@
         <v>155</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E153" s="16"/>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E153" s="15"/>
+      <c r="F153" s="20"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>153</v>
       </c>
@@ -3477,14 +3826,13 @@
         <v>156</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E154" s="16"/>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D154" s="4"/>
+      <c r="E154" s="15"/>
+      <c r="F154" s="20"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>154</v>
       </c>
@@ -3492,14 +3840,15 @@
         <v>157</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E155" s="16"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E155" s="15"/>
+      <c r="F155" s="20"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>155</v>
       </c>
@@ -3507,14 +3856,15 @@
         <v>158</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E156" s="16"/>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E156" s="15"/>
+      <c r="F156" s="20"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>156</v>
       </c>
@@ -3522,14 +3872,15 @@
         <v>159</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E157" s="16"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E157" s="15"/>
+      <c r="F157" s="20"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>157</v>
       </c>
@@ -3537,14 +3888,13 @@
         <v>160</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D158" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E158" s="16"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D158" s="4"/>
+      <c r="E158" s="15"/>
+      <c r="F158" s="20"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>158</v>
       </c>
@@ -3552,14 +3902,15 @@
         <v>161</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E159" s="16"/>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E159" s="15"/>
+      <c r="F159" s="20"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>159</v>
       </c>
@@ -3567,14 +3918,13 @@
         <v>162</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D160" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E160" s="16"/>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D160" s="4"/>
+      <c r="E160" s="15"/>
+      <c r="F160" s="20"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>160</v>
       </c>
@@ -3582,14 +3932,15 @@
         <v>163</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E161" s="16"/>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E161" s="15"/>
+      <c r="F161" s="20"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>161</v>
       </c>
@@ -3597,14 +3948,15 @@
         <v>164</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E162" s="16"/>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E162" s="15"/>
+      <c r="F162" s="20"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>162</v>
       </c>
@@ -3612,14 +3964,13 @@
         <v>165</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E163" s="16"/>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D163" s="4"/>
+      <c r="E163" s="15"/>
+      <c r="F163" s="20"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>163</v>
       </c>
@@ -3627,14 +3978,15 @@
         <v>166</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E164" s="16"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E164" s="15"/>
+      <c r="F164" s="20"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>164</v>
       </c>
@@ -3642,14 +3994,15 @@
         <v>167</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E165" s="16"/>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E165" s="15"/>
+      <c r="F165" s="20"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>165</v>
       </c>
@@ -3657,14 +4010,13 @@
         <v>168</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D166" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E166" s="16"/>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D166" s="4"/>
+      <c r="E166" s="15"/>
+      <c r="F166" s="20"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>166</v>
       </c>
@@ -3672,14 +4024,15 @@
         <v>169</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E167" s="16"/>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E167" s="15"/>
+      <c r="F167" s="20"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>167</v>
       </c>
@@ -3687,14 +4040,15 @@
         <v>170</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E168" s="16"/>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E168" s="15"/>
+      <c r="F168" s="20"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>168</v>
       </c>
@@ -3702,14 +4056,15 @@
         <v>171</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E169" s="16"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E169" s="15"/>
+      <c r="F169" s="20"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>169</v>
       </c>
@@ -3717,14 +4072,13 @@
         <v>172</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E170" s="16"/>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D170" s="4"/>
+      <c r="E170" s="15"/>
+      <c r="F170" s="20"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>170</v>
       </c>
@@ -3732,14 +4086,15 @@
         <v>173</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E171" s="16"/>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E171" s="15"/>
+      <c r="F171" s="20"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>171</v>
       </c>
@@ -3747,14 +4102,15 @@
         <v>174</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E172" s="16"/>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E172" s="15"/>
+      <c r="F172" s="20"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>172</v>
       </c>
@@ -3762,14 +4118,15 @@
         <v>175</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E173" s="16"/>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E173" s="15"/>
+      <c r="F173" s="20"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>173</v>
       </c>
@@ -3777,14 +4134,15 @@
         <v>176</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E174" s="16"/>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E174" s="15"/>
+      <c r="F174" s="20"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>174</v>
       </c>
@@ -3792,14 +4150,13 @@
         <v>177</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E175" s="16"/>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D175" s="4"/>
+      <c r="E175" s="15"/>
+      <c r="F175" s="20"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>175</v>
       </c>
@@ -3807,14 +4164,15 @@
         <v>178</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E176" s="16"/>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E176" s="15"/>
+      <c r="F176" s="20"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>176</v>
       </c>
@@ -3822,14 +4180,15 @@
         <v>179</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E177" s="16"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E177" s="15"/>
+      <c r="F177" s="20"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>177</v>
       </c>
@@ -3837,14 +4196,15 @@
         <v>180</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E178" s="16"/>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E178" s="15"/>
+      <c r="F178" s="20"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>178</v>
       </c>
@@ -3852,14 +4212,15 @@
         <v>181</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E179" s="16"/>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E179" s="15"/>
+      <c r="F179" s="20"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>179</v>
       </c>
@@ -3867,14 +4228,15 @@
         <v>182</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E180" s="16"/>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="E180" s="15"/>
+      <c r="F180" s="20"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>180</v>
       </c>
@@ -3882,14 +4244,13 @@
         <v>183</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D181" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E181" s="16"/>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="D181" s="4"/>
+      <c r="E181" s="15"/>
+      <c r="F181" s="20"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>181</v>
       </c>
@@ -3897,90 +4258,1136 @@
         <v>184</v>
       </c>
       <c r="C182" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E182" s="15"/>
+      <c r="F182" s="20"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="4">
+        <v>182</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D183" s="4"/>
+      <c r="E183" s="15"/>
+      <c r="F183" s="20"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="4">
+        <v>183</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D184" s="4"/>
+      <c r="E184" s="15"/>
+      <c r="F184" s="20"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="4">
+        <v>184</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D185" s="4"/>
+      <c r="E185" s="15"/>
+      <c r="F185" s="20"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="4">
+        <v>185</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D186" s="4"/>
+      <c r="E186" s="15"/>
+      <c r="F186" s="20"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="4">
+        <v>186</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D187" s="4"/>
+      <c r="E187" s="15"/>
+      <c r="F187" s="20"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="4">
+        <v>187</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D188" s="4"/>
+      <c r="E188" s="15"/>
+      <c r="F188" s="20"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="4">
+        <v>188</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D189" s="4"/>
+      <c r="E189" s="15"/>
+      <c r="F189" s="20"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="4">
+        <v>189</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D190" s="4"/>
+      <c r="E190" s="15"/>
+      <c r="F190" s="20"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="4">
+        <v>190</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D191" s="4"/>
+      <c r="E191" s="15"/>
+      <c r="F191" s="20"/>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="4">
         <v>191</v>
       </c>
-      <c r="D182" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E182" s="16"/>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A184" s="11">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185" s="11">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A186" s="11">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187" s="11">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A188" s="11">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A189" s="11">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A190" s="11">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A191" s="11">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A192" s="11">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A193" s="11">
+      <c r="B192" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D192" s="4"/>
+      <c r="E192" s="15"/>
+      <c r="F192" s="20"/>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="4">
         <v>192</v>
       </c>
-    </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A194" s="11">
+      <c r="B193" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D193" s="4"/>
+      <c r="E193" s="15"/>
+      <c r="F193" s="20"/>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="4">
         <v>193</v>
       </c>
-    </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A195" s="11">
+      <c r="B194" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D194" s="4"/>
+      <c r="E194" s="15"/>
+      <c r="F194" s="20"/>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="4">
         <v>194</v>
       </c>
-    </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A196" s="11">
+      <c r="B195" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D195" s="4"/>
+      <c r="E195" s="15"/>
+      <c r="F195" s="20"/>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="4">
         <v>195</v>
       </c>
-    </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A197" s="11">
+      <c r="B196" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D196" s="4"/>
+      <c r="E196" s="15"/>
+      <c r="F196" s="20"/>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="4">
         <v>196</v>
       </c>
-    </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A198" s="11">
+      <c r="B197" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D197" s="4"/>
+      <c r="E197" s="15"/>
+      <c r="F197" s="20"/>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="4">
         <v>197</v>
       </c>
+      <c r="B198" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D198" s="4"/>
+      <c r="E198" s="15"/>
+      <c r="F198" s="20"/>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="4">
+        <v>198</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D199" s="4"/>
+      <c r="E199" s="15"/>
+      <c r="F199" s="20"/>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="4">
+        <v>199</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D200" s="4"/>
+      <c r="E200" s="15"/>
+      <c r="F200" s="20"/>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="4">
+        <v>200</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D201" s="4"/>
+      <c r="E201" s="15"/>
+      <c r="F201" s="20"/>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="4">
+        <v>201</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D202" s="4"/>
+      <c r="E202" s="15"/>
+      <c r="F202" s="20"/>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="4">
+        <v>202</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D203" s="4"/>
+      <c r="E203" s="15"/>
+      <c r="F203" s="20"/>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="4">
+        <v>203</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D204" s="4"/>
+      <c r="E204" s="15"/>
+      <c r="F204" s="20"/>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="4">
+        <v>204</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D205" s="4"/>
+      <c r="E205" s="15"/>
+      <c r="F205" s="20"/>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="4">
+        <v>205</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D206" s="4"/>
+      <c r="E206" s="15"/>
+      <c r="F206" s="20"/>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="4">
+        <v>206</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D207" s="4"/>
+      <c r="E207" s="15"/>
+      <c r="F207" s="20"/>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="4">
+        <v>207</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D208" s="4"/>
+      <c r="E208" s="15"/>
+      <c r="F208" s="20"/>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="4">
+        <v>208</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D209" s="4"/>
+      <c r="E209" s="15"/>
+      <c r="F209" s="20"/>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="4">
+        <v>209</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D210" s="4"/>
+      <c r="E210" s="15"/>
+      <c r="F210" s="20"/>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="4">
+        <v>210</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D211" s="4"/>
+      <c r="E211" s="15"/>
+      <c r="F211" s="20"/>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" s="4">
+        <v>211</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D212" s="4"/>
+      <c r="E212" s="15"/>
+      <c r="F212" s="20"/>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" s="4">
+        <v>212</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D213" s="4"/>
+      <c r="E213" s="15"/>
+      <c r="F213" s="20"/>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" s="4">
+        <v>213</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D214" s="4"/>
+      <c r="E214" s="15"/>
+      <c r="F214" s="20"/>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" s="4">
+        <v>214</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D215" s="4"/>
+      <c r="E215" s="15"/>
+      <c r="F215" s="20"/>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" s="4">
+        <v>215</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D216" s="4"/>
+      <c r="E216" s="15"/>
+      <c r="F216" s="20"/>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" s="4">
+        <v>216</v>
+      </c>
+      <c r="B217" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D217" s="4"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="20"/>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" s="4">
+        <v>217</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D218" s="4"/>
+      <c r="E218" s="15"/>
+      <c r="F218" s="20"/>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" s="4">
+        <v>218</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D219" s="4"/>
+      <c r="E219" s="15"/>
+      <c r="F219" s="20"/>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" s="4">
+        <v>219</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D220" s="4"/>
+      <c r="E220" s="15"/>
+      <c r="F220" s="20"/>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" s="4">
+        <v>220</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D221" s="4"/>
+      <c r="E221" s="15"/>
+      <c r="F221" s="20"/>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" s="4">
+        <v>221</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D222" s="4"/>
+      <c r="E222" s="15"/>
+      <c r="F222" s="20"/>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" s="4">
+        <v>222</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D223" s="4"/>
+      <c r="E223" s="15"/>
+      <c r="F223" s="20"/>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" s="4">
+        <v>223</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D224" s="4"/>
+      <c r="E224" s="15"/>
+      <c r="F224" s="20"/>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" s="4">
+        <v>224</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D225" s="4"/>
+      <c r="E225" s="15"/>
+      <c r="F225" s="20"/>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" s="4">
+        <v>225</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D226" s="4"/>
+      <c r="E226" s="15"/>
+      <c r="F226" s="20"/>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" s="4">
+        <v>226</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D227" s="4"/>
+      <c r="E227" s="15"/>
+      <c r="F227" s="20"/>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" s="4">
+        <v>227</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D228" s="4"/>
+      <c r="E228" s="15"/>
+      <c r="F228" s="20"/>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" s="4">
+        <v>228</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D229" s="4"/>
+      <c r="E229" s="15"/>
+      <c r="F229" s="20"/>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="4">
+        <v>229</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D230" s="4"/>
+      <c r="E230" s="15"/>
+      <c r="F230" s="20"/>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" s="4">
+        <v>230</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D231" s="4"/>
+      <c r="E231" s="15"/>
+      <c r="F231" s="20"/>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" s="4">
+        <v>231</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D232" s="4"/>
+      <c r="E232" s="15"/>
+      <c r="F232" s="20"/>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" s="4">
+        <v>232</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D233" s="4"/>
+      <c r="E233" s="15"/>
+      <c r="F233" s="20"/>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" s="4">
+        <v>233</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D234" s="4"/>
+      <c r="E234" s="15"/>
+      <c r="F234" s="20"/>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="4">
+        <v>234</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D235" s="4"/>
+      <c r="E235" s="15"/>
+      <c r="F235" s="20"/>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" s="4">
+        <v>235</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D236" s="4"/>
+      <c r="E236" s="15"/>
+      <c r="F236" s="20"/>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="4">
+        <v>236</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D237" s="4"/>
+      <c r="E237" s="15"/>
+      <c r="F237" s="20"/>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" s="4">
+        <v>237</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D238" s="4"/>
+      <c r="E238" s="15"/>
+      <c r="F238" s="20"/>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" s="4">
+        <v>238</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D239" s="4"/>
+      <c r="E239" s="15"/>
+      <c r="F239" s="20"/>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" s="4">
+        <v>239</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D240" s="4"/>
+      <c r="E240" s="15"/>
+      <c r="F240" s="20"/>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" s="4">
+        <v>240</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D241" s="4"/>
+      <c r="E241" s="15"/>
+      <c r="F241" s="20"/>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" s="4">
+        <v>241</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D242" s="4"/>
+      <c r="E242" s="15"/>
+      <c r="F242" s="20"/>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" s="4">
+        <v>242</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D243" s="4"/>
+      <c r="E243" s="15"/>
+      <c r="F243" s="20"/>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" s="4">
+        <v>243</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D244" s="4"/>
+      <c r="E244" s="15"/>
+      <c r="F244" s="20"/>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" s="4">
+        <v>244</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D245" s="4"/>
+      <c r="E245" s="15"/>
+      <c r="F245" s="20"/>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" s="4">
+        <v>245</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D246" s="4"/>
+      <c r="E246" s="15"/>
+      <c r="F246" s="20"/>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" s="4">
+        <v>246</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D247" s="4"/>
+      <c r="E247" s="15"/>
+      <c r="F247" s="20"/>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" s="4">
+        <v>247</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D248" s="4"/>
+      <c r="E248" s="15"/>
+      <c r="F248" s="20"/>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249" s="4">
+        <v>248</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D249" s="4"/>
+      <c r="E249" s="15"/>
+      <c r="F249" s="20"/>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" s="4">
+        <v>249</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D250" s="4"/>
+      <c r="E250" s="15"/>
+      <c r="F250" s="20"/>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" s="4">
+        <v>250</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D251" s="4"/>
+      <c r="E251" s="15"/>
+      <c r="F251" s="20"/>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" s="4">
+        <v>251</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D252" s="4"/>
+      <c r="E252" s="15"/>
+      <c r="F252" s="20"/>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" s="4">
+        <v>252</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D253" s="4"/>
+      <c r="E253" s="15"/>
+      <c r="F253" s="20"/>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" s="4">
+        <v>253</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D254" s="4"/>
+      <c r="E254" s="15"/>
+      <c r="F254" s="20"/>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" s="4">
+        <v>254</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D255" s="4"/>
+      <c r="E255" s="15"/>
+      <c r="F255" s="20"/>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" s="4">
+        <v>255</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D256" s="4"/>
+      <c r="E256" s="15"/>
+      <c r="F256" s="20"/>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" s="4">
+        <v>256</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D257" s="4"/>
+      <c r="E257" s="15"/>
+      <c r="F257" s="20"/>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" s="4">
+        <v>257</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D258" s="4"/>
+      <c r="E258" s="15"/>
+      <c r="F258" s="20"/>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" s="4">
+        <v>258</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D259" s="4"/>
+      <c r="E259" s="15"/>
+      <c r="F259" s="20"/>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" s="4">
+        <v>259</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D260" s="4"/>
+      <c r="E260" s="15"/>
+      <c r="F260" s="20"/>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" s="4">
+        <v>260</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D261" s="4"/>
+      <c r="E261" s="15"/>
+      <c r="F261" s="20"/>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" s="4">
+        <v>261</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="D262" s="4"/>
+      <c r="E262" s="15"/>
+      <c r="F262" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D198" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <autoFilter ref="A1:D262" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
   <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92351AD8-913C-40FF-8C73-46DE3B4510E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6CFD46-037C-4E7C-809E-239342C500FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -612,12 +612,6 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>Khách đã lắp, lỗi không sáng đèn led, gửi lại X-Force bảo hành (01/07/2026)</t>
-  </si>
-  <si>
-    <t>Gửi lại X-Force bảo hành (01/07/2026)</t>
-  </si>
-  <si>
     <t>VNET861385071518677</t>
   </si>
   <si>
@@ -859,6 +853,12 @@
   </si>
   <si>
     <t>02/07/2026</t>
+  </si>
+  <si>
+    <t>Gửi lại X-Force bảo hành (02/07/2026)</t>
+  </si>
+  <si>
+    <t>Khách đã lắp, lỗi không sáng đèn led, gửi lại X-Force bảo hành (02/07/2026)</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1587,7 @@
         <v>103</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="9"/>
@@ -3400,7 +3400,7 @@
         <v>185</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>195</v>
+        <v>275</v>
       </c>
       <c r="F126" s="20"/>
     </row>
@@ -4271,10 +4271,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="15"/>
@@ -4285,10 +4285,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="15"/>
@@ -4299,10 +4299,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D185" s="4"/>
       <c r="E185" s="15"/>
@@ -4313,10 +4313,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="15"/>
@@ -4327,10 +4327,10 @@
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="15"/>
@@ -4341,10 +4341,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="15"/>
@@ -4355,10 +4355,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="15"/>
@@ -4369,10 +4369,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="15"/>
@@ -4383,10 +4383,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="15"/>
@@ -4397,10 +4397,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="15"/>
@@ -4411,10 +4411,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="15"/>
@@ -4425,10 +4425,10 @@
         <v>193</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="15"/>
@@ -4439,10 +4439,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D195" s="4"/>
       <c r="E195" s="15"/>
@@ -4453,10 +4453,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D196" s="4"/>
       <c r="E196" s="15"/>
@@ -4467,10 +4467,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D197" s="4"/>
       <c r="E197" s="15"/>
@@ -4481,10 +4481,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D198" s="4"/>
       <c r="E198" s="15"/>
@@ -4495,10 +4495,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D199" s="4"/>
       <c r="E199" s="15"/>
@@ -4509,10 +4509,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D200" s="4"/>
       <c r="E200" s="15"/>
@@ -4523,10 +4523,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D201" s="4"/>
       <c r="E201" s="15"/>
@@ -4537,10 +4537,10 @@
         <v>201</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D202" s="4"/>
       <c r="E202" s="15"/>
@@ -4551,10 +4551,10 @@
         <v>202</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D203" s="4"/>
       <c r="E203" s="15"/>
@@ -4565,10 +4565,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D204" s="4"/>
       <c r="E204" s="15"/>
@@ -4579,10 +4579,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D205" s="4"/>
       <c r="E205" s="15"/>
@@ -4593,10 +4593,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D206" s="4"/>
       <c r="E206" s="15"/>
@@ -4607,10 +4607,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D207" s="4"/>
       <c r="E207" s="15"/>
@@ -4621,10 +4621,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D208" s="4"/>
       <c r="E208" s="15"/>
@@ -4635,10 +4635,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="15"/>
@@ -4649,10 +4649,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D210" s="4"/>
       <c r="E210" s="15"/>
@@ -4663,10 +4663,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="15"/>
@@ -4677,10 +4677,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D212" s="4"/>
       <c r="E212" s="15"/>
@@ -4691,10 +4691,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D213" s="4"/>
       <c r="E213" s="15"/>
@@ -4705,10 +4705,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D214" s="4"/>
       <c r="E214" s="15"/>
@@ -4719,10 +4719,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D215" s="4"/>
       <c r="E215" s="15"/>
@@ -4733,10 +4733,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D216" s="4"/>
       <c r="E216" s="15"/>
@@ -4747,10 +4747,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D217" s="4"/>
       <c r="E217" s="15"/>
@@ -4761,10 +4761,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D218" s="4"/>
       <c r="E218" s="15"/>
@@ -4775,10 +4775,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D219" s="4"/>
       <c r="E219" s="15"/>
@@ -4789,10 +4789,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D220" s="4"/>
       <c r="E220" s="15"/>
@@ -4803,10 +4803,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D221" s="4"/>
       <c r="E221" s="15"/>
@@ -4817,10 +4817,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D222" s="4"/>
       <c r="E222" s="15"/>
@@ -4831,10 +4831,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D223" s="4"/>
       <c r="E223" s="15"/>
@@ -4845,10 +4845,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D224" s="4"/>
       <c r="E224" s="15"/>
@@ -4859,10 +4859,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D225" s="4"/>
       <c r="E225" s="15"/>
@@ -4873,10 +4873,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D226" s="4"/>
       <c r="E226" s="15"/>
@@ -4887,10 +4887,10 @@
         <v>226</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D227" s="4"/>
       <c r="E227" s="15"/>
@@ -4901,10 +4901,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D228" s="4"/>
       <c r="E228" s="15"/>
@@ -4915,10 +4915,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D229" s="4"/>
       <c r="E229" s="15"/>
@@ -4929,10 +4929,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D230" s="4"/>
       <c r="E230" s="15"/>
@@ -4943,10 +4943,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D231" s="4"/>
       <c r="E231" s="15"/>
@@ -4957,10 +4957,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D232" s="4"/>
       <c r="E232" s="15"/>
@@ -4971,10 +4971,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D233" s="4"/>
       <c r="E233" s="15"/>
@@ -4985,10 +4985,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D234" s="4"/>
       <c r="E234" s="15"/>
@@ -4999,10 +4999,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D235" s="4"/>
       <c r="E235" s="15"/>
@@ -5013,10 +5013,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D236" s="4"/>
       <c r="E236" s="15"/>
@@ -5027,10 +5027,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D237" s="4"/>
       <c r="E237" s="15"/>
@@ -5041,10 +5041,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D238" s="4"/>
       <c r="E238" s="15"/>
@@ -5055,10 +5055,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D239" s="4"/>
       <c r="E239" s="15"/>
@@ -5069,10 +5069,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D240" s="4"/>
       <c r="E240" s="15"/>
@@ -5083,10 +5083,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D241" s="4"/>
       <c r="E241" s="15"/>
@@ -5097,10 +5097,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D242" s="4"/>
       <c r="E242" s="15"/>
@@ -5111,10 +5111,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D243" s="4"/>
       <c r="E243" s="15"/>
@@ -5125,10 +5125,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="15"/>
@@ -5139,10 +5139,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="15"/>
@@ -5153,10 +5153,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D246" s="4"/>
       <c r="E246" s="15"/>
@@ -5167,10 +5167,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D247" s="4"/>
       <c r="E247" s="15"/>
@@ -5181,10 +5181,10 @@
         <v>247</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D248" s="4"/>
       <c r="E248" s="15"/>
@@ -5195,10 +5195,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D249" s="4"/>
       <c r="E249" s="15"/>
@@ -5209,10 +5209,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D250" s="4"/>
       <c r="E250" s="15"/>
@@ -5223,10 +5223,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D251" s="4"/>
       <c r="E251" s="15"/>
@@ -5237,10 +5237,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D252" s="4"/>
       <c r="E252" s="15"/>
@@ -5251,10 +5251,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D253" s="4"/>
       <c r="E253" s="15"/>
@@ -5265,10 +5265,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D254" s="4"/>
       <c r="E254" s="15"/>
@@ -5279,10 +5279,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D255" s="4"/>
       <c r="E255" s="15"/>
@@ -5293,10 +5293,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D256" s="4"/>
       <c r="E256" s="15"/>
@@ -5307,10 +5307,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D257" s="4"/>
       <c r="E257" s="15"/>
@@ -5321,10 +5321,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D258" s="4"/>
       <c r="E258" s="15"/>
@@ -5335,10 +5335,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D259" s="4"/>
       <c r="E259" s="15"/>
@@ -5349,10 +5349,10 @@
         <v>259</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D260" s="4"/>
       <c r="E260" s="15"/>
@@ -5363,10 +5363,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D261" s="4"/>
       <c r="E261" s="15"/>
@@ -5377,10 +5377,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D262" s="4"/>
       <c r="E262" s="15"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6CFD46-037C-4E7C-809E-239342C500FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CD96C0-1423-4D07-859E-5727DA1A078B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
+    <workbookView minimized="1" xWindow="7200" yWindow="3855" windowWidth="21600" windowHeight="11835" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
   <sheets>
     <sheet name="ID_VNSH03" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$D$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="279">
   <si>
     <t>STT</t>
   </si>
@@ -859,6 +859,12 @@
   </si>
   <si>
     <t>Khách đã lắp, lỗi không sáng đèn led, gửi lại X-Force bảo hành (02/07/2026)</t>
+  </si>
+  <si>
+    <t>Anh Thông đang giữ</t>
+  </si>
+  <si>
+    <t>Test trên web không thấy online</t>
   </si>
 </sst>
 </file>
@@ -951,7 +957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1005,6 +1011,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3494,7 +3501,9 @@
       <c r="C132" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D132" s="4"/>
+      <c r="D132" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E132" s="15"/>
       <c r="F132" s="20"/>
     </row>
@@ -3646,7 +3655,9 @@
       <c r="C142" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D142" s="4"/>
+      <c r="D142" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E142" s="15"/>
       <c r="F142" s="20"/>
     </row>
@@ -3660,7 +3671,9 @@
       <c r="C143" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D143" s="4"/>
+      <c r="D143" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E143" s="15"/>
       <c r="F143" s="20"/>
     </row>
@@ -3722,7 +3735,9 @@
       <c r="C147" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D147" s="4"/>
+      <c r="D147" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E147" s="15"/>
       <c r="F147" s="20"/>
     </row>
@@ -3736,7 +3751,9 @@
       <c r="C148" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D148" s="4"/>
+      <c r="D148" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E148" s="15"/>
       <c r="F148" s="20"/>
     </row>
@@ -3750,7 +3767,9 @@
       <c r="C149" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D149" s="4"/>
+      <c r="D149" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E149" s="15"/>
       <c r="F149" s="20"/>
     </row>
@@ -3828,7 +3847,9 @@
       <c r="C154" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D154" s="4"/>
+      <c r="D154" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E154" s="15"/>
       <c r="F154" s="20"/>
     </row>
@@ -3890,7 +3911,9 @@
       <c r="C158" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D158" s="4"/>
+      <c r="D158" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E158" s="15"/>
       <c r="F158" s="20"/>
     </row>
@@ -3920,7 +3943,9 @@
       <c r="C160" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D160" s="4"/>
+      <c r="D160" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E160" s="15"/>
       <c r="F160" s="20"/>
     </row>
@@ -4012,7 +4037,9 @@
       <c r="C166" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D166" s="4"/>
+      <c r="D166" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E166" s="15"/>
       <c r="F166" s="20"/>
     </row>
@@ -4074,7 +4101,9 @@
       <c r="C170" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D170" s="4"/>
+      <c r="D170" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E170" s="15"/>
       <c r="F170" s="20"/>
     </row>
@@ -4152,7 +4181,9 @@
       <c r="C175" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D175" s="4"/>
+      <c r="D175" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E175" s="15"/>
       <c r="F175" s="20"/>
     </row>
@@ -4246,8 +4277,12 @@
       <c r="C181" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D181" s="4"/>
-      <c r="E181" s="15"/>
+      <c r="D181" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="E181" s="21" t="s">
+        <v>278</v>
+      </c>
       <c r="F181" s="20"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5387,7 +5422,7 @@
       <c r="F262" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D262" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <autoFilter ref="A1:E1" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
   <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
@@ -5395,5 +5430,6 @@
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07CD96C0-1423-4D07-859E-5727DA1A078B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A6FD04-5B46-4DA5-930D-6B9847A57F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="7200" yWindow="3855" windowWidth="21600" windowHeight="11835" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
   <sheets>
     <sheet name="ID_VNSH03" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="279">
   <si>
     <t>STT</t>
   </si>
@@ -957,7 +957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1012,6 +1012,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1390,7 +1393,7 @@
         <v>103</v>
       </c>
       <c r="E2" s="15"/>
-      <c r="F2" s="5"/>
+      <c r="F2" s="22"/>
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1407,7 +1410,7 @@
         <v>103</v>
       </c>
       <c r="E3" s="15"/>
-      <c r="F3" s="5"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1424,7 +1427,7 @@
         <v>103</v>
       </c>
       <c r="E4" s="15"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1441,7 +1444,7 @@
         <v>103</v>
       </c>
       <c r="E5" s="15"/>
-      <c r="F5" s="5"/>
+      <c r="F5" s="22"/>
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1458,7 +1461,7 @@
         <v>103</v>
       </c>
       <c r="E6" s="15"/>
-      <c r="F6" s="5"/>
+      <c r="F6" s="22"/>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1475,7 +1478,7 @@
         <v>103</v>
       </c>
       <c r="E7" s="15"/>
-      <c r="F7" s="5"/>
+      <c r="F7" s="22"/>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1492,7 +1495,7 @@
         <v>103</v>
       </c>
       <c r="E8" s="15"/>
-      <c r="F8" s="5"/>
+      <c r="F8" s="22"/>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1509,7 +1512,7 @@
         <v>103</v>
       </c>
       <c r="E9" s="15"/>
-      <c r="F9" s="5"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1526,7 +1529,7 @@
         <v>103</v>
       </c>
       <c r="E10" s="15"/>
-      <c r="F10" s="5"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1543,7 +1546,7 @@
         <v>103</v>
       </c>
       <c r="E11" s="15"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="22"/>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1560,7 +1563,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="15"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1577,7 +1580,7 @@
         <v>103</v>
       </c>
       <c r="E13" s="15"/>
-      <c r="F13" s="5"/>
+      <c r="F13" s="22"/>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -1596,7 +1599,7 @@
       <c r="E14" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="F14" s="5"/>
+      <c r="F14" s="22"/>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1613,7 +1616,7 @@
         <v>103</v>
       </c>
       <c r="E15" s="15"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="22"/>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1630,7 +1633,7 @@
         <v>103</v>
       </c>
       <c r="E16" s="15"/>
-      <c r="F16" s="5"/>
+      <c r="F16" s="22"/>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1647,7 +1650,7 @@
         <v>103</v>
       </c>
       <c r="E17" s="15"/>
-      <c r="F17" s="5"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1664,7 +1667,7 @@
         <v>103</v>
       </c>
       <c r="E18" s="15"/>
-      <c r="F18" s="5"/>
+      <c r="F18" s="22"/>
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1681,7 +1684,7 @@
         <v>103</v>
       </c>
       <c r="E19" s="15"/>
-      <c r="F19" s="5"/>
+      <c r="F19" s="22"/>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1698,7 +1701,7 @@
         <v>103</v>
       </c>
       <c r="E20" s="15"/>
-      <c r="F20" s="5"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1715,7 +1718,7 @@
         <v>103</v>
       </c>
       <c r="E21" s="15"/>
-      <c r="F21" s="5"/>
+      <c r="F21" s="22"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1732,7 +1735,7 @@
         <v>103</v>
       </c>
       <c r="E22" s="15"/>
-      <c r="F22" s="5"/>
+      <c r="F22" s="22"/>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1749,7 +1752,7 @@
         <v>103</v>
       </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="5"/>
+      <c r="F23" s="22"/>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1766,7 +1769,7 @@
         <v>103</v>
       </c>
       <c r="E24" s="15"/>
-      <c r="F24" s="5"/>
+      <c r="F24" s="22"/>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -3533,7 +3536,9 @@
       <c r="C134" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D134" s="4"/>
+      <c r="D134" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E134" s="15"/>
       <c r="F134" s="20"/>
     </row>
@@ -3547,7 +3552,9 @@
       <c r="C135" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D135" s="4"/>
+      <c r="D135" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E135" s="15"/>
       <c r="F135" s="20"/>
     </row>
@@ -3593,7 +3600,9 @@
       <c r="C138" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D138" s="4"/>
+      <c r="D138" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E138" s="15"/>
       <c r="F138" s="20"/>
     </row>
@@ -3991,7 +4000,9 @@
       <c r="C163" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D163" s="4"/>
+      <c r="D163" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E163" s="15"/>
       <c r="F163" s="20"/>
     </row>
@@ -4325,7 +4336,9 @@
       <c r="C184" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D184" s="4"/>
+      <c r="D184" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E184" s="15"/>
       <c r="F184" s="20"/>
     </row>
@@ -4381,7 +4394,9 @@
       <c r="C188" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D188" s="4"/>
+      <c r="D188" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E188" s="15"/>
       <c r="F188" s="20"/>
     </row>
@@ -4409,7 +4424,9 @@
       <c r="C190" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D190" s="4"/>
+      <c r="D190" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E190" s="15"/>
       <c r="F190" s="20"/>
     </row>
@@ -4423,7 +4440,9 @@
       <c r="C191" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D191" s="4"/>
+      <c r="D191" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E191" s="15"/>
       <c r="F191" s="20"/>
     </row>
@@ -4437,7 +4456,9 @@
       <c r="C192" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D192" s="4"/>
+      <c r="D192" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E192" s="15"/>
       <c r="F192" s="20"/>
     </row>
@@ -4479,7 +4500,9 @@
       <c r="C195" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D195" s="4"/>
+      <c r="D195" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E195" s="15"/>
       <c r="F195" s="20"/>
     </row>
@@ -4507,7 +4530,9 @@
       <c r="C197" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D197" s="4"/>
+      <c r="D197" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E197" s="15"/>
       <c r="F197" s="20"/>
     </row>
@@ -4535,7 +4560,9 @@
       <c r="C199" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D199" s="4"/>
+      <c r="D199" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E199" s="15"/>
       <c r="F199" s="20"/>
     </row>
@@ -4549,7 +4576,9 @@
       <c r="C200" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D200" s="4"/>
+      <c r="D200" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E200" s="15"/>
       <c r="F200" s="20"/>
     </row>
@@ -4591,7 +4620,9 @@
       <c r="C203" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D203" s="4"/>
+      <c r="D203" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E203" s="15"/>
       <c r="F203" s="20"/>
     </row>
@@ -4647,7 +4678,9 @@
       <c r="C207" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D207" s="4"/>
+      <c r="D207" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E207" s="15"/>
       <c r="F207" s="20"/>
     </row>
@@ -4689,7 +4722,9 @@
       <c r="C210" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D210" s="4"/>
+      <c r="D210" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E210" s="15"/>
       <c r="F210" s="20"/>
     </row>
@@ -4703,7 +4738,9 @@
       <c r="C211" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D211" s="4"/>
+      <c r="D211" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E211" s="15"/>
       <c r="F211" s="20"/>
     </row>
@@ -4717,7 +4754,9 @@
       <c r="C212" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D212" s="4"/>
+      <c r="D212" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E212" s="15"/>
       <c r="F212" s="20"/>
     </row>
@@ -4745,7 +4784,9 @@
       <c r="C214" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D214" s="4"/>
+      <c r="D214" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E214" s="15"/>
       <c r="F214" s="20"/>
     </row>
@@ -4815,7 +4856,9 @@
       <c r="C219" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D219" s="4"/>
+      <c r="D219" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E219" s="15"/>
       <c r="F219" s="20"/>
     </row>
@@ -4871,7 +4914,9 @@
       <c r="C223" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D223" s="4"/>
+      <c r="D223" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E223" s="15"/>
       <c r="F223" s="20"/>
     </row>
@@ -4955,7 +5000,9 @@
       <c r="C229" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D229" s="4"/>
+      <c r="D229" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E229" s="15"/>
       <c r="F229" s="20"/>
     </row>
@@ -4997,7 +5044,9 @@
       <c r="C232" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D232" s="4"/>
+      <c r="D232" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E232" s="15"/>
       <c r="F232" s="20"/>
     </row>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A6FD04-5B46-4DA5-930D-6B9847A57F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C9B491-C18A-4F23-BBAD-780F5BE485D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ID_VNSH03" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$E$462</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="481">
   <si>
     <t>STT</t>
   </si>
@@ -865,6 +865,612 @@
   </si>
   <si>
     <t>Test trên web không thấy online</t>
+  </si>
+  <si>
+    <t>VNET861385071448404</t>
+  </si>
+  <si>
+    <t>VNET861385071487352</t>
+  </si>
+  <si>
+    <t>VNET861385071450558</t>
+  </si>
+  <si>
+    <t>VNET861385071448339</t>
+  </si>
+  <si>
+    <t>VNET861385071531811</t>
+  </si>
+  <si>
+    <t>VNET861385071449428</t>
+  </si>
+  <si>
+    <t>VNET861385071446978</t>
+  </si>
+  <si>
+    <t>VNET861385071449394</t>
+  </si>
+  <si>
+    <t>VNET861385071456332</t>
+  </si>
+  <si>
+    <t>VNET861385070687440</t>
+  </si>
+  <si>
+    <t>VNET861385071446952</t>
+  </si>
+  <si>
+    <t>VNET861385071486818</t>
+  </si>
+  <si>
+    <t>VNET861385071455052</t>
+  </si>
+  <si>
+    <t>VNET861385071456878</t>
+  </si>
+  <si>
+    <t>VNET861385071456381</t>
+  </si>
+  <si>
+    <t>VNET861385071448545</t>
+  </si>
+  <si>
+    <t>VNET861385070663144</t>
+  </si>
+  <si>
+    <t>VNET861385071457546</t>
+  </si>
+  <si>
+    <t>VNET861385071456274</t>
+  </si>
+  <si>
+    <t>VNET861385071457645</t>
+  </si>
+  <si>
+    <t>VNET861385071447026</t>
+  </si>
+  <si>
+    <t>VNET861385071448560</t>
+  </si>
+  <si>
+    <t>VNET861385071532082</t>
+  </si>
+  <si>
+    <t>VNET861385071455904</t>
+  </si>
+  <si>
+    <t>VNET861385071486685</t>
+  </si>
+  <si>
+    <t>VNET861385071455300</t>
+  </si>
+  <si>
+    <t>VNET861385071448412</t>
+  </si>
+  <si>
+    <t>VNET861385071448453</t>
+  </si>
+  <si>
+    <t>VNET861385071476363</t>
+  </si>
+  <si>
+    <t>VNET861385071456852</t>
+  </si>
+  <si>
+    <t>VNET861385071456324</t>
+  </si>
+  <si>
+    <t>VNET861385071456845</t>
+  </si>
+  <si>
+    <t>VNET861385071448586</t>
+  </si>
+  <si>
+    <t>VNET861385071473774</t>
+  </si>
+  <si>
+    <t>VNET861385071455698</t>
+  </si>
+  <si>
+    <t>VNET861385071527439</t>
+  </si>
+  <si>
+    <t>VNET861385071530797</t>
+  </si>
+  <si>
+    <t>VNET861385071455748</t>
+  </si>
+  <si>
+    <t>VNET861385071448578</t>
+  </si>
+  <si>
+    <t>VNET861385071535044</t>
+  </si>
+  <si>
+    <t>VNET861385071516689</t>
+  </si>
+  <si>
+    <t>VNET861385071450533</t>
+  </si>
+  <si>
+    <t>VNET861385070687283</t>
+  </si>
+  <si>
+    <t>VNET861385070742948</t>
+  </si>
+  <si>
+    <t>VNET861385070687234</t>
+  </si>
+  <si>
+    <t>VNET861385071531761</t>
+  </si>
+  <si>
+    <t>VNET861385071532165</t>
+  </si>
+  <si>
+    <t>VNET861385071448297</t>
+  </si>
+  <si>
+    <t>VNET861385071485323</t>
+  </si>
+  <si>
+    <t>VNET861385071526837</t>
+  </si>
+  <si>
+    <t>VNET861385070686764</t>
+  </si>
+  <si>
+    <t>VNET861385071455417</t>
+  </si>
+  <si>
+    <t>VNET861385071531167</t>
+  </si>
+  <si>
+    <t>VNET861385071527207</t>
+  </si>
+  <si>
+    <t>VNET861385071449154</t>
+  </si>
+  <si>
+    <t>VNET861385071455169</t>
+  </si>
+  <si>
+    <t>VNET861385071526761</t>
+  </si>
+  <si>
+    <t>VNET861385071448966</t>
+  </si>
+  <si>
+    <t>VNET861385071527926</t>
+  </si>
+  <si>
+    <t>VNET861385070611226</t>
+  </si>
+  <si>
+    <t>VNET861385071527892</t>
+  </si>
+  <si>
+    <t>VNET861385071476256</t>
+  </si>
+  <si>
+    <t>VNET861385071455409</t>
+  </si>
+  <si>
+    <t>VNET861385071455573</t>
+  </si>
+  <si>
+    <t>VNET861385071447000</t>
+  </si>
+  <si>
+    <t>VNET861385071531480</t>
+  </si>
+  <si>
+    <t>VNET861385071455433</t>
+  </si>
+  <si>
+    <t>VNET861385071531357</t>
+  </si>
+  <si>
+    <t>VNET861385071531969</t>
+  </si>
+  <si>
+    <t>VNET861385071455938</t>
+  </si>
+  <si>
+    <t>VNET861385071456282</t>
+  </si>
+  <si>
+    <t>VNET861385071457629</t>
+  </si>
+  <si>
+    <t>VNET861385071457538</t>
+  </si>
+  <si>
+    <t>VNET861385071476306</t>
+  </si>
+  <si>
+    <t>VNET861385071531340</t>
+  </si>
+  <si>
+    <t>VNET861385071530805</t>
+  </si>
+  <si>
+    <t>VNET861385071527199</t>
+  </si>
+  <si>
+    <t>VNET861385071531563</t>
+  </si>
+  <si>
+    <t>VNET861385071531738</t>
+  </si>
+  <si>
+    <t>VNET861385071448636</t>
+  </si>
+  <si>
+    <t>VNET861385071531530</t>
+  </si>
+  <si>
+    <t>VNET861385071449451</t>
+  </si>
+  <si>
+    <t>VNET861385071448289</t>
+  </si>
+  <si>
+    <t>VNET861385071517778</t>
+  </si>
+  <si>
+    <t>VNET861385071448305</t>
+  </si>
+  <si>
+    <t>VNET861385071450574</t>
+  </si>
+  <si>
+    <t>VNET861385071486768</t>
+  </si>
+  <si>
+    <t>VNET861385071531696</t>
+  </si>
+  <si>
+    <t>VNET861385071455375</t>
+  </si>
+  <si>
+    <t>VNET861385071486560</t>
+  </si>
+  <si>
+    <t>VNET861385071455318</t>
+  </si>
+  <si>
+    <t>VNET861385071532017</t>
+  </si>
+  <si>
+    <t>VNET861385071456241</t>
+  </si>
+  <si>
+    <t>VNET861385071526811</t>
+  </si>
+  <si>
+    <t>VNET861385071542768</t>
+  </si>
+  <si>
+    <t>VNET861385071531993</t>
+  </si>
+  <si>
+    <t>VNET861385070693778</t>
+  </si>
+  <si>
+    <t>VNET861385071486842</t>
+  </si>
+  <si>
+    <t>VNET861385071449105</t>
+  </si>
+  <si>
+    <t>VNET861385071455565</t>
+  </si>
+  <si>
+    <t>VNET861385071527561</t>
+  </si>
+  <si>
+    <t>VNET861385071476231</t>
+  </si>
+  <si>
+    <t>VNET861385071540705</t>
+  </si>
+  <si>
+    <t>VNET861385071456316</t>
+  </si>
+  <si>
+    <t>VNET861385071455268</t>
+  </si>
+  <si>
+    <t>VNET861385071455391</t>
+  </si>
+  <si>
+    <t>VNET861385071448396</t>
+  </si>
+  <si>
+    <t>VNET861385071528403</t>
+  </si>
+  <si>
+    <t>VNET861385071486941</t>
+  </si>
+  <si>
+    <t>VNET861385071476371</t>
+  </si>
+  <si>
+    <t>VNET861385071455359</t>
+  </si>
+  <si>
+    <t>VNET861385071518685</t>
+  </si>
+  <si>
+    <t>VNET861385071455664</t>
+  </si>
+  <si>
+    <t>VNET861385071455425</t>
+  </si>
+  <si>
+    <t>VNET861385071455334</t>
+  </si>
+  <si>
+    <t>VNET861385071455896</t>
+  </si>
+  <si>
+    <t>VNET861385071448370</t>
+  </si>
+  <si>
+    <t>VNET861385071455656</t>
+  </si>
+  <si>
+    <t>VNET861385071516473</t>
+  </si>
+  <si>
+    <t>VNET861385071455110</t>
+  </si>
+  <si>
+    <t>VNET861385071448313</t>
+  </si>
+  <si>
+    <t>VNET861385071516481</t>
+  </si>
+  <si>
+    <t>VNET861385071455482</t>
+  </si>
+  <si>
+    <t>VNET861385070661239</t>
+  </si>
+  <si>
+    <t>VNET861385070687879</t>
+  </si>
+  <si>
+    <t>VNET861385071455862</t>
+  </si>
+  <si>
+    <t>VNET861385070647949</t>
+  </si>
+  <si>
+    <t>VNET861385071455870</t>
+  </si>
+  <si>
+    <t>VNET861385071527603</t>
+  </si>
+  <si>
+    <t>VNET861385071455730</t>
+  </si>
+  <si>
+    <t>VNET861385071535101</t>
+  </si>
+  <si>
+    <t>VNET861385071527363</t>
+  </si>
+  <si>
+    <t>VNET861385071455136</t>
+  </si>
+  <si>
+    <t>VNET861385071486958</t>
+  </si>
+  <si>
+    <t>VNET861385071516614</t>
+  </si>
+  <si>
+    <t>VNET861385071526688</t>
+  </si>
+  <si>
+    <t>VNET861385070648095</t>
+  </si>
+  <si>
+    <t>VNET861385070694339</t>
+  </si>
+  <si>
+    <t>VNET861385071486834</t>
+  </si>
+  <si>
+    <t>VNET861385070647865</t>
+  </si>
+  <si>
+    <t>VNET861385070623023</t>
+  </si>
+  <si>
+    <t>VNET861385070647204</t>
+  </si>
+  <si>
+    <t>VNET861385071471216</t>
+  </si>
+  <si>
+    <t>VNET861385070693299</t>
+  </si>
+  <si>
+    <t>VNET861385071483476</t>
+  </si>
+  <si>
+    <t>VNET861385070708154</t>
+  </si>
+  <si>
+    <t>VNET861385070693950</t>
+  </si>
+  <si>
+    <t>VNET861385071517711</t>
+  </si>
+  <si>
+    <t>VNET861385070647840</t>
+  </si>
+  <si>
+    <t>VNET861385071530813</t>
+  </si>
+  <si>
+    <t>VNET861385070647709</t>
+  </si>
+  <si>
+    <t>VNET861385070741650</t>
+  </si>
+  <si>
+    <t>VNET861385070647295</t>
+  </si>
+  <si>
+    <t>VNET861385071455383</t>
+  </si>
+  <si>
+    <t>VNET861385071446986</t>
+  </si>
+  <si>
+    <t>VNET861385071489739</t>
+  </si>
+  <si>
+    <t>VNET861385071486883</t>
+  </si>
+  <si>
+    <t>VNET861385071531381</t>
+  </si>
+  <si>
+    <t>VNET861385070624872</t>
+  </si>
+  <si>
+    <t>VNET861385071455888</t>
+  </si>
+  <si>
+    <t>VNET861385070661494</t>
+  </si>
+  <si>
+    <t>VNET861385071531415</t>
+  </si>
+  <si>
+    <t>VNET861385071486875</t>
+  </si>
+  <si>
+    <t>VNET861385070647261</t>
+  </si>
+  <si>
+    <t>VNET861385071486917</t>
+  </si>
+  <si>
+    <t>VNET861385071457173</t>
+  </si>
+  <si>
+    <t>VNET861385071461407</t>
+  </si>
+  <si>
+    <t>VNET861385070625184</t>
+  </si>
+  <si>
+    <t>VNET861385070741767</t>
+  </si>
+  <si>
+    <t>VNET861385070647154</t>
+  </si>
+  <si>
+    <t>VNET861385070688109</t>
+  </si>
+  <si>
+    <t>VNET861385070693935</t>
+  </si>
+  <si>
+    <t>VNET861385070687374</t>
+  </si>
+  <si>
+    <t>VNET861385070686970</t>
+  </si>
+  <si>
+    <t>VNET861385070647543</t>
+  </si>
+  <si>
+    <t>VNET861385070693364</t>
+  </si>
+  <si>
+    <t>VNET861385071486792</t>
+  </si>
+  <si>
+    <t>VNET861385071457108</t>
+  </si>
+  <si>
+    <t>VNET861385071527082</t>
+  </si>
+  <si>
+    <t>VNET861385071486909</t>
+  </si>
+  <si>
+    <t>VNET861385070647584</t>
+  </si>
+  <si>
+    <t>VNET861385071528387</t>
+  </si>
+  <si>
+    <t>VNET861385070692374</t>
+  </si>
+  <si>
+    <t>VNET861385070692838</t>
+  </si>
+  <si>
+    <t>VNET861385070692887</t>
+  </si>
+  <si>
+    <t>VNET861385071530888</t>
+  </si>
+  <si>
+    <t>VNET861385070625226</t>
+  </si>
+  <si>
+    <t>VNET861385070664340</t>
+  </si>
+  <si>
+    <t>VNET861385070647956</t>
+  </si>
+  <si>
+    <t>VNET861385071448610</t>
+  </si>
+  <si>
+    <t>VNET861385071517976</t>
+  </si>
+  <si>
+    <t>VNET861385071455532</t>
+  </si>
+  <si>
+    <t>VNET861385071455466</t>
+  </si>
+  <si>
+    <t>VNET861385070647469</t>
+  </si>
+  <si>
+    <t>VNET861385070647782</t>
+  </si>
+  <si>
+    <t>VNET861385071531985</t>
+  </si>
+  <si>
+    <t>VNET861385070647519</t>
+  </si>
+  <si>
+    <t>VNET861385070606028</t>
+  </si>
+  <si>
+    <t>VNET861385071517216</t>
+  </si>
+  <si>
+    <t>VNET86138507145805</t>
+  </si>
+  <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>ID sai</t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1956,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <dimension ref="A1:G262"/>
+  <dimension ref="A1:G462"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="11" customWidth="1"/>
@@ -1786,7 +2392,7 @@
         <v>103</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="5"/>
+      <c r="F25" s="22"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1803,7 +2409,7 @@
         <v>103</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="5"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1820,7 +2426,7 @@
         <v>103</v>
       </c>
       <c r="E27" s="15"/>
-      <c r="F27" s="5"/>
+      <c r="F27" s="22"/>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -1837,7 +2443,7 @@
         <v>103</v>
       </c>
       <c r="E28" s="15"/>
-      <c r="F28" s="5"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -1854,7 +2460,7 @@
         <v>103</v>
       </c>
       <c r="E29" s="15"/>
-      <c r="F29" s="5"/>
+      <c r="F29" s="22"/>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -1871,7 +2477,7 @@
         <v>103</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="5"/>
+      <c r="F30" s="22"/>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -1888,7 +2494,7 @@
         <v>103</v>
       </c>
       <c r="E31" s="15"/>
-      <c r="F31" s="5"/>
+      <c r="F31" s="22"/>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -1905,7 +2511,7 @@
         <v>103</v>
       </c>
       <c r="E32" s="15"/>
-      <c r="F32" s="5"/>
+      <c r="F32" s="22"/>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1922,7 +2528,7 @@
         <v>103</v>
       </c>
       <c r="E33" s="15"/>
-      <c r="F33" s="5"/>
+      <c r="F33" s="22"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -1938,7 +2544,7 @@
         <v>103</v>
       </c>
       <c r="E34" s="15"/>
-      <c r="F34" s="5"/>
+      <c r="F34" s="22"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -1954,7 +2560,7 @@
         <v>103</v>
       </c>
       <c r="E35" s="15"/>
-      <c r="F35" s="5"/>
+      <c r="F35" s="22"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -1970,7 +2576,7 @@
         <v>103</v>
       </c>
       <c r="E36" s="15"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="22"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -1986,7 +2592,7 @@
         <v>103</v>
       </c>
       <c r="E37" s="15"/>
-      <c r="F37" s="5"/>
+      <c r="F37" s="22"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -2002,7 +2608,7 @@
         <v>103</v>
       </c>
       <c r="E38" s="15"/>
-      <c r="F38" s="5"/>
+      <c r="F38" s="22"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
@@ -2018,7 +2624,7 @@
         <v>103</v>
       </c>
       <c r="E39" s="15"/>
-      <c r="F39" s="5"/>
+      <c r="F39" s="22"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
@@ -2034,7 +2640,7 @@
         <v>103</v>
       </c>
       <c r="E40" s="15"/>
-      <c r="F40" s="5"/>
+      <c r="F40" s="22"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
@@ -2050,7 +2656,7 @@
         <v>103</v>
       </c>
       <c r="E41" s="15"/>
-      <c r="F41" s="5"/>
+      <c r="F41" s="22"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
@@ -4322,7 +4928,9 @@
       <c r="C183" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D183" s="4"/>
+      <c r="D183" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E183" s="15"/>
       <c r="F183" s="20"/>
     </row>
@@ -4352,7 +4960,9 @@
       <c r="C185" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D185" s="4"/>
+      <c r="D185" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E185" s="15"/>
       <c r="F185" s="20"/>
     </row>
@@ -4366,7 +4976,9 @@
       <c r="C186" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D186" s="4"/>
+      <c r="D186" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E186" s="15"/>
       <c r="F186" s="20"/>
     </row>
@@ -4380,7 +4992,9 @@
       <c r="C187" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D187" s="4"/>
+      <c r="D187" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E187" s="15"/>
       <c r="F187" s="20"/>
     </row>
@@ -4410,7 +5024,9 @@
       <c r="C189" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D189" s="4"/>
+      <c r="D189" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E189" s="15"/>
       <c r="F189" s="20"/>
     </row>
@@ -4472,7 +5088,9 @@
       <c r="C193" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D193" s="4"/>
+      <c r="D193" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E193" s="15"/>
       <c r="F193" s="20"/>
     </row>
@@ -4486,7 +5104,9 @@
       <c r="C194" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D194" s="4"/>
+      <c r="D194" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E194" s="15"/>
       <c r="F194" s="20"/>
     </row>
@@ -4516,7 +5136,9 @@
       <c r="C196" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D196" s="4"/>
+      <c r="D196" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E196" s="15"/>
       <c r="F196" s="20"/>
     </row>
@@ -4546,7 +5168,9 @@
       <c r="C198" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D198" s="4"/>
+      <c r="D198" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E198" s="15"/>
       <c r="F198" s="20"/>
     </row>
@@ -4592,7 +5216,9 @@
       <c r="C201" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D201" s="4"/>
+      <c r="D201" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E201" s="15"/>
       <c r="F201" s="20"/>
     </row>
@@ -4606,7 +5232,9 @@
       <c r="C202" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D202" s="4"/>
+      <c r="D202" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E202" s="15"/>
       <c r="F202" s="20"/>
     </row>
@@ -4636,7 +5264,9 @@
       <c r="C204" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D204" s="4"/>
+      <c r="D204" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E204" s="15"/>
       <c r="F204" s="20"/>
     </row>
@@ -4650,7 +5280,9 @@
       <c r="C205" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D205" s="4"/>
+      <c r="D205" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E205" s="15"/>
       <c r="F205" s="20"/>
     </row>
@@ -4664,7 +5296,9 @@
       <c r="C206" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D206" s="4"/>
+      <c r="D206" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E206" s="15"/>
       <c r="F206" s="20"/>
     </row>
@@ -4694,7 +5328,9 @@
       <c r="C208" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D208" s="4"/>
+      <c r="D208" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E208" s="15"/>
       <c r="F208" s="20"/>
     </row>
@@ -4708,7 +5344,9 @@
       <c r="C209" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D209" s="4"/>
+      <c r="D209" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E209" s="15"/>
       <c r="F209" s="20"/>
     </row>
@@ -4800,7 +5438,9 @@
       <c r="C215" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D215" s="4"/>
+      <c r="D215" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E215" s="15"/>
       <c r="F215" s="20"/>
     </row>
@@ -4814,7 +5454,9 @@
       <c r="C216" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D216" s="4"/>
+      <c r="D216" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E216" s="15"/>
       <c r="F216" s="20"/>
     </row>
@@ -4842,7 +5484,9 @@
       <c r="C218" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D218" s="4"/>
+      <c r="D218" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E218" s="15"/>
       <c r="F218" s="20"/>
     </row>
@@ -4872,7 +5516,9 @@
       <c r="C220" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D220" s="4"/>
+      <c r="D220" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E220" s="15"/>
       <c r="F220" s="20"/>
     </row>
@@ -4958,7 +5604,9 @@
       <c r="C226" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D226" s="4"/>
+      <c r="D226" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E226" s="15"/>
       <c r="F226" s="20"/>
     </row>
@@ -4972,7 +5620,9 @@
       <c r="C227" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D227" s="4"/>
+      <c r="D227" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E227" s="15"/>
       <c r="F227" s="20"/>
     </row>
@@ -4986,7 +5636,9 @@
       <c r="C228" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D228" s="4"/>
+      <c r="D228" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E228" s="15"/>
       <c r="F228" s="20"/>
     </row>
@@ -5016,7 +5668,9 @@
       <c r="C230" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D230" s="4"/>
+      <c r="D230" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E230" s="15"/>
       <c r="F230" s="20"/>
     </row>
@@ -5060,7 +5714,9 @@
       <c r="C233" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D233" s="4"/>
+      <c r="D233" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E233" s="15"/>
       <c r="F233" s="20"/>
     </row>
@@ -5074,7 +5730,9 @@
       <c r="C234" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D234" s="4"/>
+      <c r="D234" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E234" s="15"/>
       <c r="F234" s="20"/>
     </row>
@@ -5116,7 +5774,9 @@
       <c r="C237" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D237" s="4"/>
+      <c r="D237" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E237" s="15"/>
       <c r="F237" s="20"/>
     </row>
@@ -5144,7 +5804,9 @@
       <c r="C239" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D239" s="4"/>
+      <c r="D239" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E239" s="15"/>
       <c r="F239" s="20"/>
     </row>
@@ -5186,7 +5848,9 @@
       <c r="C242" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D242" s="4"/>
+      <c r="D242" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E242" s="15"/>
       <c r="F242" s="20"/>
     </row>
@@ -5200,7 +5864,9 @@
       <c r="C243" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D243" s="4"/>
+      <c r="D243" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E243" s="15"/>
       <c r="F243" s="20"/>
     </row>
@@ -5228,7 +5894,9 @@
       <c r="C245" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D245" s="4"/>
+      <c r="D245" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E245" s="15"/>
       <c r="F245" s="20"/>
     </row>
@@ -5242,7 +5910,9 @@
       <c r="C246" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D246" s="4"/>
+      <c r="D246" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E246" s="15"/>
       <c r="F246" s="20"/>
     </row>
@@ -5312,7 +5982,9 @@
       <c r="C251" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D251" s="4"/>
+      <c r="D251" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E251" s="15"/>
       <c r="F251" s="20"/>
     </row>
@@ -5326,7 +5998,9 @@
       <c r="C252" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D252" s="4"/>
+      <c r="D252" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E252" s="15"/>
       <c r="F252" s="20"/>
     </row>
@@ -5340,7 +6014,9 @@
       <c r="C253" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D253" s="4"/>
+      <c r="D253" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E253" s="15"/>
       <c r="F253" s="20"/>
     </row>
@@ -5354,7 +6030,9 @@
       <c r="C254" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D254" s="4"/>
+      <c r="D254" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E254" s="15"/>
       <c r="F254" s="20"/>
     </row>
@@ -5368,7 +6046,9 @@
       <c r="C255" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D255" s="4"/>
+      <c r="D255" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E255" s="15"/>
       <c r="F255" s="20"/>
     </row>
@@ -5382,7 +6062,9 @@
       <c r="C256" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D256" s="4"/>
+      <c r="D256" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E256" s="15"/>
       <c r="F256" s="20"/>
     </row>
@@ -5424,7 +6106,9 @@
       <c r="C259" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D259" s="4"/>
+      <c r="D259" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E259" s="15"/>
       <c r="F259" s="20"/>
     </row>
@@ -5466,12 +6150,2816 @@
       <c r="C262" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D262" s="4"/>
+      <c r="D262" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E262" s="15"/>
       <c r="F262" s="20"/>
     </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" s="4">
+        <v>262</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D263" s="4"/>
+      <c r="E263" s="4"/>
+      <c r="F263" s="4"/>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" s="4">
+        <v>263</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D264" s="4"/>
+      <c r="E264" s="4"/>
+      <c r="F264" s="4"/>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" s="4">
+        <v>264</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D265" s="4"/>
+      <c r="E265" s="4"/>
+      <c r="F265" s="4"/>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" s="4">
+        <v>265</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D266" s="4"/>
+      <c r="E266" s="4"/>
+      <c r="F266" s="4"/>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" s="4">
+        <v>266</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D267" s="4"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="4"/>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" s="4">
+        <v>267</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D268" s="4"/>
+      <c r="E268" s="4"/>
+      <c r="F268" s="4"/>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" s="4">
+        <v>268</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D269" s="4"/>
+      <c r="E269" s="4"/>
+      <c r="F269" s="4"/>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" s="4">
+        <v>269</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D270" s="4"/>
+      <c r="E270" s="4"/>
+      <c r="F270" s="4"/>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" s="4">
+        <v>270</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D271" s="4"/>
+      <c r="E271" s="4"/>
+      <c r="F271" s="4"/>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" s="4">
+        <v>271</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D272" s="4"/>
+      <c r="E272" s="4"/>
+      <c r="F272" s="4"/>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" s="4">
+        <v>272</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D273" s="4"/>
+      <c r="E273" s="4"/>
+      <c r="F273" s="4"/>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" s="4">
+        <v>273</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D274" s="4"/>
+      <c r="E274" s="4"/>
+      <c r="F274" s="4"/>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" s="4">
+        <v>274</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D275" s="4"/>
+      <c r="E275" s="4"/>
+      <c r="F275" s="4"/>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" s="4">
+        <v>275</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D276" s="4"/>
+      <c r="E276" s="4"/>
+      <c r="F276" s="4"/>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" s="4">
+        <v>276</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D277" s="4"/>
+      <c r="E277" s="4"/>
+      <c r="F277" s="4"/>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" s="4">
+        <v>277</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D278" s="4"/>
+      <c r="E278" s="4"/>
+      <c r="F278" s="4"/>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" s="4">
+        <v>278</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D279" s="4"/>
+      <c r="E279" s="4"/>
+      <c r="F279" s="4"/>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" s="4">
+        <v>279</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D280" s="4"/>
+      <c r="E280" s="4"/>
+      <c r="F280" s="4"/>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" s="4">
+        <v>280</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D281" s="4"/>
+      <c r="E281" s="4"/>
+      <c r="F281" s="4"/>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" s="4">
+        <v>281</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D282" s="4"/>
+      <c r="E282" s="4"/>
+      <c r="F282" s="4"/>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" s="4">
+        <v>282</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D283" s="4"/>
+      <c r="E283" s="4"/>
+      <c r="F283" s="4"/>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" s="4">
+        <v>283</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D284" s="4"/>
+      <c r="E284" s="4"/>
+      <c r="F284" s="4"/>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" s="4">
+        <v>284</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D285" s="4"/>
+      <c r="E285" s="4"/>
+      <c r="F285" s="4"/>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" s="4">
+        <v>285</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D286" s="4"/>
+      <c r="E286" s="4"/>
+      <c r="F286" s="4"/>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" s="4">
+        <v>286</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D287" s="4"/>
+      <c r="E287" s="4"/>
+      <c r="F287" s="4"/>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" s="4">
+        <v>287</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D288" s="4"/>
+      <c r="E288" s="4"/>
+      <c r="F288" s="4"/>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" s="4">
+        <v>288</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D289" s="4"/>
+      <c r="E289" s="4"/>
+      <c r="F289" s="4"/>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" s="4">
+        <v>289</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D290" s="4"/>
+      <c r="E290" s="4"/>
+      <c r="F290" s="4"/>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" s="4">
+        <v>290</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D291" s="4"/>
+      <c r="E291" s="4"/>
+      <c r="F291" s="4"/>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" s="4">
+        <v>291</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D292" s="4"/>
+      <c r="E292" s="4"/>
+      <c r="F292" s="4"/>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" s="4">
+        <v>292</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D293" s="4"/>
+      <c r="E293" s="4"/>
+      <c r="F293" s="4"/>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" s="4">
+        <v>293</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D294" s="4"/>
+      <c r="E294" s="4"/>
+      <c r="F294" s="4"/>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" s="4">
+        <v>294</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D295" s="4"/>
+      <c r="E295" s="4"/>
+      <c r="F295" s="4"/>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" s="4">
+        <v>295</v>
+      </c>
+      <c r="B296" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D296" s="4"/>
+      <c r="E296" s="4"/>
+      <c r="F296" s="4"/>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" s="4">
+        <v>296</v>
+      </c>
+      <c r="B297" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D297" s="4"/>
+      <c r="E297" s="4"/>
+      <c r="F297" s="4"/>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" s="4">
+        <v>297</v>
+      </c>
+      <c r="B298" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D298" s="4"/>
+      <c r="E298" s="4"/>
+      <c r="F298" s="4"/>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" s="4">
+        <v>298</v>
+      </c>
+      <c r="B299" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D299" s="4"/>
+      <c r="E299" s="4"/>
+      <c r="F299" s="4"/>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" s="4">
+        <v>299</v>
+      </c>
+      <c r="B300" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D300" s="4"/>
+      <c r="E300" s="4"/>
+      <c r="F300" s="4"/>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" s="4">
+        <v>300</v>
+      </c>
+      <c r="B301" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D301" s="4"/>
+      <c r="E301" s="4"/>
+      <c r="F301" s="4"/>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" s="4">
+        <v>301</v>
+      </c>
+      <c r="B302" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D302" s="4"/>
+      <c r="E302" s="4"/>
+      <c r="F302" s="4"/>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" s="4">
+        <v>302</v>
+      </c>
+      <c r="B303" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D303" s="4"/>
+      <c r="E303" s="4"/>
+      <c r="F303" s="4"/>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" s="4">
+        <v>303</v>
+      </c>
+      <c r="B304" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D304" s="4"/>
+      <c r="E304" s="4"/>
+      <c r="F304" s="4"/>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" s="4">
+        <v>304</v>
+      </c>
+      <c r="B305" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D305" s="4"/>
+      <c r="E305" s="4"/>
+      <c r="F305" s="4"/>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" s="4">
+        <v>305</v>
+      </c>
+      <c r="B306" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D306" s="4"/>
+      <c r="E306" s="4"/>
+      <c r="F306" s="4"/>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" s="4">
+        <v>306</v>
+      </c>
+      <c r="B307" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D307" s="4"/>
+      <c r="E307" s="4"/>
+      <c r="F307" s="4"/>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" s="4">
+        <v>307</v>
+      </c>
+      <c r="B308" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D308" s="4"/>
+      <c r="E308" s="4"/>
+      <c r="F308" s="4"/>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A309" s="4">
+        <v>308</v>
+      </c>
+      <c r="B309" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D309" s="4"/>
+      <c r="E309" s="4"/>
+      <c r="F309" s="4"/>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310" s="4">
+        <v>309</v>
+      </c>
+      <c r="B310" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D310" s="4"/>
+      <c r="E310" s="4"/>
+      <c r="F310" s="4"/>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" s="4">
+        <v>310</v>
+      </c>
+      <c r="B311" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D311" s="4"/>
+      <c r="E311" s="4"/>
+      <c r="F311" s="4"/>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" s="4">
+        <v>311</v>
+      </c>
+      <c r="B312" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D312" s="4"/>
+      <c r="E312" s="4"/>
+      <c r="F312" s="4"/>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" s="4">
+        <v>312</v>
+      </c>
+      <c r="B313" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D313" s="4"/>
+      <c r="E313" s="4"/>
+      <c r="F313" s="4"/>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" s="4">
+        <v>313</v>
+      </c>
+      <c r="B314" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D314" s="4"/>
+      <c r="E314" s="4"/>
+      <c r="F314" s="4"/>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" s="4">
+        <v>314</v>
+      </c>
+      <c r="B315" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D315" s="4"/>
+      <c r="E315" s="4"/>
+      <c r="F315" s="4"/>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" s="4">
+        <v>315</v>
+      </c>
+      <c r="B316" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D316" s="4"/>
+      <c r="E316" s="4"/>
+      <c r="F316" s="4"/>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" s="4">
+        <v>316</v>
+      </c>
+      <c r="B317" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D317" s="4"/>
+      <c r="E317" s="4"/>
+      <c r="F317" s="4"/>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" s="4">
+        <v>317</v>
+      </c>
+      <c r="B318" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D318" s="4"/>
+      <c r="E318" s="4"/>
+      <c r="F318" s="4"/>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" s="4">
+        <v>318</v>
+      </c>
+      <c r="B319" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D319" s="4"/>
+      <c r="E319" s="4"/>
+      <c r="F319" s="4"/>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" s="4">
+        <v>319</v>
+      </c>
+      <c r="B320" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D320" s="4"/>
+      <c r="E320" s="4"/>
+      <c r="F320" s="4"/>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A321" s="4">
+        <v>320</v>
+      </c>
+      <c r="B321" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D321" s="4"/>
+      <c r="E321" s="4"/>
+      <c r="F321" s="4"/>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A322" s="4">
+        <v>321</v>
+      </c>
+      <c r="B322" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D322" s="4"/>
+      <c r="E322" s="4"/>
+      <c r="F322" s="4"/>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A323" s="4">
+        <v>322</v>
+      </c>
+      <c r="B323" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D323" s="4"/>
+      <c r="E323" s="4"/>
+      <c r="F323" s="4"/>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A324" s="4">
+        <v>323</v>
+      </c>
+      <c r="B324" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="C324" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D324" s="4"/>
+      <c r="E324" s="4"/>
+      <c r="F324" s="4"/>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A325" s="4">
+        <v>324</v>
+      </c>
+      <c r="B325" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D325" s="4"/>
+      <c r="E325" s="4"/>
+      <c r="F325" s="4"/>
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A326" s="4">
+        <v>325</v>
+      </c>
+      <c r="B326" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D326" s="4"/>
+      <c r="E326" s="4"/>
+      <c r="F326" s="4"/>
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A327" s="4">
+        <v>326</v>
+      </c>
+      <c r="B327" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D327" s="4"/>
+      <c r="E327" s="4"/>
+      <c r="F327" s="4"/>
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A328" s="4">
+        <v>327</v>
+      </c>
+      <c r="B328" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D328" s="4"/>
+      <c r="E328" s="4"/>
+      <c r="F328" s="4"/>
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A329" s="4">
+        <v>328</v>
+      </c>
+      <c r="B329" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D329" s="4"/>
+      <c r="E329" s="4"/>
+      <c r="F329" s="4"/>
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A330" s="4">
+        <v>329</v>
+      </c>
+      <c r="B330" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D330" s="4"/>
+      <c r="E330" s="4"/>
+      <c r="F330" s="4"/>
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A331" s="4">
+        <v>330</v>
+      </c>
+      <c r="B331" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D331" s="4"/>
+      <c r="E331" s="4"/>
+      <c r="F331" s="4"/>
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A332" s="4">
+        <v>331</v>
+      </c>
+      <c r="B332" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C332" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D332" s="4"/>
+      <c r="E332" s="4"/>
+      <c r="F332" s="4"/>
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A333" s="4">
+        <v>332</v>
+      </c>
+      <c r="B333" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C333" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D333" s="4"/>
+      <c r="E333" s="4"/>
+      <c r="F333" s="4"/>
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A334" s="4">
+        <v>333</v>
+      </c>
+      <c r="B334" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C334" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D334" s="4"/>
+      <c r="E334" s="4"/>
+      <c r="F334" s="4"/>
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A335" s="4">
+        <v>334</v>
+      </c>
+      <c r="B335" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D335" s="4"/>
+      <c r="E335" s="4"/>
+      <c r="F335" s="4"/>
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A336" s="4">
+        <v>335</v>
+      </c>
+      <c r="B336" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D336" s="4"/>
+      <c r="E336" s="4"/>
+      <c r="F336" s="4"/>
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A337" s="4">
+        <v>336</v>
+      </c>
+      <c r="B337" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D337" s="4"/>
+      <c r="E337" s="4"/>
+      <c r="F337" s="4"/>
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A338" s="4">
+        <v>337</v>
+      </c>
+      <c r="B338" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D338" s="4"/>
+      <c r="E338" s="4"/>
+      <c r="F338" s="4"/>
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A339" s="4">
+        <v>338</v>
+      </c>
+      <c r="B339" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D339" s="4"/>
+      <c r="E339" s="4"/>
+      <c r="F339" s="4"/>
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A340" s="4">
+        <v>339</v>
+      </c>
+      <c r="B340" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D340" s="4"/>
+      <c r="E340" s="4"/>
+      <c r="F340" s="4"/>
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A341" s="4">
+        <v>340</v>
+      </c>
+      <c r="B341" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D341" s="4"/>
+      <c r="E341" s="4"/>
+      <c r="F341" s="4"/>
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A342" s="4">
+        <v>341</v>
+      </c>
+      <c r="B342" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D342" s="4"/>
+      <c r="E342" s="4"/>
+      <c r="F342" s="4"/>
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A343" s="4">
+        <v>342</v>
+      </c>
+      <c r="B343" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D343" s="4"/>
+      <c r="E343" s="4"/>
+      <c r="F343" s="4"/>
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A344" s="4">
+        <v>343</v>
+      </c>
+      <c r="B344" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D344" s="4"/>
+      <c r="E344" s="4"/>
+      <c r="F344" s="4"/>
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A345" s="4">
+        <v>344</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D345" s="4"/>
+      <c r="E345" s="4"/>
+      <c r="F345" s="4"/>
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A346" s="4">
+        <v>345</v>
+      </c>
+      <c r="B346" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D346" s="4"/>
+      <c r="E346" s="4"/>
+      <c r="F346" s="4"/>
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A347" s="4">
+        <v>346</v>
+      </c>
+      <c r="B347" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D347" s="4"/>
+      <c r="E347" s="4"/>
+      <c r="F347" s="4"/>
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A348" s="4">
+        <v>347</v>
+      </c>
+      <c r="B348" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D348" s="4"/>
+      <c r="E348" s="4"/>
+      <c r="F348" s="4"/>
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A349" s="4">
+        <v>348</v>
+      </c>
+      <c r="B349" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D349" s="4"/>
+      <c r="E349" s="4"/>
+      <c r="F349" s="4"/>
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A350" s="4">
+        <v>349</v>
+      </c>
+      <c r="B350" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D350" s="4"/>
+      <c r="E350" s="4"/>
+      <c r="F350" s="4"/>
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A351" s="4">
+        <v>350</v>
+      </c>
+      <c r="B351" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D351" s="4"/>
+      <c r="E351" s="4"/>
+      <c r="F351" s="4"/>
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A352" s="4">
+        <v>351</v>
+      </c>
+      <c r="B352" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D352" s="4"/>
+      <c r="E352" s="4"/>
+      <c r="F352" s="4"/>
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A353" s="4">
+        <v>352</v>
+      </c>
+      <c r="B353" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D353" s="4"/>
+      <c r="E353" s="4"/>
+      <c r="F353" s="4"/>
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A354" s="4">
+        <v>353</v>
+      </c>
+      <c r="B354" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D354" s="4"/>
+      <c r="E354" s="4"/>
+      <c r="F354" s="4"/>
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A355" s="4">
+        <v>354</v>
+      </c>
+      <c r="B355" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D355" s="4"/>
+      <c r="E355" s="4"/>
+      <c r="F355" s="4"/>
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A356" s="4">
+        <v>355</v>
+      </c>
+      <c r="B356" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D356" s="4"/>
+      <c r="E356" s="4"/>
+      <c r="F356" s="4"/>
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" s="4">
+        <v>356</v>
+      </c>
+      <c r="B357" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D357" s="4"/>
+      <c r="E357" s="4"/>
+      <c r="F357" s="4"/>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" s="4">
+        <v>357</v>
+      </c>
+      <c r="B358" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D358" s="4"/>
+      <c r="E358" s="4"/>
+      <c r="F358" s="4"/>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A359" s="4">
+        <v>358</v>
+      </c>
+      <c r="B359" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D359" s="4"/>
+      <c r="E359" s="4"/>
+      <c r="F359" s="4"/>
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A360" s="4">
+        <v>359</v>
+      </c>
+      <c r="B360" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D360" s="4"/>
+      <c r="E360" s="4"/>
+      <c r="F360" s="4"/>
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A361" s="4">
+        <v>360</v>
+      </c>
+      <c r="B361" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D361" s="4"/>
+      <c r="E361" s="4"/>
+      <c r="F361" s="4"/>
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A362" s="4">
+        <v>361</v>
+      </c>
+      <c r="B362" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D362" s="4"/>
+      <c r="E362" s="4"/>
+      <c r="F362" s="4"/>
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A363" s="4">
+        <v>362</v>
+      </c>
+      <c r="B363" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C363" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D363" s="4"/>
+      <c r="E363" s="4"/>
+      <c r="F363" s="4"/>
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A364" s="4">
+        <v>363</v>
+      </c>
+      <c r="B364" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D364" s="4"/>
+      <c r="E364" s="4"/>
+      <c r="F364" s="4"/>
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A365" s="4">
+        <v>364</v>
+      </c>
+      <c r="B365" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D365" s="4"/>
+      <c r="E365" s="4"/>
+      <c r="F365" s="4"/>
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A366" s="4">
+        <v>365</v>
+      </c>
+      <c r="B366" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D366" s="4"/>
+      <c r="E366" s="4"/>
+      <c r="F366" s="4"/>
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A367" s="4">
+        <v>366</v>
+      </c>
+      <c r="B367" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="C367" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D367" s="4"/>
+      <c r="E367" s="4"/>
+      <c r="F367" s="4"/>
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A368" s="4">
+        <v>367</v>
+      </c>
+      <c r="B368" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C368" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D368" s="4"/>
+      <c r="E368" s="4"/>
+      <c r="F368" s="4"/>
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A369" s="4">
+        <v>368</v>
+      </c>
+      <c r="B369" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="C369" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D369" s="4"/>
+      <c r="E369" s="4"/>
+      <c r="F369" s="4"/>
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A370" s="4">
+        <v>369</v>
+      </c>
+      <c r="B370" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D370" s="4"/>
+      <c r="E370" s="4"/>
+      <c r="F370" s="4"/>
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A371" s="4">
+        <v>370</v>
+      </c>
+      <c r="B371" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="C371" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D371" s="4"/>
+      <c r="E371" s="4"/>
+      <c r="F371" s="4"/>
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A372" s="4">
+        <v>371</v>
+      </c>
+      <c r="B372" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D372" s="4"/>
+      <c r="E372" s="4"/>
+      <c r="F372" s="4"/>
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A373" s="4">
+        <v>372</v>
+      </c>
+      <c r="B373" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C373" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D373" s="4"/>
+      <c r="E373" s="4"/>
+      <c r="F373" s="4"/>
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A374" s="4">
+        <v>373</v>
+      </c>
+      <c r="B374" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C374" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D374" s="4"/>
+      <c r="E374" s="4"/>
+      <c r="F374" s="4"/>
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A375" s="4">
+        <v>374</v>
+      </c>
+      <c r="B375" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C375" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D375" s="4"/>
+      <c r="E375" s="4"/>
+      <c r="F375" s="4"/>
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A376" s="4">
+        <v>375</v>
+      </c>
+      <c r="B376" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D376" s="4"/>
+      <c r="E376" s="4"/>
+      <c r="F376" s="4"/>
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A377" s="4">
+        <v>376</v>
+      </c>
+      <c r="B377" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="C377" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D377" s="4"/>
+      <c r="E377" s="4"/>
+      <c r="F377" s="4"/>
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A378" s="4">
+        <v>377</v>
+      </c>
+      <c r="B378" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D378" s="4"/>
+      <c r="E378" s="4"/>
+      <c r="F378" s="4"/>
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A379" s="4">
+        <v>378</v>
+      </c>
+      <c r="B379" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D379" s="4"/>
+      <c r="E379" s="4"/>
+      <c r="F379" s="4"/>
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A380" s="4">
+        <v>379</v>
+      </c>
+      <c r="B380" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D380" s="4"/>
+      <c r="E380" s="4"/>
+      <c r="F380" s="4"/>
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A381" s="4">
+        <v>380</v>
+      </c>
+      <c r="B381" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D381" s="4"/>
+      <c r="E381" s="4"/>
+      <c r="F381" s="4"/>
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A382" s="4">
+        <v>381</v>
+      </c>
+      <c r="B382" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D382" s="4"/>
+      <c r="E382" s="4"/>
+      <c r="F382" s="4"/>
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A383" s="4">
+        <v>382</v>
+      </c>
+      <c r="B383" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="C383" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D383" s="4"/>
+      <c r="E383" s="4"/>
+      <c r="F383" s="4"/>
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A384" s="4">
+        <v>383</v>
+      </c>
+      <c r="B384" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D384" s="4"/>
+      <c r="E384" s="4"/>
+      <c r="F384" s="4"/>
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A385" s="4">
+        <v>384</v>
+      </c>
+      <c r="B385" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D385" s="4"/>
+      <c r="E385" s="4"/>
+      <c r="F385" s="4"/>
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A386" s="4">
+        <v>385</v>
+      </c>
+      <c r="B386" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D386" s="4"/>
+      <c r="E386" s="4"/>
+      <c r="F386" s="4"/>
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A387" s="4">
+        <v>386</v>
+      </c>
+      <c r="B387" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D387" s="4"/>
+      <c r="E387" s="4"/>
+      <c r="F387" s="4"/>
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A388" s="4">
+        <v>387</v>
+      </c>
+      <c r="B388" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D388" s="4"/>
+      <c r="E388" s="4"/>
+      <c r="F388" s="4"/>
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A389" s="4">
+        <v>388</v>
+      </c>
+      <c r="B389" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="C389" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D389" s="4"/>
+      <c r="E389" s="4"/>
+      <c r="F389" s="4"/>
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A390" s="4">
+        <v>389</v>
+      </c>
+      <c r="B390" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C390" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D390" s="4"/>
+      <c r="E390" s="4"/>
+      <c r="F390" s="4"/>
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A391" s="4">
+        <v>390</v>
+      </c>
+      <c r="B391" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="C391" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D391" s="4"/>
+      <c r="E391" s="4"/>
+      <c r="F391" s="4"/>
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A392" s="4">
+        <v>391</v>
+      </c>
+      <c r="B392" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="C392" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D392" s="4"/>
+      <c r="E392" s="4"/>
+      <c r="F392" s="4"/>
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A393" s="4">
+        <v>392</v>
+      </c>
+      <c r="B393" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D393" s="4"/>
+      <c r="E393" s="4"/>
+      <c r="F393" s="4"/>
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A394" s="4">
+        <v>393</v>
+      </c>
+      <c r="B394" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C394" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D394" s="4"/>
+      <c r="E394" s="4"/>
+      <c r="F394" s="4"/>
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A395" s="4">
+        <v>394</v>
+      </c>
+      <c r="B395" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="C395" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D395" s="4"/>
+      <c r="E395" s="4"/>
+      <c r="F395" s="4"/>
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A396" s="4">
+        <v>395</v>
+      </c>
+      <c r="B396" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="C396" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D396" s="4"/>
+      <c r="E396" s="4"/>
+      <c r="F396" s="4"/>
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A397" s="4">
+        <v>396</v>
+      </c>
+      <c r="B397" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C397" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D397" s="4"/>
+      <c r="E397" s="4"/>
+      <c r="F397" s="4"/>
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A398" s="4">
+        <v>397</v>
+      </c>
+      <c r="B398" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="C398" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D398" s="4"/>
+      <c r="E398" s="4"/>
+      <c r="F398" s="4"/>
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A399" s="4">
+        <v>398</v>
+      </c>
+      <c r="B399" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C399" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D399" s="4"/>
+      <c r="E399" s="4"/>
+      <c r="F399" s="4"/>
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A400" s="4">
+        <v>399</v>
+      </c>
+      <c r="B400" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C400" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D400" s="4"/>
+      <c r="E400" s="4"/>
+      <c r="F400" s="4"/>
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A401" s="4">
+        <v>400</v>
+      </c>
+      <c r="B401" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="C401" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D401" s="4"/>
+      <c r="E401" s="4"/>
+      <c r="F401" s="4"/>
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A402" s="4">
+        <v>401</v>
+      </c>
+      <c r="B402" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C402" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D402" s="4"/>
+      <c r="E402" s="4"/>
+      <c r="F402" s="4"/>
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A403" s="4">
+        <v>402</v>
+      </c>
+      <c r="B403" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="C403" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D403" s="4"/>
+      <c r="E403" s="4"/>
+      <c r="F403" s="4"/>
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A404" s="4">
+        <v>403</v>
+      </c>
+      <c r="B404" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C404" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D404" s="4"/>
+      <c r="E404" s="4"/>
+      <c r="F404" s="4"/>
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A405" s="4">
+        <v>404</v>
+      </c>
+      <c r="B405" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="C405" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D405" s="4"/>
+      <c r="E405" s="4"/>
+      <c r="F405" s="4"/>
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A406" s="4">
+        <v>405</v>
+      </c>
+      <c r="B406" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="C406" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D406" s="4"/>
+      <c r="E406" s="4"/>
+      <c r="F406" s="4"/>
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A407" s="4">
+        <v>406</v>
+      </c>
+      <c r="B407" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="C407" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D407" s="4"/>
+      <c r="E407" s="4"/>
+      <c r="F407" s="4"/>
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A408" s="4">
+        <v>407</v>
+      </c>
+      <c r="B408" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C408" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D408" s="4"/>
+      <c r="E408" s="4"/>
+      <c r="F408" s="4"/>
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A409" s="4">
+        <v>408</v>
+      </c>
+      <c r="B409" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="C409" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D409" s="4"/>
+      <c r="E409" s="4"/>
+      <c r="F409" s="4"/>
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A410" s="4">
+        <v>409</v>
+      </c>
+      <c r="B410" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="C410" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D410" s="4"/>
+      <c r="E410" s="4"/>
+      <c r="F410" s="4"/>
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A411" s="4">
+        <v>410</v>
+      </c>
+      <c r="B411" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C411" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D411" s="4"/>
+      <c r="E411" s="4"/>
+      <c r="F411" s="4"/>
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A412" s="4">
+        <v>411</v>
+      </c>
+      <c r="B412" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="C412" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D412" s="4"/>
+      <c r="E412" s="4"/>
+      <c r="F412" s="4"/>
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A413" s="4">
+        <v>412</v>
+      </c>
+      <c r="B413" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="C413" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D413" s="4"/>
+      <c r="E413" s="4"/>
+      <c r="F413" s="4"/>
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A414" s="4">
+        <v>413</v>
+      </c>
+      <c r="B414" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C414" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D414" s="4"/>
+      <c r="E414" s="4"/>
+      <c r="F414" s="4"/>
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A415" s="4">
+        <v>414</v>
+      </c>
+      <c r="B415" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="C415" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D415" s="4"/>
+      <c r="E415" s="4"/>
+      <c r="F415" s="4"/>
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A416" s="4">
+        <v>415</v>
+      </c>
+      <c r="B416" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="C416" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D416" s="4"/>
+      <c r="E416" s="4"/>
+      <c r="F416" s="4"/>
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A417" s="4">
+        <v>416</v>
+      </c>
+      <c r="B417" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="C417" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D417" s="4"/>
+      <c r="E417" s="4"/>
+      <c r="F417" s="4"/>
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A418" s="4">
+        <v>417</v>
+      </c>
+      <c r="B418" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="C418" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D418" s="4"/>
+      <c r="E418" s="4"/>
+      <c r="F418" s="4"/>
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A419" s="4">
+        <v>418</v>
+      </c>
+      <c r="B419" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="C419" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D419" s="4"/>
+      <c r="E419" s="4"/>
+      <c r="F419" s="4"/>
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A420" s="4">
+        <v>419</v>
+      </c>
+      <c r="B420" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="C420" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D420" s="4"/>
+      <c r="E420" s="4"/>
+      <c r="F420" s="4"/>
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A421" s="4">
+        <v>420</v>
+      </c>
+      <c r="B421" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="C421" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D421" s="4"/>
+      <c r="E421" s="4"/>
+      <c r="F421" s="4"/>
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A422" s="4">
+        <v>421</v>
+      </c>
+      <c r="B422" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C422" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D422" s="4"/>
+      <c r="E422" s="4"/>
+      <c r="F422" s="4"/>
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A423" s="4">
+        <v>422</v>
+      </c>
+      <c r="B423" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="C423" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D423" s="4"/>
+      <c r="E423" s="4"/>
+      <c r="F423" s="4"/>
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A424" s="4">
+        <v>423</v>
+      </c>
+      <c r="B424" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="C424" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D424" s="4"/>
+      <c r="E424" s="4"/>
+      <c r="F424" s="4"/>
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A425" s="4">
+        <v>424</v>
+      </c>
+      <c r="B425" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="C425" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D425" s="4"/>
+      <c r="E425" s="4"/>
+      <c r="F425" s="4"/>
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A426" s="4">
+        <v>425</v>
+      </c>
+      <c r="B426" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C426" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D426" s="4"/>
+      <c r="E426" s="4"/>
+      <c r="F426" s="4"/>
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A427" s="4">
+        <v>426</v>
+      </c>
+      <c r="B427" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C427" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D427" s="4"/>
+      <c r="E427" s="4"/>
+      <c r="F427" s="4"/>
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A428" s="4">
+        <v>427</v>
+      </c>
+      <c r="B428" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C428" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D428" s="4"/>
+      <c r="E428" s="4"/>
+      <c r="F428" s="4"/>
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A429" s="4">
+        <v>428</v>
+      </c>
+      <c r="B429" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C429" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D429" s="4"/>
+      <c r="E429" s="4"/>
+      <c r="F429" s="4"/>
+    </row>
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A430" s="4">
+        <v>429</v>
+      </c>
+      <c r="B430" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C430" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D430" s="4"/>
+      <c r="E430" s="4"/>
+      <c r="F430" s="4"/>
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A431" s="4">
+        <v>430</v>
+      </c>
+      <c r="B431" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="C431" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D431" s="4"/>
+      <c r="E431" s="4"/>
+      <c r="F431" s="4"/>
+    </row>
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A432" s="4">
+        <v>431</v>
+      </c>
+      <c r="B432" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="C432" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D432" s="4"/>
+      <c r="E432" s="4"/>
+      <c r="F432" s="4"/>
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A433" s="4">
+        <v>432</v>
+      </c>
+      <c r="B433" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C433" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D433" s="4"/>
+      <c r="E433" s="4"/>
+      <c r="F433" s="4"/>
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A434" s="4">
+        <v>433</v>
+      </c>
+      <c r="B434" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="C434" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D434" s="4"/>
+      <c r="E434" s="4"/>
+      <c r="F434" s="4"/>
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A435" s="4">
+        <v>434</v>
+      </c>
+      <c r="B435" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="C435" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D435" s="4"/>
+      <c r="E435" s="4"/>
+      <c r="F435" s="4"/>
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A436" s="4">
+        <v>435</v>
+      </c>
+      <c r="B436" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="C436" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D436" s="4"/>
+      <c r="E436" s="4"/>
+      <c r="F436" s="4"/>
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A437" s="4">
+        <v>436</v>
+      </c>
+      <c r="B437" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C437" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D437" s="4"/>
+      <c r="E437" s="4"/>
+      <c r="F437" s="4"/>
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A438" s="4">
+        <v>437</v>
+      </c>
+      <c r="B438" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="C438" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D438" s="4"/>
+      <c r="E438" s="4"/>
+      <c r="F438" s="4"/>
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A439" s="4">
+        <v>438</v>
+      </c>
+      <c r="B439" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C439" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D439" s="4"/>
+      <c r="E439" s="4"/>
+      <c r="F439" s="4"/>
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A440" s="4">
+        <v>439</v>
+      </c>
+      <c r="B440" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="C440" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D440" s="4"/>
+      <c r="E440" s="4"/>
+      <c r="F440" s="4"/>
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A441" s="4">
+        <v>440</v>
+      </c>
+      <c r="B441" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="C441" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D441" s="4"/>
+      <c r="E441" s="4"/>
+      <c r="F441" s="4"/>
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A442" s="4">
+        <v>441</v>
+      </c>
+      <c r="B442" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="C442" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D442" s="4"/>
+      <c r="E442" s="4"/>
+      <c r="F442" s="4"/>
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A443" s="4">
+        <v>442</v>
+      </c>
+      <c r="B443" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C443" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D443" s="4"/>
+      <c r="E443" s="4"/>
+      <c r="F443" s="4"/>
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A444" s="4">
+        <v>443</v>
+      </c>
+      <c r="B444" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="C444" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D444" s="4"/>
+      <c r="E444" s="4"/>
+      <c r="F444" s="4"/>
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A445" s="4">
+        <v>444</v>
+      </c>
+      <c r="B445" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="C445" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D445" s="4"/>
+      <c r="E445" s="4"/>
+      <c r="F445" s="4"/>
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A446" s="4">
+        <v>445</v>
+      </c>
+      <c r="B446" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C446" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D446" s="4"/>
+      <c r="E446" s="4"/>
+      <c r="F446" s="4"/>
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A447" s="4">
+        <v>446</v>
+      </c>
+      <c r="B447" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="C447" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D447" s="4"/>
+      <c r="E447" s="4"/>
+      <c r="F447" s="4"/>
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A448" s="4">
+        <v>447</v>
+      </c>
+      <c r="B448" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="C448" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D448" s="4"/>
+      <c r="E448" s="4"/>
+      <c r="F448" s="4"/>
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A449" s="4">
+        <v>448</v>
+      </c>
+      <c r="B449" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="C449" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D449" s="4"/>
+      <c r="E449" s="4"/>
+      <c r="F449" s="4"/>
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A450" s="4">
+        <v>449</v>
+      </c>
+      <c r="B450" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="C450" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D450" s="4"/>
+      <c r="E450" s="4"/>
+      <c r="F450" s="4"/>
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A451" s="4">
+        <v>450</v>
+      </c>
+      <c r="B451" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C451" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D451" s="4"/>
+      <c r="E451" s="4"/>
+      <c r="F451" s="4"/>
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A452" s="4">
+        <v>451</v>
+      </c>
+      <c r="B452" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C452" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D452" s="4"/>
+      <c r="E452" s="4"/>
+      <c r="F452" s="4"/>
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A453" s="4">
+        <v>452</v>
+      </c>
+      <c r="B453" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C453" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D453" s="4"/>
+      <c r="E453" s="4"/>
+      <c r="F453" s="4"/>
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A454" s="4">
+        <v>453</v>
+      </c>
+      <c r="B454" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="C454" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D454" s="4"/>
+      <c r="E454" s="4"/>
+      <c r="F454" s="4"/>
+    </row>
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A455" s="4">
+        <v>454</v>
+      </c>
+      <c r="B455" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C455" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D455" s="4"/>
+      <c r="E455" s="4"/>
+      <c r="F455" s="4"/>
+    </row>
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A456" s="4">
+        <v>455</v>
+      </c>
+      <c r="B456" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="C456" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D456" s="4"/>
+      <c r="E456" s="4"/>
+      <c r="F456" s="4"/>
+    </row>
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A457" s="4">
+        <v>456</v>
+      </c>
+      <c r="B457" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C457" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D457" s="4"/>
+      <c r="E457" s="4"/>
+      <c r="F457" s="4"/>
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A458" s="4">
+        <v>457</v>
+      </c>
+      <c r="B458" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="C458" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D458" s="4"/>
+      <c r="E458" s="4"/>
+      <c r="F458" s="4"/>
+    </row>
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A459" s="4">
+        <v>458</v>
+      </c>
+      <c r="B459" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="C459" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D459" s="4"/>
+      <c r="E459" s="4"/>
+      <c r="F459" s="4"/>
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A460" s="4">
+        <v>459</v>
+      </c>
+      <c r="B460" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="C460" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D460" s="4"/>
+      <c r="E460" s="4"/>
+      <c r="F460" s="4"/>
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A461" s="4">
+        <v>460</v>
+      </c>
+      <c r="B461" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C461" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D461" s="4"/>
+      <c r="E461" s="4"/>
+      <c r="F461" s="4"/>
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A462" s="4">
+        <v>461</v>
+      </c>
+      <c r="B462" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C462" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D462" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="E462" s="4"/>
+      <c r="F462" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <autoFilter ref="A1:E462" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
   <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C9B491-C18A-4F23-BBAD-780F5BE485D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEAE6E8-AB43-45A8-9A59-DAEA81094561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="481">
   <si>
     <t>STT</t>
   </si>
@@ -5408,7 +5408,9 @@
       <c r="C213" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D213" s="4"/>
+      <c r="D213" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E213" s="15"/>
       <c r="F213" s="20"/>
     </row>
@@ -5470,7 +5472,9 @@
       <c r="C217" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D217" s="4"/>
+      <c r="D217" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E217" s="15"/>
       <c r="F217" s="20"/>
     </row>
@@ -5546,7 +5550,9 @@
       <c r="C222" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D222" s="4"/>
+      <c r="D222" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E222" s="15"/>
       <c r="F222" s="20"/>
     </row>
@@ -5576,7 +5582,9 @@
       <c r="C224" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D224" s="4"/>
+      <c r="D224" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E224" s="15"/>
       <c r="F224" s="20"/>
     </row>
@@ -5684,7 +5692,9 @@
       <c r="C231" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D231" s="4"/>
+      <c r="D231" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E231" s="15"/>
       <c r="F231" s="20"/>
     </row>
@@ -5760,7 +5770,9 @@
       <c r="C236" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D236" s="4"/>
+      <c r="D236" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E236" s="15"/>
       <c r="F236" s="20"/>
     </row>
@@ -5790,7 +5802,9 @@
       <c r="C238" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D238" s="4"/>
+      <c r="D238" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E238" s="15"/>
       <c r="F238" s="20"/>
     </row>
@@ -5820,7 +5834,9 @@
       <c r="C240" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D240" s="4"/>
+      <c r="D240" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E240" s="15"/>
       <c r="F240" s="20"/>
     </row>
@@ -5880,7 +5896,9 @@
       <c r="C244" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D244" s="4"/>
+      <c r="D244" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E244" s="15"/>
       <c r="F244" s="20"/>
     </row>
@@ -5926,7 +5944,9 @@
       <c r="C247" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D247" s="4"/>
+      <c r="D247" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E247" s="15"/>
       <c r="F247" s="20"/>
     </row>
@@ -5940,7 +5960,9 @@
       <c r="C248" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D248" s="4"/>
+      <c r="D248" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E248" s="15"/>
       <c r="F248" s="20"/>
     </row>
@@ -5954,7 +5976,9 @@
       <c r="C249" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D249" s="4"/>
+      <c r="D249" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E249" s="15"/>
       <c r="F249" s="20"/>
     </row>
@@ -5968,7 +5992,9 @@
       <c r="C250" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D250" s="4"/>
+      <c r="D250" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E250" s="15"/>
       <c r="F250" s="20"/>
     </row>
@@ -6092,7 +6118,9 @@
       <c r="C258" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D258" s="4"/>
+      <c r="D258" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E258" s="15"/>
       <c r="F258" s="20"/>
     </row>
@@ -6122,7 +6150,9 @@
       <c r="C260" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D260" s="4"/>
+      <c r="D260" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E260" s="15"/>
       <c r="F260" s="20"/>
     </row>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECEAE6E8-AB43-45A8-9A59-DAEA81094561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C02B78-A2A6-4F7C-B149-2168A3E6E82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C02B78-A2A6-4F7C-B149-2168A3E6E82C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CBC074-E7A5-4BF7-8316-5A1851B506C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="482">
   <si>
     <t>STT</t>
   </si>
@@ -1471,6 +1471,9 @@
   </si>
   <si>
     <t>ID sai</t>
+  </si>
+  <si>
+    <t>Victory trả về, lỗi không LED trạng thái</t>
   </si>
 </sst>
 </file>
@@ -5030,7 +5033,7 @@
       <c r="E189" s="15"/>
       <c r="F189" s="20"/>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -5043,7 +5046,9 @@
       <c r="D190" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E190" s="15"/>
+      <c r="E190" s="17" t="s">
+        <v>481</v>
+      </c>
       <c r="F190" s="20"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3CBC074-E7A5-4BF7-8316-5A1851B506C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E942955-DDAC-446E-802B-5A7E4D27169D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="482">
   <si>
     <t>STT</t>
   </si>
@@ -1566,7 +1566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1622,6 +1622,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2002,7 +2005,9 @@
         <v>103</v>
       </c>
       <c r="E2" s="15"/>
-      <c r="F2" s="22"/>
+      <c r="F2" s="22" t="s">
+        <v>360</v>
+      </c>
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2019,7 +2024,9 @@
         <v>103</v>
       </c>
       <c r="E3" s="15"/>
-      <c r="F3" s="22"/>
+      <c r="F3" s="22" t="s">
+        <v>353</v>
+      </c>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2036,7 +2043,9 @@
         <v>103</v>
       </c>
       <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
+      <c r="F4" s="22" t="s">
+        <v>298</v>
+      </c>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2053,7 +2062,9 @@
         <v>103</v>
       </c>
       <c r="E5" s="15"/>
-      <c r="F5" s="22"/>
+      <c r="F5" s="22" t="s">
+        <v>285</v>
+      </c>
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2070,7 +2081,9 @@
         <v>103</v>
       </c>
       <c r="E6" s="15"/>
-      <c r="F6" s="22"/>
+      <c r="F6" s="22" t="s">
+        <v>349</v>
+      </c>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2087,7 +2100,9 @@
         <v>103</v>
       </c>
       <c r="E7" s="15"/>
-      <c r="F7" s="22"/>
+      <c r="F7" s="22" t="s">
+        <v>293</v>
+      </c>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2104,7 +2119,9 @@
         <v>103</v>
       </c>
       <c r="E8" s="15"/>
-      <c r="F8" s="22"/>
+      <c r="F8" s="22" t="s">
+        <v>297</v>
+      </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2121,7 +2138,9 @@
         <v>103</v>
       </c>
       <c r="E9" s="15"/>
-      <c r="F9" s="22"/>
+      <c r="F9" s="22" t="s">
+        <v>279</v>
+      </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2138,7 +2157,9 @@
         <v>103</v>
       </c>
       <c r="E10" s="15"/>
-      <c r="F10" s="22"/>
+      <c r="F10" s="22" t="s">
+        <v>362</v>
+      </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2155,7 +2176,9 @@
         <v>103</v>
       </c>
       <c r="E11" s="15"/>
-      <c r="F11" s="22"/>
+      <c r="F11" s="22" t="s">
+        <v>361</v>
+      </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2172,7 +2195,9 @@
         <v>103</v>
       </c>
       <c r="E12" s="15"/>
-      <c r="F12" s="22"/>
+      <c r="F12" s="22" t="s">
+        <v>352</v>
+      </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2189,7 +2214,9 @@
         <v>103</v>
       </c>
       <c r="E13" s="15"/>
-      <c r="F13" s="22"/>
+      <c r="F13" s="22" t="s">
+        <v>345</v>
+      </c>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2208,7 +2235,9 @@
       <c r="E14" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="F14" s="22"/>
+      <c r="F14" s="22" t="s">
+        <v>332</v>
+      </c>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2225,7 +2254,9 @@
         <v>103</v>
       </c>
       <c r="E15" s="15"/>
-      <c r="F15" s="22"/>
+      <c r="F15" s="22" t="s">
+        <v>378</v>
+      </c>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2242,7 +2273,9 @@
         <v>103</v>
       </c>
       <c r="E16" s="15"/>
-      <c r="F16" s="22"/>
+      <c r="F16" s="23" t="s">
+        <v>340</v>
+      </c>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2259,7 +2292,9 @@
         <v>103</v>
       </c>
       <c r="E17" s="15"/>
-      <c r="F17" s="22"/>
+      <c r="F17" s="23" t="s">
+        <v>473</v>
+      </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2276,7 +2311,9 @@
         <v>103</v>
       </c>
       <c r="E18" s="15"/>
-      <c r="F18" s="22"/>
+      <c r="F18" s="23" t="s">
+        <v>356</v>
+      </c>
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2293,7 +2330,9 @@
         <v>103</v>
       </c>
       <c r="E19" s="15"/>
-      <c r="F19" s="22"/>
+      <c r="F19" s="23" t="s">
+        <v>359</v>
+      </c>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2310,7 +2349,9 @@
         <v>103</v>
       </c>
       <c r="E20" s="15"/>
-      <c r="F20" s="22"/>
+      <c r="F20" s="23" t="s">
+        <v>409</v>
+      </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2327,7 +2368,9 @@
         <v>103</v>
       </c>
       <c r="E21" s="15"/>
-      <c r="F21" s="22"/>
+      <c r="F21" s="23" t="s">
+        <v>381</v>
+      </c>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2344,7 +2387,9 @@
         <v>103</v>
       </c>
       <c r="E22" s="15"/>
-      <c r="F22" s="22"/>
+      <c r="F22" s="23" t="s">
+        <v>430</v>
+      </c>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2361,7 +2406,9 @@
         <v>103</v>
       </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="22"/>
+      <c r="F23" s="23" t="s">
+        <v>446</v>
+      </c>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2378,7 +2425,9 @@
         <v>103</v>
       </c>
       <c r="E24" s="15"/>
-      <c r="F24" s="22"/>
+      <c r="F24" s="23" t="s">
+        <v>416</v>
+      </c>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2395,7 +2444,9 @@
         <v>103</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="22"/>
+      <c r="F25" s="23" t="s">
+        <v>420</v>
+      </c>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2412,7 +2463,9 @@
         <v>103</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="22"/>
+      <c r="F26" s="23" t="s">
+        <v>428</v>
+      </c>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2429,7 +2482,9 @@
         <v>103</v>
       </c>
       <c r="E27" s="15"/>
-      <c r="F27" s="22"/>
+      <c r="F27" s="23" t="s">
+        <v>475</v>
+      </c>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2446,7 +2501,9 @@
         <v>103</v>
       </c>
       <c r="E28" s="15"/>
-      <c r="F28" s="22"/>
+      <c r="F28" s="23" t="s">
+        <v>426</v>
+      </c>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2463,7 +2520,9 @@
         <v>103</v>
       </c>
       <c r="E29" s="15"/>
-      <c r="F29" s="22"/>
+      <c r="F29" s="23" t="s">
+        <v>474</v>
+      </c>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2480,7 +2539,9 @@
         <v>103</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="22"/>
+      <c r="F30" s="23" t="s">
+        <v>419</v>
+      </c>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2497,7 +2558,9 @@
         <v>103</v>
       </c>
       <c r="E31" s="15"/>
-      <c r="F31" s="22"/>
+      <c r="F31" s="23" t="s">
+        <v>467</v>
+      </c>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2514,7 +2577,9 @@
         <v>103</v>
       </c>
       <c r="E32" s="15"/>
-      <c r="F32" s="22"/>
+      <c r="F32" s="23" t="s">
+        <v>415</v>
+      </c>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2531,7 +2596,9 @@
         <v>103</v>
       </c>
       <c r="E33" s="15"/>
-      <c r="F33" s="22"/>
+      <c r="F33" s="23" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -2547,7 +2614,9 @@
         <v>103</v>
       </c>
       <c r="E34" s="15"/>
-      <c r="F34" s="22"/>
+      <c r="F34" s="23" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -2563,7 +2632,9 @@
         <v>103</v>
       </c>
       <c r="E35" s="15"/>
-      <c r="F35" s="22"/>
+      <c r="F35" s="23" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -2579,7 +2650,9 @@
         <v>103</v>
       </c>
       <c r="E36" s="15"/>
-      <c r="F36" s="22"/>
+      <c r="F36" s="23" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -2595,7 +2668,9 @@
         <v>103</v>
       </c>
       <c r="E37" s="15"/>
-      <c r="F37" s="22"/>
+      <c r="F37" s="23" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -2611,7 +2686,9 @@
         <v>103</v>
       </c>
       <c r="E38" s="15"/>
-      <c r="F38" s="22"/>
+      <c r="F38" s="23" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
@@ -2627,7 +2704,9 @@
         <v>103</v>
       </c>
       <c r="E39" s="15"/>
-      <c r="F39" s="22"/>
+      <c r="F39" s="23" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
@@ -5541,7 +5620,9 @@
       <c r="C221" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D221" s="4"/>
+      <c r="D221" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E221" s="15"/>
       <c r="F221" s="20"/>
     </row>
@@ -5603,7 +5684,9 @@
       <c r="C225" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D225" s="4"/>
+      <c r="D225" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E225" s="15"/>
       <c r="F225" s="20"/>
     </row>
@@ -5761,7 +5844,9 @@
       <c r="C235" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D235" s="4"/>
+      <c r="D235" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E235" s="15"/>
       <c r="F235" s="20"/>
     </row>
@@ -5855,7 +5940,9 @@
       <c r="C241" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D241" s="4"/>
+      <c r="D241" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E241" s="15"/>
       <c r="F241" s="20"/>
     </row>
@@ -6109,7 +6196,9 @@
       <c r="C257" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D257" s="4"/>
+      <c r="D257" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E257" s="15"/>
       <c r="F257" s="20"/>
     </row>
@@ -6171,7 +6260,9 @@
       <c r="C261" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="D261" s="4"/>
+      <c r="D261" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E261" s="15"/>
       <c r="F261" s="20"/>
     </row>
@@ -6201,7 +6292,9 @@
       <c r="C263" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D263" s="4"/>
+      <c r="D263" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E263" s="4"/>
       <c r="F263" s="4"/>
     </row>
@@ -6285,7 +6378,9 @@
       <c r="C269" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D269" s="4"/>
+      <c r="D269" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E269" s="4"/>
       <c r="F269" s="4"/>
     </row>
@@ -6397,7 +6492,9 @@
       <c r="C277" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D277" s="4"/>
+      <c r="D277" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E277" s="4"/>
       <c r="F277" s="4"/>
     </row>
@@ -6453,7 +6550,9 @@
       <c r="C281" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D281" s="4"/>
+      <c r="D281" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E281" s="4"/>
       <c r="F281" s="4"/>
     </row>
@@ -6467,7 +6566,9 @@
       <c r="C282" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D282" s="4"/>
+      <c r="D282" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E282" s="4"/>
       <c r="F282" s="4"/>
     </row>
@@ -6943,7 +7044,9 @@
       <c r="C316" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D316" s="4"/>
+      <c r="D316" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E316" s="4"/>
       <c r="F316" s="4"/>
     </row>
@@ -7055,7 +7158,9 @@
       <c r="C324" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D324" s="4"/>
+      <c r="D324" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E324" s="4"/>
       <c r="F324" s="4"/>
     </row>
@@ -7125,7 +7230,9 @@
       <c r="C329" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D329" s="4"/>
+      <c r="D329" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E329" s="4"/>
       <c r="F329" s="4"/>
     </row>
@@ -7181,7 +7288,9 @@
       <c r="C333" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D333" s="4"/>
+      <c r="D333" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E333" s="4"/>
       <c r="F333" s="4"/>
     </row>
@@ -7223,7 +7332,9 @@
       <c r="C336" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D336" s="4"/>
+      <c r="D336" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E336" s="4"/>
       <c r="F336" s="4"/>
     </row>
@@ -7237,7 +7348,9 @@
       <c r="C337" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D337" s="4"/>
+      <c r="D337" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E337" s="4"/>
       <c r="F337" s="4"/>
     </row>
@@ -7279,7 +7392,9 @@
       <c r="C340" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D340" s="4"/>
+      <c r="D340" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E340" s="4"/>
       <c r="F340" s="4"/>
     </row>
@@ -7321,7 +7436,9 @@
       <c r="C343" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D343" s="4"/>
+      <c r="D343" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E343" s="4"/>
       <c r="F343" s="4"/>
     </row>
@@ -7335,7 +7452,9 @@
       <c r="C344" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D344" s="4"/>
+      <c r="D344" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E344" s="4"/>
       <c r="F344" s="4"/>
     </row>
@@ -7349,7 +7468,9 @@
       <c r="C345" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D345" s="4"/>
+      <c r="D345" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E345" s="4"/>
       <c r="F345" s="4"/>
     </row>
@@ -7363,7 +7484,9 @@
       <c r="C346" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D346" s="4"/>
+      <c r="D346" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E346" s="4"/>
       <c r="F346" s="4"/>
     </row>
@@ -7587,7 +7710,9 @@
       <c r="C362" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D362" s="4"/>
+      <c r="D362" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E362" s="4"/>
       <c r="F362" s="4"/>
     </row>
@@ -7629,7 +7754,9 @@
       <c r="C365" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D365" s="4"/>
+      <c r="D365" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E365" s="4"/>
       <c r="F365" s="4"/>
     </row>
@@ -8021,7 +8148,9 @@
       <c r="C393" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D393" s="4"/>
+      <c r="D393" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E393" s="4"/>
       <c r="F393" s="4"/>
     </row>
@@ -8105,7 +8234,9 @@
       <c r="C399" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D399" s="4"/>
+      <c r="D399" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E399" s="4"/>
       <c r="F399" s="4"/>
     </row>
@@ -8119,7 +8250,9 @@
       <c r="C400" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D400" s="4"/>
+      <c r="D400" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E400" s="4"/>
       <c r="F400" s="4"/>
     </row>
@@ -8161,7 +8294,9 @@
       <c r="C403" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D403" s="4"/>
+      <c r="D403" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E403" s="4"/>
       <c r="F403" s="4"/>
     </row>
@@ -8175,7 +8310,9 @@
       <c r="C404" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D404" s="4"/>
+      <c r="D404" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E404" s="4"/>
       <c r="F404" s="4"/>
     </row>
@@ -8217,7 +8354,9 @@
       <c r="C407" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D407" s="4"/>
+      <c r="D407" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E407" s="4"/>
       <c r="F407" s="4"/>
     </row>
@@ -8259,7 +8398,9 @@
       <c r="C410" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D410" s="4"/>
+      <c r="D410" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E410" s="4"/>
       <c r="F410" s="4"/>
     </row>
@@ -8287,7 +8428,9 @@
       <c r="C412" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D412" s="4"/>
+      <c r="D412" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E412" s="4"/>
       <c r="F412" s="4"/>
     </row>
@@ -8315,7 +8458,9 @@
       <c r="C414" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D414" s="4"/>
+      <c r="D414" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E414" s="4"/>
       <c r="F414" s="4"/>
     </row>
@@ -8539,7 +8684,9 @@
       <c r="C430" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D430" s="4"/>
+      <c r="D430" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E430" s="4"/>
       <c r="F430" s="4"/>
     </row>
@@ -8833,7 +8980,9 @@
       <c r="C451" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D451" s="4"/>
+      <c r="D451" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E451" s="4"/>
       <c r="F451" s="4"/>
     </row>
@@ -8917,7 +9066,9 @@
       <c r="C457" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D457" s="4"/>
+      <c r="D457" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E457" s="4"/>
       <c r="F457" s="4"/>
     </row>
@@ -8931,7 +9082,9 @@
       <c r="C458" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D458" s="4"/>
+      <c r="D458" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E458" s="4"/>
       <c r="F458" s="4"/>
     </row>
@@ -8945,7 +9098,9 @@
       <c r="C459" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D459" s="4"/>
+      <c r="D459" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E459" s="4"/>
       <c r="F459" s="4"/>
     </row>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E942955-DDAC-446E-802B-5A7E4D27169D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ECAAF5-4965-4C00-AC66-FD62D488652E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1263" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="483">
   <si>
     <t>STT</t>
   </si>
@@ -1474,6 +1474,9 @@
   </si>
   <si>
     <t>Victory trả về, lỗi không LED trạng thái</t>
+  </si>
+  <si>
+    <t>Không chốt GPS, IPEX bị lỏng</t>
   </si>
 </sst>
 </file>
@@ -1631,7 +1634,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6423,7 +6436,9 @@
         <v>479</v>
       </c>
       <c r="D272" s="4"/>
-      <c r="E272" s="4"/>
+      <c r="E272" s="4" t="s">
+        <v>482</v>
+      </c>
       <c r="F272" s="4"/>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
@@ -8327,7 +8342,9 @@
         <v>479</v>
       </c>
       <c r="D405" s="4"/>
-      <c r="E405" s="4"/>
+      <c r="E405" s="21" t="s">
+        <v>278</v>
+      </c>
       <c r="F405" s="4"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -9151,10 +9168,13 @@
   </sheetData>
   <autoFilter ref="A1:E462" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
   <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5 B1:B1048576 G1:G1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E272">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48ECAAF5-4965-4C00-AC66-FD62D488652E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9146AD7C-435E-4D1A-A0A7-042512129806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="483">
   <si>
     <t>STT</t>
   </si>
@@ -2018,9 +2018,7 @@
         <v>103</v>
       </c>
       <c r="E2" s="15"/>
-      <c r="F2" s="22" t="s">
-        <v>360</v>
-      </c>
+      <c r="F2" s="22"/>
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2037,9 +2035,7 @@
         <v>103</v>
       </c>
       <c r="E3" s="15"/>
-      <c r="F3" s="22" t="s">
-        <v>353</v>
-      </c>
+      <c r="F3" s="22"/>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2056,9 +2052,7 @@
         <v>103</v>
       </c>
       <c r="E4" s="15"/>
-      <c r="F4" s="22" t="s">
-        <v>298</v>
-      </c>
+      <c r="F4" s="22"/>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2075,9 +2069,7 @@
         <v>103</v>
       </c>
       <c r="E5" s="15"/>
-      <c r="F5" s="22" t="s">
-        <v>285</v>
-      </c>
+      <c r="F5" s="22"/>
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2094,9 +2086,7 @@
         <v>103</v>
       </c>
       <c r="E6" s="15"/>
-      <c r="F6" s="22" t="s">
-        <v>349</v>
-      </c>
+      <c r="F6" s="22"/>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2113,9 +2103,7 @@
         <v>103</v>
       </c>
       <c r="E7" s="15"/>
-      <c r="F7" s="22" t="s">
-        <v>293</v>
-      </c>
+      <c r="F7" s="22"/>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2132,9 +2120,7 @@
         <v>103</v>
       </c>
       <c r="E8" s="15"/>
-      <c r="F8" s="22" t="s">
-        <v>297</v>
-      </c>
+      <c r="F8" s="22"/>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2151,9 +2137,7 @@
         <v>103</v>
       </c>
       <c r="E9" s="15"/>
-      <c r="F9" s="22" t="s">
-        <v>279</v>
-      </c>
+      <c r="F9" s="22"/>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2170,9 +2154,7 @@
         <v>103</v>
       </c>
       <c r="E10" s="15"/>
-      <c r="F10" s="22" t="s">
-        <v>362</v>
-      </c>
+      <c r="F10" s="22"/>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2189,9 +2171,7 @@
         <v>103</v>
       </c>
       <c r="E11" s="15"/>
-      <c r="F11" s="22" t="s">
-        <v>361</v>
-      </c>
+      <c r="F11" s="22"/>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2208,9 +2188,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="15"/>
-      <c r="F12" s="22" t="s">
-        <v>352</v>
-      </c>
+      <c r="F12" s="22"/>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2227,9 +2205,7 @@
         <v>103</v>
       </c>
       <c r="E13" s="15"/>
-      <c r="F13" s="22" t="s">
-        <v>345</v>
-      </c>
+      <c r="F13" s="22"/>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2248,9 +2224,7 @@
       <c r="E14" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="F14" s="22" t="s">
-        <v>332</v>
-      </c>
+      <c r="F14" s="22"/>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2267,9 +2241,7 @@
         <v>103</v>
       </c>
       <c r="E15" s="15"/>
-      <c r="F15" s="22" t="s">
-        <v>378</v>
-      </c>
+      <c r="F15" s="22"/>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2286,9 +2258,7 @@
         <v>103</v>
       </c>
       <c r="E16" s="15"/>
-      <c r="F16" s="23" t="s">
-        <v>340</v>
-      </c>
+      <c r="F16" s="23"/>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2305,9 +2275,7 @@
         <v>103</v>
       </c>
       <c r="E17" s="15"/>
-      <c r="F17" s="23" t="s">
-        <v>473</v>
-      </c>
+      <c r="F17" s="23"/>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2324,9 +2292,7 @@
         <v>103</v>
       </c>
       <c r="E18" s="15"/>
-      <c r="F18" s="23" t="s">
-        <v>356</v>
-      </c>
+      <c r="F18" s="23"/>
       <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2343,9 +2309,7 @@
         <v>103</v>
       </c>
       <c r="E19" s="15"/>
-      <c r="F19" s="23" t="s">
-        <v>359</v>
-      </c>
+      <c r="F19" s="23"/>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2362,9 +2326,7 @@
         <v>103</v>
       </c>
       <c r="E20" s="15"/>
-      <c r="F20" s="23" t="s">
-        <v>409</v>
-      </c>
+      <c r="F20" s="23"/>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2381,9 +2343,7 @@
         <v>103</v>
       </c>
       <c r="E21" s="15"/>
-      <c r="F21" s="23" t="s">
-        <v>381</v>
-      </c>
+      <c r="F21" s="23"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2400,9 +2360,7 @@
         <v>103</v>
       </c>
       <c r="E22" s="15"/>
-      <c r="F22" s="23" t="s">
-        <v>430</v>
-      </c>
+      <c r="F22" s="23"/>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2419,9 +2377,7 @@
         <v>103</v>
       </c>
       <c r="E23" s="15"/>
-      <c r="F23" s="23" t="s">
-        <v>446</v>
-      </c>
+      <c r="F23" s="23"/>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2438,9 +2394,7 @@
         <v>103</v>
       </c>
       <c r="E24" s="15"/>
-      <c r="F24" s="23" t="s">
-        <v>416</v>
-      </c>
+      <c r="F24" s="23"/>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2457,9 +2411,7 @@
         <v>103</v>
       </c>
       <c r="E25" s="15"/>
-      <c r="F25" s="23" t="s">
-        <v>420</v>
-      </c>
+      <c r="F25" s="23"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2476,9 +2428,7 @@
         <v>103</v>
       </c>
       <c r="E26" s="15"/>
-      <c r="F26" s="23" t="s">
-        <v>428</v>
-      </c>
+      <c r="F26" s="23"/>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2495,9 +2445,7 @@
         <v>103</v>
       </c>
       <c r="E27" s="15"/>
-      <c r="F27" s="23" t="s">
-        <v>475</v>
-      </c>
+      <c r="F27" s="23"/>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2514,9 +2462,7 @@
         <v>103</v>
       </c>
       <c r="E28" s="15"/>
-      <c r="F28" s="23" t="s">
-        <v>426</v>
-      </c>
+      <c r="F28" s="23"/>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2533,9 +2479,7 @@
         <v>103</v>
       </c>
       <c r="E29" s="15"/>
-      <c r="F29" s="23" t="s">
-        <v>474</v>
-      </c>
+      <c r="F29" s="23"/>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2552,9 +2496,7 @@
         <v>103</v>
       </c>
       <c r="E30" s="15"/>
-      <c r="F30" s="23" t="s">
-        <v>419</v>
-      </c>
+      <c r="F30" s="23"/>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2571,9 +2513,7 @@
         <v>103</v>
       </c>
       <c r="E31" s="15"/>
-      <c r="F31" s="23" t="s">
-        <v>467</v>
-      </c>
+      <c r="F31" s="23"/>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2590,9 +2530,7 @@
         <v>103</v>
       </c>
       <c r="E32" s="15"/>
-      <c r="F32" s="23" t="s">
-        <v>415</v>
-      </c>
+      <c r="F32" s="23"/>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2609,9 +2547,7 @@
         <v>103</v>
       </c>
       <c r="E33" s="15"/>
-      <c r="F33" s="23" t="s">
-        <v>423</v>
-      </c>
+      <c r="F33" s="23"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -2627,9 +2563,7 @@
         <v>103</v>
       </c>
       <c r="E34" s="15"/>
-      <c r="F34" s="23" t="s">
-        <v>268</v>
-      </c>
+      <c r="F34" s="23"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -2645,9 +2579,7 @@
         <v>103</v>
       </c>
       <c r="E35" s="15"/>
-      <c r="F35" s="23" t="s">
-        <v>246</v>
-      </c>
+      <c r="F35" s="23"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -2663,9 +2595,7 @@
         <v>103</v>
       </c>
       <c r="E36" s="15"/>
-      <c r="F36" s="23" t="s">
-        <v>252</v>
-      </c>
+      <c r="F36" s="23"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -2681,9 +2611,7 @@
         <v>103</v>
       </c>
       <c r="E37" s="15"/>
-      <c r="F37" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="F37" s="23"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -2699,9 +2627,7 @@
         <v>103</v>
       </c>
       <c r="E38" s="15"/>
-      <c r="F38" s="23" t="s">
-        <v>272</v>
-      </c>
+      <c r="F38" s="23"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
@@ -2717,9 +2643,7 @@
         <v>103</v>
       </c>
       <c r="E39" s="15"/>
-      <c r="F39" s="23" t="s">
-        <v>236</v>
-      </c>
+      <c r="F39" s="23"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
@@ -9167,14 +9091,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E462" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <conditionalFormatting sqref="E272">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I5 B1:B1048576 G1:G1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E272">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9146AD7C-435E-4D1A-A0A7-042512129806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF9219F-DC9F-4DB8-8E0D-014617CA1E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="481">
   <si>
     <t>STT</t>
   </si>
@@ -859,12 +859,6 @@
   </si>
   <si>
     <t>Khách đã lắp, lỗi không sáng đèn led, gửi lại X-Force bảo hành (02/07/2026)</t>
-  </si>
-  <si>
-    <t>Anh Thông đang giữ</t>
-  </si>
-  <si>
-    <t>Test trên web không thấy online</t>
   </si>
   <si>
     <t>VNET861385071448404</t>
@@ -4913,12 +4907,8 @@
       <c r="C181" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D181" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="E181" s="21" t="s">
-        <v>278</v>
-      </c>
+      <c r="D181" s="13"/>
+      <c r="E181" s="21"/>
       <c r="F181" s="20"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5063,7 +5053,7 @@
         <v>103</v>
       </c>
       <c r="E190" s="17" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F190" s="20"/>
     </row>
@@ -6224,10 +6214,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>103</v>
@@ -6240,12 +6230,14 @@
         <v>263</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D264" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D264" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E264" s="4"/>
       <c r="F264" s="4"/>
     </row>
@@ -6254,10 +6246,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -6268,12 +6260,14 @@
         <v>265</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D266" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D266" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E266" s="4"/>
       <c r="F266" s="4"/>
     </row>
@@ -6282,12 +6276,14 @@
         <v>266</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D267" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D267" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E267" s="4"/>
       <c r="F267" s="4"/>
     </row>
@@ -6296,10 +6292,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -6310,10 +6306,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>103</v>
@@ -6326,10 +6322,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
@@ -6340,10 +6336,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
@@ -6354,14 +6350,16 @@
         <v>271</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D272" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E272" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F272" s="4"/>
     </row>
@@ -6370,10 +6368,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
@@ -6384,10 +6382,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
@@ -6398,10 +6396,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
@@ -6412,10 +6410,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
@@ -6426,10 +6424,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>103</v>
@@ -6442,10 +6440,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
@@ -6456,10 +6454,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
@@ -6470,10 +6468,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
@@ -6484,10 +6482,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>103</v>
@@ -6500,10 +6498,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>103</v>
@@ -6516,10 +6514,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
@@ -6530,10 +6528,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
@@ -6544,10 +6542,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
@@ -6558,10 +6556,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
@@ -6572,10 +6570,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
@@ -6586,10 +6584,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
@@ -6600,10 +6598,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
@@ -6614,12 +6612,14 @@
         <v>289</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D290" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E290" s="4"/>
       <c r="F290" s="4"/>
     </row>
@@ -6628,10 +6628,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
@@ -6642,10 +6642,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
@@ -6656,10 +6656,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
@@ -6670,10 +6670,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
@@ -6684,12 +6684,14 @@
         <v>294</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D295" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E295" s="4"/>
       <c r="F295" s="4"/>
     </row>
@@ -6698,10 +6700,10 @@
         <v>295</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
@@ -6712,10 +6714,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
@@ -6726,12 +6728,14 @@
         <v>297</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D298" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D298" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E298" s="4"/>
       <c r="F298" s="4"/>
     </row>
@@ -6740,12 +6744,14 @@
         <v>298</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D299" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E299" s="4"/>
       <c r="F299" s="4"/>
     </row>
@@ -6754,10 +6760,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
@@ -6768,10 +6774,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
@@ -6782,12 +6788,14 @@
         <v>301</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D302" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E302" s="4"/>
       <c r="F302" s="4"/>
     </row>
@@ -6796,12 +6804,14 @@
         <v>302</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D303" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E303" s="4"/>
       <c r="F303" s="4"/>
     </row>
@@ -6810,12 +6820,14 @@
         <v>303</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D304" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E304" s="4"/>
       <c r="F304" s="4"/>
     </row>
@@ -6824,12 +6836,14 @@
         <v>304</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D305" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E305" s="4"/>
       <c r="F305" s="4"/>
     </row>
@@ -6838,12 +6852,14 @@
         <v>305</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D306" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E306" s="4"/>
       <c r="F306" s="4"/>
     </row>
@@ -6852,12 +6868,14 @@
         <v>306</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D307" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E307" s="4"/>
       <c r="F307" s="4"/>
     </row>
@@ -6866,10 +6884,10 @@
         <v>307</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
@@ -6880,12 +6898,14 @@
         <v>308</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D309" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E309" s="4"/>
       <c r="F309" s="4"/>
     </row>
@@ -6894,12 +6914,14 @@
         <v>309</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D310" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E310" s="4"/>
       <c r="F310" s="4"/>
     </row>
@@ -6908,12 +6930,14 @@
         <v>310</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D311" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E311" s="4"/>
       <c r="F311" s="4"/>
     </row>
@@ -6922,12 +6946,14 @@
         <v>311</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D312" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E312" s="4"/>
       <c r="F312" s="4"/>
     </row>
@@ -6936,10 +6962,10 @@
         <v>312</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
@@ -6950,12 +6976,14 @@
         <v>313</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D314" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E314" s="4"/>
       <c r="F314" s="4"/>
     </row>
@@ -6964,12 +6992,14 @@
         <v>314</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D315" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E315" s="4"/>
       <c r="F315" s="4"/>
     </row>
@@ -6978,10 +7008,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>103</v>
@@ -6994,12 +7024,14 @@
         <v>316</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D317" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E317" s="4"/>
       <c r="F317" s="4"/>
     </row>
@@ -7008,10 +7040,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
@@ -7022,12 +7054,14 @@
         <v>318</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D319" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E319" s="4"/>
       <c r="F319" s="4"/>
     </row>
@@ -7036,10 +7070,10 @@
         <v>319</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
@@ -7050,10 +7084,10 @@
         <v>320</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
@@ -7064,12 +7098,14 @@
         <v>321</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D322" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E322" s="4"/>
       <c r="F322" s="4"/>
     </row>
@@ -7078,12 +7114,14 @@
         <v>322</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D323" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E323" s="4"/>
       <c r="F323" s="4"/>
     </row>
@@ -7092,10 +7130,10 @@
         <v>323</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>103</v>
@@ -7108,12 +7146,14 @@
         <v>324</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D325" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D325" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E325" s="4"/>
       <c r="F325" s="4"/>
     </row>
@@ -7122,10 +7162,10 @@
         <v>325</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -7136,10 +7176,10 @@
         <v>326</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
@@ -7150,12 +7190,14 @@
         <v>327</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D328" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E328" s="4"/>
       <c r="F328" s="4"/>
     </row>
@@ -7164,10 +7206,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>103</v>
@@ -7180,10 +7222,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
@@ -7194,10 +7236,10 @@
         <v>330</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
@@ -7208,10 +7250,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
@@ -7222,10 +7264,10 @@
         <v>332</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>103</v>
@@ -7238,10 +7280,10 @@
         <v>333</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
@@ -7252,10 +7294,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -7266,10 +7308,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>103</v>
@@ -7282,10 +7324,10 @@
         <v>336</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>103</v>
@@ -7298,12 +7340,14 @@
         <v>337</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D338" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D338" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E338" s="4"/>
       <c r="F338" s="4"/>
     </row>
@@ -7312,12 +7356,14 @@
         <v>338</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D339" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E339" s="4"/>
       <c r="F339" s="4"/>
     </row>
@@ -7326,10 +7372,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>103</v>
@@ -7342,10 +7388,10 @@
         <v>340</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
@@ -7356,10 +7402,10 @@
         <v>341</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
@@ -7370,10 +7416,10 @@
         <v>342</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>103</v>
@@ -7386,10 +7432,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>103</v>
@@ -7402,10 +7448,10 @@
         <v>344</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>103</v>
@@ -7418,10 +7464,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>103</v>
@@ -7434,10 +7480,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
@@ -7448,12 +7494,14 @@
         <v>347</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D348" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D348" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E348" s="4"/>
       <c r="F348" s="4"/>
     </row>
@@ -7462,12 +7510,14 @@
         <v>348</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D349" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D349" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E349" s="4"/>
       <c r="F349" s="4"/>
     </row>
@@ -7476,12 +7526,14 @@
         <v>349</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D350" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E350" s="4"/>
       <c r="F350" s="4"/>
     </row>
@@ -7490,10 +7542,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
@@ -7504,10 +7556,10 @@
         <v>351</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
@@ -7518,12 +7570,14 @@
         <v>352</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D353" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E353" s="4"/>
       <c r="F353" s="4"/>
     </row>
@@ -7532,12 +7586,14 @@
         <v>353</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D354" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E354" s="4"/>
       <c r="F354" s="4"/>
     </row>
@@ -7546,12 +7602,14 @@
         <v>354</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D355" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D355" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E355" s="4"/>
       <c r="F355" s="4"/>
     </row>
@@ -7560,12 +7618,14 @@
         <v>355</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D356" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D356" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E356" s="4"/>
       <c r="F356" s="4"/>
     </row>
@@ -7574,12 +7634,14 @@
         <v>356</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D357" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D357" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E357" s="4"/>
       <c r="F357" s="4"/>
     </row>
@@ -7588,12 +7650,14 @@
         <v>357</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D358" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D358" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E358" s="4"/>
       <c r="F358" s="4"/>
     </row>
@@ -7602,12 +7666,14 @@
         <v>358</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D359" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D359" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E359" s="4"/>
       <c r="F359" s="4"/>
     </row>
@@ -7616,12 +7682,14 @@
         <v>359</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D360" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D360" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E360" s="4"/>
       <c r="F360" s="4"/>
     </row>
@@ -7630,12 +7698,14 @@
         <v>360</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D361" s="4"/>
+        <v>477</v>
+      </c>
+      <c r="D361" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E361" s="4"/>
       <c r="F361" s="4"/>
     </row>
@@ -7644,10 +7714,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>103</v>
@@ -7660,10 +7730,10 @@
         <v>362</v>
       </c>
       <c r="B363" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
@@ -7674,10 +7744,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
@@ -7688,10 +7758,10 @@
         <v>364</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>103</v>
@@ -7704,10 +7774,10 @@
         <v>365</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
@@ -7718,10 +7788,10 @@
         <v>366</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
@@ -7732,10 +7802,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
@@ -7746,10 +7816,10 @@
         <v>368</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
@@ -7760,10 +7830,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
@@ -7774,10 +7844,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
@@ -7788,10 +7858,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
@@ -7802,10 +7872,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
@@ -7816,10 +7886,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
@@ -7830,10 +7900,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
@@ -7844,10 +7914,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
@@ -7858,10 +7928,10 @@
         <v>376</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -7872,10 +7942,10 @@
         <v>377</v>
       </c>
       <c r="B378" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
@@ -7886,10 +7956,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
@@ -7900,10 +7970,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
@@ -7914,10 +7984,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
@@ -7928,10 +7998,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
@@ -7942,10 +8012,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
@@ -7956,10 +8026,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
@@ -7970,10 +8040,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
@@ -7984,10 +8054,10 @@
         <v>385</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
@@ -7998,10 +8068,10 @@
         <v>386</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
@@ -8012,10 +8082,10 @@
         <v>387</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
@@ -8026,10 +8096,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
@@ -8040,10 +8110,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
@@ -8054,10 +8124,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
@@ -8068,10 +8138,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -8082,10 +8152,10 @@
         <v>392</v>
       </c>
       <c r="B393" s="6" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>103</v>
@@ -8098,10 +8168,10 @@
         <v>393</v>
       </c>
       <c r="B394" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -8112,10 +8182,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -8126,10 +8196,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -8140,10 +8210,10 @@
         <v>396</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -8154,10 +8224,10 @@
         <v>397</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -8168,10 +8238,10 @@
         <v>398</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>103</v>
@@ -8184,10 +8254,10 @@
         <v>399</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>103</v>
@@ -8200,10 +8270,10 @@
         <v>400</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
@@ -8214,10 +8284,10 @@
         <v>401</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
@@ -8228,10 +8298,10 @@
         <v>402</v>
       </c>
       <c r="B403" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>103</v>
@@ -8244,10 +8314,10 @@
         <v>403</v>
       </c>
       <c r="B404" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>103</v>
@@ -8260,15 +8330,13 @@
         <v>404</v>
       </c>
       <c r="B405" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D405" s="4"/>
-      <c r="E405" s="21" t="s">
-        <v>278</v>
-      </c>
+      <c r="E405" s="21"/>
       <c r="F405" s="4"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -8276,10 +8344,10 @@
         <v>405</v>
       </c>
       <c r="B406" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
@@ -8290,10 +8358,10 @@
         <v>406</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>103</v>
@@ -8306,10 +8374,10 @@
         <v>407</v>
       </c>
       <c r="B408" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
@@ -8320,10 +8388,10 @@
         <v>408</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
@@ -8334,10 +8402,10 @@
         <v>409</v>
       </c>
       <c r="B410" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>103</v>
@@ -8350,10 +8418,10 @@
         <v>410</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
@@ -8364,10 +8432,10 @@
         <v>411</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>103</v>
@@ -8380,10 +8448,10 @@
         <v>412</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
@@ -8394,10 +8462,10 @@
         <v>413</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>103</v>
@@ -8410,10 +8478,10 @@
         <v>414</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
@@ -8424,10 +8492,10 @@
         <v>415</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
@@ -8438,10 +8506,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
@@ -8452,10 +8520,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
@@ -8466,10 +8534,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
@@ -8480,10 +8548,10 @@
         <v>419</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
@@ -8494,10 +8562,10 @@
         <v>420</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
@@ -8508,10 +8576,10 @@
         <v>421</v>
       </c>
       <c r="B422" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
@@ -8522,10 +8590,10 @@
         <v>422</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
@@ -8536,10 +8604,10 @@
         <v>423</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -8550,10 +8618,10 @@
         <v>424</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
@@ -8564,10 +8632,10 @@
         <v>425</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
@@ -8578,10 +8646,10 @@
         <v>426</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
@@ -8592,10 +8660,10 @@
         <v>427</v>
       </c>
       <c r="B428" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
@@ -8606,10 +8674,10 @@
         <v>428</v>
       </c>
       <c r="B429" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
@@ -8620,10 +8688,10 @@
         <v>429</v>
       </c>
       <c r="B430" s="6" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>103</v>
@@ -8636,10 +8704,10 @@
         <v>430</v>
       </c>
       <c r="B431" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -8650,10 +8718,10 @@
         <v>431</v>
       </c>
       <c r="B432" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -8664,10 +8732,10 @@
         <v>432</v>
       </c>
       <c r="B433" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -8678,10 +8746,10 @@
         <v>433</v>
       </c>
       <c r="B434" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
@@ -8692,10 +8760,10 @@
         <v>434</v>
       </c>
       <c r="B435" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -8706,10 +8774,10 @@
         <v>435</v>
       </c>
       <c r="B436" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -8720,10 +8788,10 @@
         <v>436</v>
       </c>
       <c r="B437" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -8734,10 +8802,10 @@
         <v>437</v>
       </c>
       <c r="B438" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
@@ -8748,10 +8816,10 @@
         <v>438</v>
       </c>
       <c r="B439" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
@@ -8762,10 +8830,10 @@
         <v>439</v>
       </c>
       <c r="B440" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
@@ -8776,10 +8844,10 @@
         <v>440</v>
       </c>
       <c r="B441" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
@@ -8790,10 +8858,10 @@
         <v>441</v>
       </c>
       <c r="B442" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
@@ -8804,10 +8872,10 @@
         <v>442</v>
       </c>
       <c r="B443" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
@@ -8818,10 +8886,10 @@
         <v>443</v>
       </c>
       <c r="B444" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
@@ -8832,10 +8900,10 @@
         <v>444</v>
       </c>
       <c r="B445" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
@@ -8846,10 +8914,10 @@
         <v>445</v>
       </c>
       <c r="B446" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
@@ -8860,10 +8928,10 @@
         <v>446</v>
       </c>
       <c r="B447" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
@@ -8874,10 +8942,10 @@
         <v>447</v>
       </c>
       <c r="B448" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
@@ -8888,10 +8956,10 @@
         <v>448</v>
       </c>
       <c r="B449" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
@@ -8902,10 +8970,10 @@
         <v>449</v>
       </c>
       <c r="B450" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
@@ -8916,10 +8984,10 @@
         <v>450</v>
       </c>
       <c r="B451" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>103</v>
@@ -8932,10 +9000,10 @@
         <v>451</v>
       </c>
       <c r="B452" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
@@ -8946,10 +9014,10 @@
         <v>452</v>
       </c>
       <c r="B453" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
@@ -8960,10 +9028,10 @@
         <v>453</v>
       </c>
       <c r="B454" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C454" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
@@ -8974,10 +9042,10 @@
         <v>454</v>
       </c>
       <c r="B455" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
@@ -8988,10 +9056,10 @@
         <v>455</v>
       </c>
       <c r="B456" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C456" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
@@ -9002,10 +9070,10 @@
         <v>456</v>
       </c>
       <c r="B457" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>103</v>
@@ -9018,10 +9086,10 @@
         <v>457</v>
       </c>
       <c r="B458" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C458" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>103</v>
@@ -9034,10 +9102,10 @@
         <v>458</v>
       </c>
       <c r="B459" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C459" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>103</v>
@@ -9050,10 +9118,10 @@
         <v>459</v>
       </c>
       <c r="B460" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
@@ -9064,10 +9132,10 @@
         <v>460</v>
       </c>
       <c r="B461" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
@@ -9078,13 +9146,13 @@
         <v>461</v>
       </c>
       <c r="B462" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="C462" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="D462" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="C462" s="6" t="s">
-        <v>479</v>
-      </c>
-      <c r="D462" s="4" t="s">
-        <v>480</v>
       </c>
       <c r="E462" s="4"/>
       <c r="F462" s="4"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF9219F-DC9F-4DB8-8E0D-014617CA1E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD74E50A-198A-44C0-AC8A-D711027DF64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD74E50A-198A-44C0-AC8A-D711027DF64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E18171C-B527-4369-BFB8-CD38C4D950FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="482">
   <si>
     <t>STT</t>
   </si>
@@ -1471,6 +1471,9 @@
   </si>
   <si>
     <t>Không chốt GPS, IPEX bị lỏng</t>
+  </si>
+  <si>
+    <t>Gửi Thịnh Aithings kiểm tra</t>
   </si>
 </sst>
 </file>
@@ -5055,7 +5058,9 @@
       <c r="E190" s="17" t="s">
         <v>479</v>
       </c>
-      <c r="F190" s="20"/>
+      <c r="F190" s="20" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="4">

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E18171C-B527-4369-BFB8-CD38C4D950FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752E2119-950B-44EE-864F-8A9019DE8BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1265" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="494">
   <si>
     <t>STT</t>
   </si>
@@ -855,9 +855,6 @@
     <t>02/07/2026</t>
   </si>
   <si>
-    <t>Gửi lại X-Force bảo hành (02/07/2026)</t>
-  </si>
-  <si>
     <t>Khách đã lắp, lỗi không sáng đèn led, gửi lại X-Force bảo hành (02/07/2026)</t>
   </si>
   <si>
@@ -1474,6 +1471,45 @@
   </si>
   <si>
     <t>Gửi Thịnh Aithings kiểm tra</t>
+  </si>
+  <si>
+    <t>VNET861385070647477</t>
+  </si>
+  <si>
+    <t>VNET861385071455128</t>
+  </si>
+  <si>
+    <t>VNET861385070686830</t>
+  </si>
+  <si>
+    <t>VNET861385070649788</t>
+  </si>
+  <si>
+    <t>VNET861385070647907</t>
+  </si>
+  <si>
+    <t>VNET861385071447141</t>
+  </si>
+  <si>
+    <t>VNET861385071476314</t>
+  </si>
+  <si>
+    <t>VNET861385070686905</t>
+  </si>
+  <si>
+    <t>VNET861385071482486</t>
+  </si>
+  <si>
+    <t>22/07/2026</t>
+  </si>
+  <si>
+    <t>Nhận từ Aithings</t>
+  </si>
+  <si>
+    <t>Gửi lại X-Force bảo hành (02/07/2026), đã nhận lại ngày 22/07/2026</t>
+  </si>
+  <si>
+    <t>Thiết bị đã đổi BH 1 lần nhận lại lỗi quạt gió, có phản hồi từ HTKT đèn trạng thái thiết bị không khởi động được</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1626,6 +1662,12 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1972,7 +2014,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}">
-  <dimension ref="A1:G462"/>
+  <dimension ref="A1:G471"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="11" customWidth="1"/>
@@ -2219,7 +2261,7 @@
         <v>103</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F14" s="22"/>
       <c r="G14" s="9"/>
@@ -4018,7 +4060,7 @@
       <c r="E125" s="15"/>
       <c r="F125" s="20"/>
     </row>
-    <row r="126" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>125</v>
       </c>
@@ -4032,7 +4074,7 @@
         <v>185</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>275</v>
+        <v>492</v>
       </c>
       <c r="F126" s="20"/>
     </row>
@@ -5056,10 +5098,10 @@
         <v>103</v>
       </c>
       <c r="E190" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F190" s="20" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6166,7 +6208,7 @@
       <c r="E259" s="15"/>
       <c r="F259" s="20"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -6179,7 +6221,9 @@
       <c r="D260" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E260" s="15"/>
+      <c r="E260" s="17" t="s">
+        <v>493</v>
+      </c>
       <c r="F260" s="20"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -6219,10 +6263,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>103</v>
@@ -6235,10 +6279,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>103</v>
@@ -6251,10 +6295,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -6265,10 +6309,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>103</v>
@@ -6281,10 +6325,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>103</v>
@@ -6297,10 +6341,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -6311,10 +6355,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>103</v>
@@ -6327,10 +6371,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
@@ -6341,10 +6385,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
@@ -6355,16 +6399,16 @@
         <v>271</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>103</v>
       </c>
       <c r="E272" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F272" s="4"/>
     </row>
@@ -6373,10 +6417,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
@@ -6387,10 +6431,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
@@ -6401,10 +6445,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
@@ -6415,10 +6459,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
@@ -6429,10 +6473,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>103</v>
@@ -6445,10 +6489,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
@@ -6459,10 +6503,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
@@ -6473,10 +6517,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
@@ -6487,10 +6531,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>103</v>
@@ -6503,10 +6547,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>103</v>
@@ -6519,10 +6563,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
@@ -6533,10 +6577,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
@@ -6547,10 +6591,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
@@ -6561,10 +6605,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
@@ -6575,10 +6619,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
@@ -6589,10 +6633,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
@@ -6603,10 +6647,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
@@ -6617,10 +6661,10 @@
         <v>289</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>103</v>
@@ -6633,10 +6677,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
@@ -6647,10 +6691,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
@@ -6661,10 +6705,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
@@ -6675,10 +6719,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
@@ -6689,10 +6733,10 @@
         <v>294</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>103</v>
@@ -6705,10 +6749,10 @@
         <v>295</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
@@ -6719,10 +6763,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
@@ -6733,10 +6777,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>103</v>
@@ -6749,10 +6793,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>103</v>
@@ -6765,10 +6809,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
@@ -6779,10 +6823,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
@@ -6793,10 +6837,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>103</v>
@@ -6809,10 +6853,10 @@
         <v>302</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>103</v>
@@ -6825,10 +6869,10 @@
         <v>303</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>103</v>
@@ -6841,10 +6885,10 @@
         <v>304</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>103</v>
@@ -6857,10 +6901,10 @@
         <v>305</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>103</v>
@@ -6873,10 +6917,10 @@
         <v>306</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>103</v>
@@ -6889,10 +6933,10 @@
         <v>307</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
@@ -6903,10 +6947,10 @@
         <v>308</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>103</v>
@@ -6919,10 +6963,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>103</v>
@@ -6935,10 +6979,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>103</v>
@@ -6951,10 +6995,10 @@
         <v>311</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>103</v>
@@ -6967,10 +7011,10 @@
         <v>312</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
@@ -6981,10 +7025,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>103</v>
@@ -6997,10 +7041,10 @@
         <v>314</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>103</v>
@@ -7013,10 +7057,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>103</v>
@@ -7029,10 +7073,10 @@
         <v>316</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>103</v>
@@ -7045,10 +7089,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
@@ -7059,10 +7103,10 @@
         <v>318</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>103</v>
@@ -7075,10 +7119,10 @@
         <v>319</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
@@ -7089,10 +7133,10 @@
         <v>320</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
@@ -7103,10 +7147,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>103</v>
@@ -7119,10 +7163,10 @@
         <v>322</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>103</v>
@@ -7135,10 +7179,10 @@
         <v>323</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>103</v>
@@ -7151,10 +7195,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>103</v>
@@ -7167,10 +7211,10 @@
         <v>325</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -7181,10 +7225,10 @@
         <v>326</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
@@ -7195,10 +7239,10 @@
         <v>327</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>103</v>
@@ -7211,10 +7255,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>103</v>
@@ -7227,10 +7271,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
@@ -7241,10 +7285,10 @@
         <v>330</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
@@ -7255,10 +7299,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
@@ -7269,10 +7313,10 @@
         <v>332</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>103</v>
@@ -7285,10 +7329,10 @@
         <v>333</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
@@ -7299,10 +7343,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -7313,10 +7357,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>103</v>
@@ -7329,10 +7373,10 @@
         <v>336</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>103</v>
@@ -7345,10 +7389,10 @@
         <v>337</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>103</v>
@@ -7361,10 +7405,10 @@
         <v>338</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>103</v>
@@ -7377,10 +7421,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>103</v>
@@ -7393,10 +7437,10 @@
         <v>340</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
@@ -7407,10 +7451,10 @@
         <v>341</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
@@ -7421,10 +7465,10 @@
         <v>342</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>103</v>
@@ -7437,10 +7481,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>103</v>
@@ -7453,10 +7497,10 @@
         <v>344</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>103</v>
@@ -7469,10 +7513,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>103</v>
@@ -7485,10 +7529,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
@@ -7499,10 +7543,10 @@
         <v>347</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>103</v>
@@ -7515,10 +7559,10 @@
         <v>348</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>103</v>
@@ -7531,10 +7575,10 @@
         <v>349</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>103</v>
@@ -7547,10 +7591,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
@@ -7561,10 +7605,10 @@
         <v>351</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
@@ -7575,10 +7619,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>103</v>
@@ -7591,10 +7635,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>103</v>
@@ -7607,10 +7651,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>103</v>
@@ -7623,10 +7667,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>103</v>
@@ -7639,10 +7683,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>103</v>
@@ -7655,10 +7699,10 @@
         <v>357</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>103</v>
@@ -7671,10 +7715,10 @@
         <v>358</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>103</v>
@@ -7687,10 +7731,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>103</v>
@@ -7703,10 +7747,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>103</v>
@@ -7719,10 +7763,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>103</v>
@@ -7735,10 +7779,10 @@
         <v>362</v>
       </c>
       <c r="B363" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
@@ -7749,10 +7793,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
@@ -7763,10 +7807,10 @@
         <v>364</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>103</v>
@@ -7779,10 +7823,10 @@
         <v>365</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
@@ -7793,10 +7837,10 @@
         <v>366</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
@@ -7807,10 +7851,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
@@ -7821,10 +7865,10 @@
         <v>368</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
@@ -7835,10 +7879,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
@@ -7849,10 +7893,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
@@ -7863,10 +7907,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
@@ -7877,10 +7921,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
@@ -7891,10 +7935,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
@@ -7905,10 +7949,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
@@ -7919,10 +7963,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
@@ -7933,10 +7977,10 @@
         <v>376</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -7947,10 +7991,10 @@
         <v>377</v>
       </c>
       <c r="B378" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
@@ -7961,10 +8005,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
@@ -7975,10 +8019,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
@@ -7989,10 +8033,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
@@ -8003,10 +8047,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
@@ -8017,10 +8061,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
@@ -8031,10 +8075,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
@@ -8045,10 +8089,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
@@ -8059,10 +8103,10 @@
         <v>385</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
@@ -8073,10 +8117,10 @@
         <v>386</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
@@ -8087,10 +8131,10 @@
         <v>387</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
@@ -8101,10 +8145,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
@@ -8115,10 +8159,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
@@ -8129,10 +8173,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
@@ -8143,10 +8187,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -8157,10 +8201,10 @@
         <v>392</v>
       </c>
       <c r="B393" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>103</v>
@@ -8173,10 +8217,10 @@
         <v>393</v>
       </c>
       <c r="B394" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -8187,10 +8231,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -8201,10 +8245,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -8215,10 +8259,10 @@
         <v>396</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -8229,10 +8273,10 @@
         <v>397</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -8243,10 +8287,10 @@
         <v>398</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>103</v>
@@ -8259,10 +8303,10 @@
         <v>399</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>103</v>
@@ -8275,10 +8319,10 @@
         <v>400</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
@@ -8289,10 +8333,10 @@
         <v>401</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
@@ -8303,10 +8347,10 @@
         <v>402</v>
       </c>
       <c r="B403" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>103</v>
@@ -8319,10 +8363,10 @@
         <v>403</v>
       </c>
       <c r="B404" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>103</v>
@@ -8335,10 +8379,10 @@
         <v>404</v>
       </c>
       <c r="B405" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D405" s="4"/>
       <c r="E405" s="21"/>
@@ -8349,10 +8393,10 @@
         <v>405</v>
       </c>
       <c r="B406" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
@@ -8363,10 +8407,10 @@
         <v>406</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>103</v>
@@ -8379,10 +8423,10 @@
         <v>407</v>
       </c>
       <c r="B408" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
@@ -8393,10 +8437,10 @@
         <v>408</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
@@ -8407,10 +8451,10 @@
         <v>409</v>
       </c>
       <c r="B410" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>103</v>
@@ -8423,10 +8467,10 @@
         <v>410</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
@@ -8437,10 +8481,10 @@
         <v>411</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>103</v>
@@ -8453,10 +8497,10 @@
         <v>412</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
@@ -8467,10 +8511,10 @@
         <v>413</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>103</v>
@@ -8483,10 +8527,10 @@
         <v>414</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
@@ -8497,10 +8541,10 @@
         <v>415</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
@@ -8511,10 +8555,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
@@ -8525,10 +8569,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
@@ -8539,10 +8583,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
@@ -8553,10 +8597,10 @@
         <v>419</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
@@ -8567,10 +8611,10 @@
         <v>420</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
@@ -8581,10 +8625,10 @@
         <v>421</v>
       </c>
       <c r="B422" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
@@ -8595,10 +8639,10 @@
         <v>422</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
@@ -8609,10 +8653,10 @@
         <v>423</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -8623,10 +8667,10 @@
         <v>424</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
@@ -8637,10 +8681,10 @@
         <v>425</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
@@ -8651,10 +8695,10 @@
         <v>426</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
@@ -8665,10 +8709,10 @@
         <v>427</v>
       </c>
       <c r="B428" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
@@ -8679,10 +8723,10 @@
         <v>428</v>
       </c>
       <c r="B429" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
@@ -8693,10 +8737,10 @@
         <v>429</v>
       </c>
       <c r="B430" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>103</v>
@@ -8709,10 +8753,10 @@
         <v>430</v>
       </c>
       <c r="B431" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -8723,10 +8767,10 @@
         <v>431</v>
       </c>
       <c r="B432" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -8737,10 +8781,10 @@
         <v>432</v>
       </c>
       <c r="B433" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -8751,10 +8795,10 @@
         <v>433</v>
       </c>
       <c r="B434" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
@@ -8765,10 +8809,10 @@
         <v>434</v>
       </c>
       <c r="B435" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -8779,10 +8823,10 @@
         <v>435</v>
       </c>
       <c r="B436" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -8793,10 +8837,10 @@
         <v>436</v>
       </c>
       <c r="B437" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -8807,10 +8851,10 @@
         <v>437</v>
       </c>
       <c r="B438" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
@@ -8821,10 +8865,10 @@
         <v>438</v>
       </c>
       <c r="B439" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
@@ -8835,10 +8879,10 @@
         <v>439</v>
       </c>
       <c r="B440" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
@@ -8849,10 +8893,10 @@
         <v>440</v>
       </c>
       <c r="B441" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
@@ -8863,10 +8907,10 @@
         <v>441</v>
       </c>
       <c r="B442" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
@@ -8877,10 +8921,10 @@
         <v>442</v>
       </c>
       <c r="B443" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
@@ -8891,10 +8935,10 @@
         <v>443</v>
       </c>
       <c r="B444" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
@@ -8905,10 +8949,10 @@
         <v>444</v>
       </c>
       <c r="B445" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
@@ -8919,10 +8963,10 @@
         <v>445</v>
       </c>
       <c r="B446" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
@@ -8933,10 +8977,10 @@
         <v>446</v>
       </c>
       <c r="B447" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
@@ -8947,10 +8991,10 @@
         <v>447</v>
       </c>
       <c r="B448" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
@@ -8961,10 +9005,10 @@
         <v>448</v>
       </c>
       <c r="B449" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
@@ -8975,10 +9019,10 @@
         <v>449</v>
       </c>
       <c r="B450" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
@@ -8989,10 +9033,10 @@
         <v>450</v>
       </c>
       <c r="B451" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>103</v>
@@ -9005,10 +9049,10 @@
         <v>451</v>
       </c>
       <c r="B452" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
@@ -9019,10 +9063,10 @@
         <v>452</v>
       </c>
       <c r="B453" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
@@ -9033,10 +9077,10 @@
         <v>453</v>
       </c>
       <c r="B454" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C454" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
@@ -9047,10 +9091,10 @@
         <v>454</v>
       </c>
       <c r="B455" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
@@ -9061,10 +9105,10 @@
         <v>455</v>
       </c>
       <c r="B456" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C456" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
@@ -9075,10 +9119,10 @@
         <v>456</v>
       </c>
       <c r="B457" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>103</v>
@@ -9091,10 +9135,10 @@
         <v>457</v>
       </c>
       <c r="B458" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C458" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>103</v>
@@ -9107,10 +9151,10 @@
         <v>458</v>
       </c>
       <c r="B459" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C459" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>103</v>
@@ -9123,10 +9167,10 @@
         <v>459</v>
       </c>
       <c r="B460" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
@@ -9137,10 +9181,10 @@
         <v>460</v>
       </c>
       <c r="B461" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
@@ -9151,16 +9195,160 @@
         <v>461</v>
       </c>
       <c r="B462" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C462" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="D462" s="4" t="s">
         <v>477</v>
-      </c>
-      <c r="D462" s="4" t="s">
-        <v>478</v>
       </c>
       <c r="E462" s="4"/>
       <c r="F462" s="4"/>
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A463" s="4">
+        <v>462</v>
+      </c>
+      <c r="B463" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="C463" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D463" s="25"/>
+      <c r="E463" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F463" s="20"/>
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A464" s="4">
+        <v>463</v>
+      </c>
+      <c r="B464" s="24" t="s">
+        <v>482</v>
+      </c>
+      <c r="C464" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D464" s="25"/>
+      <c r="E464" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F464" s="20"/>
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A465" s="4">
+        <v>464</v>
+      </c>
+      <c r="B465" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="C465" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D465" s="25"/>
+      <c r="E465" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F465" s="20"/>
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A466" s="4">
+        <v>465</v>
+      </c>
+      <c r="B466" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="C466" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D466" s="25"/>
+      <c r="E466" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F466" s="20"/>
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A467" s="4">
+        <v>466</v>
+      </c>
+      <c r="B467" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="C467" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D467" s="25"/>
+      <c r="E467" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F467" s="20"/>
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A468" s="4">
+        <v>467</v>
+      </c>
+      <c r="B468" s="24" t="s">
+        <v>486</v>
+      </c>
+      <c r="C468" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D468" s="25"/>
+      <c r="E468" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F468" s="20"/>
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A469" s="4">
+        <v>468</v>
+      </c>
+      <c r="B469" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="C469" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D469" s="25"/>
+      <c r="E469" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F469" s="20"/>
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A470" s="4">
+        <v>469</v>
+      </c>
+      <c r="B470" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="C470" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D470" s="25"/>
+      <c r="E470" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F470" s="20"/>
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A471" s="4">
+        <v>470</v>
+      </c>
+      <c r="B471" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="C471" s="24" t="s">
+        <v>490</v>
+      </c>
+      <c r="D471" s="25"/>
+      <c r="E471" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="F471" s="20"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E462" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752E2119-950B-44EE-864F-8A9019DE8BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A39776C-2909-4BFE-9855-7B7F2758D221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -1464,9 +1464,6 @@
     <t>ID sai</t>
   </si>
   <si>
-    <t>Victory trả về, lỗi không LED trạng thái</t>
-  </si>
-  <si>
     <t>Không chốt GPS, IPEX bị lỏng</t>
   </si>
   <si>
@@ -1510,6 +1507,9 @@
   </si>
   <si>
     <t>Thiết bị đã đổi BH 1 lần nhận lại lỗi quạt gió, có phản hồi từ HTKT đèn trạng thái thiết bị không khởi động được</t>
+  </si>
+  <si>
+    <t>Victory trả về, lỗi không LED trạng thái, gửi Thịnh Aithings xử lý 21/07/2026</t>
   </si>
 </sst>
 </file>
@@ -1602,7 +1602,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1668,6 +1668,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4074,7 +4077,7 @@
         <v>185</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F126" s="20"/>
     </row>
@@ -5084,7 +5087,7 @@
       <c r="E189" s="15"/>
       <c r="F189" s="20"/>
     </row>
-    <row r="190" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>189</v>
       </c>
@@ -5098,10 +5101,10 @@
         <v>103</v>
       </c>
       <c r="E190" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="F190" s="20" t="s">
-        <v>480</v>
+        <v>493</v>
+      </c>
+      <c r="F190" s="26" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6222,7 +6225,7 @@
         <v>103</v>
       </c>
       <c r="E260" s="17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F260" s="20"/>
     </row>
@@ -6408,7 +6411,7 @@
         <v>103</v>
       </c>
       <c r="E272" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F272" s="4"/>
     </row>
@@ -9211,14 +9214,14 @@
         <v>462</v>
       </c>
       <c r="B463" s="24" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C463" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D463" s="25"/>
       <c r="E463" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F463" s="20"/>
     </row>
@@ -9227,14 +9230,14 @@
         <v>463</v>
       </c>
       <c r="B464" s="24" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C464" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D464" s="25"/>
       <c r="E464" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F464" s="20"/>
     </row>
@@ -9243,14 +9246,14 @@
         <v>464</v>
       </c>
       <c r="B465" s="24" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C465" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D465" s="25"/>
       <c r="E465" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F465" s="20"/>
     </row>
@@ -9259,14 +9262,14 @@
         <v>465</v>
       </c>
       <c r="B466" s="24" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C466" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D466" s="25"/>
       <c r="E466" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F466" s="20"/>
     </row>
@@ -9275,14 +9278,14 @@
         <v>466</v>
       </c>
       <c r="B467" s="24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C467" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D467" s="25"/>
       <c r="E467" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F467" s="20"/>
     </row>
@@ -9291,14 +9294,14 @@
         <v>467</v>
       </c>
       <c r="B468" s="24" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C468" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D468" s="25"/>
       <c r="E468" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F468" s="20"/>
     </row>
@@ -9307,14 +9310,14 @@
         <v>468</v>
       </c>
       <c r="B469" s="24" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C469" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D469" s="25"/>
       <c r="E469" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F469" s="20"/>
     </row>
@@ -9323,14 +9326,14 @@
         <v>469</v>
       </c>
       <c r="B470" s="24" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C470" s="24" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D470" s="25"/>
       <c r="E470" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F470" s="20"/>
     </row>
@@ -9339,14 +9342,14 @@
         <v>470</v>
       </c>
       <c r="B471" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="C471" s="24" t="s">
         <v>489</v>
-      </c>
-      <c r="C471" s="24" t="s">
-        <v>490</v>
       </c>
       <c r="D471" s="25"/>
       <c r="E471" s="15" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F471" s="20"/>
     </row>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A39776C-2909-4BFE-9855-7B7F2758D221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99BFC66-C8AB-49E9-A8B1-15B89E41007E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="ID_VNSH03" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$E$462</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID_VNSH03!$A$1:$E$471</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -9354,7 +9354,7 @@
       <c r="F471" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E462" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
+  <autoFilter ref="A1:E471" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
   <conditionalFormatting sqref="E272">
     <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99BFC66-C8AB-49E9-A8B1-15B89E41007E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F67DF0D-9B2C-454D-A142-177B8CF79C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F67DF0D-9B2C-454D-A142-177B8CF79C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96A7EFA-AF59-4941-88B5-43CC2B3D0100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96A7EFA-AF59-4941-88B5-43CC2B3D0100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB4EDE4-1387-40D9-8C6B-D7E01A219D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
+    <workbookView minimized="1" xWindow="8085" yWindow="2145" windowWidth="21600" windowHeight="11835" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
   <sheets>
     <sheet name="ID_VNSH03" sheetId="1" r:id="rId1"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB4EDE4-1387-40D9-8C6B-D7E01A219D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F66DBB-F9EC-4905-B3D1-E01368E33A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="8085" yWindow="2145" windowWidth="21600" windowHeight="11835" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
   <sheets>
     <sheet name="ID_VNSH03" sheetId="1" r:id="rId1"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F66DBB-F9EC-4905-B3D1-E01368E33A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D806EED4-0450-4ECF-8D75-B1C263C3AD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -1455,9 +1455,6 @@
     <t>VNET861385071517216</t>
   </si>
   <si>
-    <t>VNET86138507145805</t>
-  </si>
-  <si>
     <t>06/07/2026</t>
   </si>
   <si>
@@ -1510,6 +1507,9 @@
   </si>
   <si>
     <t>Victory trả về, lỗi không LED trạng thái, gửi Thịnh Aithings xử lý 21/07/2026</t>
+  </si>
+  <si>
+    <t>VNET861385071455805</t>
   </si>
 </sst>
 </file>
@@ -4077,7 +4077,7 @@
         <v>185</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F126" s="20"/>
     </row>
@@ -5101,10 +5101,10 @@
         <v>103</v>
       </c>
       <c r="E190" s="17" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="F190" s="26" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6225,7 +6225,7 @@
         <v>103</v>
       </c>
       <c r="E260" s="17" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F260" s="20"/>
     </row>
@@ -6269,7 +6269,7 @@
         <v>276</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>103</v>
@@ -6285,7 +6285,7 @@
         <v>277</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>103</v>
@@ -6301,7 +6301,7 @@
         <v>278</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -6315,7 +6315,7 @@
         <v>279</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>103</v>
@@ -6331,7 +6331,7 @@
         <v>280</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>103</v>
@@ -6347,7 +6347,7 @@
         <v>281</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -6361,7 +6361,7 @@
         <v>282</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>103</v>
@@ -6377,7 +6377,7 @@
         <v>283</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
@@ -6391,7 +6391,7 @@
         <v>284</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
@@ -6405,13 +6405,13 @@
         <v>285</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D272" s="4" t="s">
         <v>103</v>
       </c>
       <c r="E272" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F272" s="4"/>
     </row>
@@ -6423,7 +6423,7 @@
         <v>286</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
@@ -6437,7 +6437,7 @@
         <v>287</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
@@ -6451,7 +6451,7 @@
         <v>288</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
@@ -6465,7 +6465,7 @@
         <v>289</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
@@ -6479,7 +6479,7 @@
         <v>290</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>103</v>
@@ -6495,7 +6495,7 @@
         <v>291</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
@@ -6509,7 +6509,7 @@
         <v>292</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
@@ -6523,7 +6523,7 @@
         <v>293</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
@@ -6537,7 +6537,7 @@
         <v>294</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>103</v>
@@ -6553,7 +6553,7 @@
         <v>295</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>103</v>
@@ -6569,7 +6569,7 @@
         <v>296</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
@@ -6583,7 +6583,7 @@
         <v>297</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
@@ -6597,7 +6597,7 @@
         <v>298</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
@@ -6611,7 +6611,7 @@
         <v>299</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
@@ -6625,7 +6625,7 @@
         <v>300</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
@@ -6639,7 +6639,7 @@
         <v>301</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
@@ -6653,7 +6653,7 @@
         <v>302</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
@@ -6667,7 +6667,7 @@
         <v>303</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>103</v>
@@ -6683,7 +6683,7 @@
         <v>304</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
@@ -6697,7 +6697,7 @@
         <v>305</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
@@ -6711,7 +6711,7 @@
         <v>306</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
@@ -6725,7 +6725,7 @@
         <v>307</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
@@ -6739,7 +6739,7 @@
         <v>308</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>103</v>
@@ -6755,7 +6755,7 @@
         <v>309</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
@@ -6769,7 +6769,7 @@
         <v>310</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
@@ -6783,7 +6783,7 @@
         <v>311</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>103</v>
@@ -6799,7 +6799,7 @@
         <v>312</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>103</v>
@@ -6815,7 +6815,7 @@
         <v>313</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
@@ -6829,7 +6829,7 @@
         <v>314</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
@@ -6843,7 +6843,7 @@
         <v>315</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>103</v>
@@ -6859,7 +6859,7 @@
         <v>316</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>103</v>
@@ -6875,7 +6875,7 @@
         <v>317</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>103</v>
@@ -6891,7 +6891,7 @@
         <v>318</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>103</v>
@@ -6907,7 +6907,7 @@
         <v>319</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>103</v>
@@ -6923,7 +6923,7 @@
         <v>320</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>103</v>
@@ -6939,7 +6939,7 @@
         <v>321</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
@@ -6953,7 +6953,7 @@
         <v>322</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>103</v>
@@ -6969,7 +6969,7 @@
         <v>323</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>103</v>
@@ -6985,7 +6985,7 @@
         <v>324</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>103</v>
@@ -7001,7 +7001,7 @@
         <v>325</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>103</v>
@@ -7017,7 +7017,7 @@
         <v>326</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
@@ -7031,7 +7031,7 @@
         <v>327</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>103</v>
@@ -7047,7 +7047,7 @@
         <v>328</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>103</v>
@@ -7063,7 +7063,7 @@
         <v>329</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>103</v>
@@ -7079,7 +7079,7 @@
         <v>330</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>103</v>
@@ -7095,7 +7095,7 @@
         <v>331</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
@@ -7109,7 +7109,7 @@
         <v>332</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>103</v>
@@ -7125,7 +7125,7 @@
         <v>333</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
@@ -7139,7 +7139,7 @@
         <v>334</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
@@ -7153,7 +7153,7 @@
         <v>335</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>103</v>
@@ -7169,7 +7169,7 @@
         <v>336</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>103</v>
@@ -7185,7 +7185,7 @@
         <v>337</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>103</v>
@@ -7201,7 +7201,7 @@
         <v>338</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>103</v>
@@ -7217,7 +7217,7 @@
         <v>339</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -7231,7 +7231,7 @@
         <v>340</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
@@ -7245,7 +7245,7 @@
         <v>341</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>103</v>
@@ -7261,7 +7261,7 @@
         <v>342</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>103</v>
@@ -7277,7 +7277,7 @@
         <v>343</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
@@ -7291,7 +7291,7 @@
         <v>344</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
@@ -7305,7 +7305,7 @@
         <v>345</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
@@ -7319,7 +7319,7 @@
         <v>346</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>103</v>
@@ -7335,7 +7335,7 @@
         <v>347</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
@@ -7349,7 +7349,7 @@
         <v>348</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -7363,7 +7363,7 @@
         <v>349</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>103</v>
@@ -7379,7 +7379,7 @@
         <v>350</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>103</v>
@@ -7395,7 +7395,7 @@
         <v>351</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>103</v>
@@ -7411,7 +7411,7 @@
         <v>352</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>103</v>
@@ -7427,7 +7427,7 @@
         <v>353</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>103</v>
@@ -7443,7 +7443,7 @@
         <v>354</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
@@ -7457,7 +7457,7 @@
         <v>355</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
@@ -7471,7 +7471,7 @@
         <v>356</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>103</v>
@@ -7487,7 +7487,7 @@
         <v>357</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>103</v>
@@ -7503,7 +7503,7 @@
         <v>358</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>103</v>
@@ -7519,7 +7519,7 @@
         <v>359</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>103</v>
@@ -7535,7 +7535,7 @@
         <v>360</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
@@ -7549,7 +7549,7 @@
         <v>361</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>103</v>
@@ -7565,7 +7565,7 @@
         <v>362</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>103</v>
@@ -7581,7 +7581,7 @@
         <v>363</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>103</v>
@@ -7597,7 +7597,7 @@
         <v>364</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
@@ -7611,7 +7611,7 @@
         <v>365</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
@@ -7625,7 +7625,7 @@
         <v>366</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>103</v>
@@ -7641,7 +7641,7 @@
         <v>367</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>103</v>
@@ -7657,7 +7657,7 @@
         <v>368</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>103</v>
@@ -7673,7 +7673,7 @@
         <v>369</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>103</v>
@@ -7689,7 +7689,7 @@
         <v>370</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>103</v>
@@ -7705,7 +7705,7 @@
         <v>371</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>103</v>
@@ -7721,7 +7721,7 @@
         <v>372</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>103</v>
@@ -7737,7 +7737,7 @@
         <v>373</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>103</v>
@@ -7753,7 +7753,7 @@
         <v>374</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>103</v>
@@ -7769,7 +7769,7 @@
         <v>375</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>103</v>
@@ -7785,7 +7785,7 @@
         <v>376</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
@@ -7799,7 +7799,7 @@
         <v>377</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
@@ -7813,7 +7813,7 @@
         <v>378</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>103</v>
@@ -7829,7 +7829,7 @@
         <v>379</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
@@ -7843,7 +7843,7 @@
         <v>380</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
@@ -7857,7 +7857,7 @@
         <v>381</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
@@ -7871,7 +7871,7 @@
         <v>382</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
@@ -7885,7 +7885,7 @@
         <v>383</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
@@ -7899,7 +7899,7 @@
         <v>384</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
@@ -7913,7 +7913,7 @@
         <v>385</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
@@ -7927,7 +7927,7 @@
         <v>386</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
@@ -7941,7 +7941,7 @@
         <v>387</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
@@ -7955,7 +7955,7 @@
         <v>388</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
@@ -7969,7 +7969,7 @@
         <v>389</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
@@ -7983,7 +7983,7 @@
         <v>390</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -7997,7 +7997,7 @@
         <v>391</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
@@ -8011,7 +8011,7 @@
         <v>392</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
@@ -8025,7 +8025,7 @@
         <v>393</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
@@ -8039,7 +8039,7 @@
         <v>394</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
@@ -8053,7 +8053,7 @@
         <v>395</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
@@ -8067,7 +8067,7 @@
         <v>396</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
@@ -8081,7 +8081,7 @@
         <v>397</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
@@ -8095,7 +8095,7 @@
         <v>398</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
@@ -8109,7 +8109,7 @@
         <v>399</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
@@ -8123,7 +8123,7 @@
         <v>400</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
@@ -8137,7 +8137,7 @@
         <v>401</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
@@ -8151,7 +8151,7 @@
         <v>402</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
@@ -8165,7 +8165,7 @@
         <v>403</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
@@ -8179,7 +8179,7 @@
         <v>404</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
@@ -8193,7 +8193,7 @@
         <v>405</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -8207,7 +8207,7 @@
         <v>406</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>103</v>
@@ -8223,7 +8223,7 @@
         <v>407</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -8237,7 +8237,7 @@
         <v>408</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -8251,7 +8251,7 @@
         <v>409</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -8265,7 +8265,7 @@
         <v>410</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -8279,7 +8279,7 @@
         <v>411</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -8293,7 +8293,7 @@
         <v>412</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>103</v>
@@ -8309,7 +8309,7 @@
         <v>413</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>103</v>
@@ -8325,7 +8325,7 @@
         <v>414</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
@@ -8339,7 +8339,7 @@
         <v>415</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
@@ -8353,7 +8353,7 @@
         <v>416</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>103</v>
@@ -8369,7 +8369,7 @@
         <v>417</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>103</v>
@@ -8385,7 +8385,7 @@
         <v>418</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D405" s="4"/>
       <c r="E405" s="21"/>
@@ -8399,7 +8399,7 @@
         <v>419</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
@@ -8413,7 +8413,7 @@
         <v>420</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>103</v>
@@ -8429,7 +8429,7 @@
         <v>421</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
@@ -8443,7 +8443,7 @@
         <v>422</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
@@ -8457,7 +8457,7 @@
         <v>423</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>103</v>
@@ -8473,7 +8473,7 @@
         <v>424</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
@@ -8487,7 +8487,7 @@
         <v>425</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>103</v>
@@ -8503,7 +8503,7 @@
         <v>426</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
@@ -8517,7 +8517,7 @@
         <v>427</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>103</v>
@@ -8533,7 +8533,7 @@
         <v>428</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
@@ -8547,7 +8547,7 @@
         <v>429</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
@@ -8561,7 +8561,7 @@
         <v>430</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
@@ -8575,7 +8575,7 @@
         <v>431</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
@@ -8589,7 +8589,7 @@
         <v>432</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
@@ -8603,7 +8603,7 @@
         <v>433</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
@@ -8617,7 +8617,7 @@
         <v>434</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
@@ -8631,7 +8631,7 @@
         <v>435</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
@@ -8645,7 +8645,7 @@
         <v>436</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
@@ -8659,7 +8659,7 @@
         <v>437</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -8673,7 +8673,7 @@
         <v>438</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
@@ -8687,7 +8687,7 @@
         <v>439</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
@@ -8701,7 +8701,7 @@
         <v>440</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
@@ -8715,7 +8715,7 @@
         <v>441</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
@@ -8729,7 +8729,7 @@
         <v>442</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
@@ -8743,7 +8743,7 @@
         <v>443</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>103</v>
@@ -8759,7 +8759,7 @@
         <v>444</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -8773,7 +8773,7 @@
         <v>445</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -8787,7 +8787,7 @@
         <v>446</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -8801,7 +8801,7 @@
         <v>447</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
@@ -8815,7 +8815,7 @@
         <v>448</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -8829,7 +8829,7 @@
         <v>449</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -8843,7 +8843,7 @@
         <v>450</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -8857,7 +8857,7 @@
         <v>451</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
@@ -8871,7 +8871,7 @@
         <v>452</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
@@ -8885,7 +8885,7 @@
         <v>453</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
@@ -8899,7 +8899,7 @@
         <v>454</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
@@ -8913,7 +8913,7 @@
         <v>455</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
@@ -8927,7 +8927,7 @@
         <v>456</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
@@ -8941,7 +8941,7 @@
         <v>457</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
@@ -8955,7 +8955,7 @@
         <v>458</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
@@ -8969,7 +8969,7 @@
         <v>459</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
@@ -8983,7 +8983,7 @@
         <v>460</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
@@ -8997,7 +8997,7 @@
         <v>461</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
@@ -9011,7 +9011,7 @@
         <v>462</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
@@ -9025,7 +9025,7 @@
         <v>463</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
@@ -9039,7 +9039,7 @@
         <v>464</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>103</v>
@@ -9055,7 +9055,7 @@
         <v>465</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
@@ -9069,7 +9069,7 @@
         <v>466</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
@@ -9083,7 +9083,7 @@
         <v>467</v>
       </c>
       <c r="C454" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
@@ -9097,7 +9097,7 @@
         <v>468</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
@@ -9111,7 +9111,7 @@
         <v>469</v>
       </c>
       <c r="C456" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
@@ -9125,7 +9125,7 @@
         <v>470</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>103</v>
@@ -9141,7 +9141,7 @@
         <v>471</v>
       </c>
       <c r="C458" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>103</v>
@@ -9157,7 +9157,7 @@
         <v>472</v>
       </c>
       <c r="C459" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>103</v>
@@ -9173,7 +9173,7 @@
         <v>473</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
@@ -9187,7 +9187,7 @@
         <v>474</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
@@ -9198,13 +9198,13 @@
         <v>461</v>
       </c>
       <c r="B462" s="6" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C462" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="D462" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="D462" s="4" t="s">
-        <v>477</v>
       </c>
       <c r="E462" s="4"/>
       <c r="F462" s="4"/>
@@ -9214,14 +9214,14 @@
         <v>462</v>
       </c>
       <c r="B463" s="24" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C463" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D463" s="25"/>
       <c r="E463" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F463" s="20"/>
     </row>
@@ -9230,14 +9230,14 @@
         <v>463</v>
       </c>
       <c r="B464" s="24" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C464" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D464" s="25"/>
       <c r="E464" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F464" s="20"/>
     </row>
@@ -9246,14 +9246,14 @@
         <v>464</v>
       </c>
       <c r="B465" s="24" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C465" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D465" s="25"/>
       <c r="E465" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F465" s="20"/>
     </row>
@@ -9262,14 +9262,14 @@
         <v>465</v>
       </c>
       <c r="B466" s="24" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C466" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D466" s="25"/>
       <c r="E466" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F466" s="20"/>
     </row>
@@ -9278,14 +9278,14 @@
         <v>466</v>
       </c>
       <c r="B467" s="24" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C467" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D467" s="25"/>
       <c r="E467" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F467" s="20"/>
     </row>
@@ -9294,14 +9294,14 @@
         <v>467</v>
       </c>
       <c r="B468" s="24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C468" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D468" s="25"/>
       <c r="E468" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F468" s="20"/>
     </row>
@@ -9310,14 +9310,14 @@
         <v>468</v>
       </c>
       <c r="B469" s="24" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C469" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D469" s="25"/>
       <c r="E469" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F469" s="20"/>
     </row>
@@ -9326,14 +9326,14 @@
         <v>469</v>
       </c>
       <c r="B470" s="24" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C470" s="24" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D470" s="25"/>
       <c r="E470" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F470" s="20"/>
     </row>
@@ -9342,14 +9342,14 @@
         <v>470</v>
       </c>
       <c r="B471" s="24" t="s">
+        <v>487</v>
+      </c>
+      <c r="C471" s="24" t="s">
         <v>488</v>
-      </c>
-      <c r="C471" s="24" t="s">
-        <v>489</v>
       </c>
       <c r="D471" s="25"/>
       <c r="E471" s="15" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F471" s="20"/>
     </row>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D806EED4-0450-4ECF-8D75-B1C263C3AD5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DBB788-4138-4F7C-B9D0-B8EFA3C6BEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="492">
   <si>
     <t>STT</t>
   </si>
@@ -585,9 +585,6 @@
     <t>VNET861385071527587</t>
   </si>
   <si>
-    <t>Không có nguồn RFID</t>
-  </si>
-  <si>
     <t>Thịnh đang test</t>
   </si>
   <si>
@@ -1458,9 +1455,6 @@
     <t>06/07/2026</t>
   </si>
   <si>
-    <t>ID sai</t>
-  </si>
-  <si>
     <t>Không chốt GPS, IPEX bị lỏng</t>
   </si>
   <si>
@@ -1491,9 +1485,6 @@
     <t>VNET861385070686905</t>
   </si>
   <si>
-    <t>VNET861385071482486</t>
-  </si>
-  <si>
     <t>22/07/2026</t>
   </si>
   <si>
@@ -1510,6 +1501,9 @@
   </si>
   <si>
     <t>VNET861385071455805</t>
+  </si>
+  <si>
+    <t>VNET861375071482486</t>
   </si>
 </sst>
 </file>
@@ -1602,7 +1596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1634,12 +1628,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1655,7 +1643,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1663,30 +1650,20 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2020,13 +1997,13 @@
   <dimension ref="A1:G471"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="15" style="12" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" style="11" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" style="14" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" style="10" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" style="22" customWidth="1"/>
+    <col min="3" max="3" width="15" style="22" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" style="12" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -2037,13 +2014,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>193</v>
+      <c r="E1" s="17" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -2054,13 +2031,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="15"/>
-      <c r="F2" s="22"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="21"/>
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2071,13 +2048,13 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="22"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="21"/>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2088,13 +2065,13 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="22"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="21"/>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2105,13 +2082,13 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="22"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="21"/>
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2122,13 +2099,13 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="22"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="21"/>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2139,13 +2116,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="22"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="21"/>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2156,13 +2133,13 @@
         <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="22"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="21"/>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2173,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="22"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="21"/>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2190,13 +2167,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="22"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2207,13 +2184,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="22"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2224,13 +2201,13 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="22"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="21"/>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2241,13 +2218,13 @@
         <v>13</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="22"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="21"/>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2258,15 +2235,15 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="F14" s="22"/>
+      <c r="E14" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2277,13 +2254,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2294,13 +2271,13 @@
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="23"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="21"/>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2311,13 +2288,13 @@
         <v>17</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="23"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="21"/>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2328,14 +2305,14 @@
         <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="9"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
@@ -2345,13 +2322,13 @@
         <v>19</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="23"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="21"/>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2362,13 +2339,13 @@
         <v>20</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="23"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="21"/>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2379,13 +2356,13 @@
         <v>21</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="23"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="21"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2396,13 +2373,13 @@
         <v>22</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="23"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="20"/>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2413,13 +2390,13 @@
         <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="23"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="20"/>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2430,13 +2407,13 @@
         <v>24</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="23"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2447,13 +2424,13 @@
         <v>25</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="23"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="20"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2464,13 +2441,13 @@
         <v>26</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="23"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="20"/>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2481,13 +2458,13 @@
         <v>27</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="23"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="20"/>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2498,13 +2475,13 @@
         <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="23"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="20"/>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2515,13 +2492,13 @@
         <v>29</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="23"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="20"/>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2532,13 +2509,13 @@
         <v>30</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="23"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="20"/>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2549,13 +2526,13 @@
         <v>31</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="23"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="20"/>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2566,13 +2543,13 @@
         <v>32</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="23"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="20"/>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2583,13 +2560,13 @@
         <v>33</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="23"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="20"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -2599,13 +2576,13 @@
         <v>34</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="15"/>
-      <c r="F34" s="23"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="20"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -2615,13 +2592,13 @@
         <v>35</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="23"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="20"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -2631,13 +2608,13 @@
         <v>36</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="23"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="20"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -2647,13 +2624,13 @@
         <v>37</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="23"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="20"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -2663,13 +2640,13 @@
         <v>38</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="15"/>
-      <c r="F38" s="23"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="20"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
@@ -2679,13 +2656,13 @@
         <v>39</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="23"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="20"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
@@ -2695,13 +2672,13 @@
         <v>40</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="22"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="19"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
@@ -2711,13 +2688,13 @@
         <v>41</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="22"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="19"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
@@ -2727,13 +2704,13 @@
         <v>42</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="20"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
@@ -2743,13 +2720,13 @@
         <v>43</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="20"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
@@ -2759,13 +2736,13 @@
         <v>44</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="20"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
@@ -2775,13 +2752,13 @@
         <v>45</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="20"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
@@ -2791,13 +2768,13 @@
         <v>46</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E46" s="15"/>
-      <c r="F46" s="20"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
@@ -2807,13 +2784,13 @@
         <v>47</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="15"/>
-      <c r="F47" s="20"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
@@ -2823,13 +2800,13 @@
         <v>48</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="20"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
@@ -2839,13 +2816,13 @@
         <v>49</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="20"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
@@ -2855,13 +2832,13 @@
         <v>50</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="20"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
@@ -2871,13 +2848,13 @@
         <v>51</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="20"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
@@ -2887,13 +2864,13 @@
         <v>52</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="20"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
@@ -2903,13 +2880,13 @@
         <v>53</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="20"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
@@ -2919,13 +2896,13 @@
         <v>54</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="20"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
@@ -2935,13 +2912,13 @@
         <v>55</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E55" s="15"/>
-      <c r="F55" s="20"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
@@ -2951,13 +2928,13 @@
         <v>56</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="20"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
@@ -2967,13 +2944,13 @@
         <v>57</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="20"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
@@ -2983,13 +2960,13 @@
         <v>58</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E58" s="15"/>
-      <c r="F58" s="20"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
@@ -2999,13 +2976,13 @@
         <v>59</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E59" s="15"/>
-      <c r="F59" s="20"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
@@ -3015,13 +2992,13 @@
         <v>60</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="20"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
@@ -3031,13 +3008,13 @@
         <v>61</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="20"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
@@ -3047,13 +3024,13 @@
         <v>62</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E62" s="15"/>
-      <c r="F62" s="20"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
@@ -3063,13 +3040,13 @@
         <v>63</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E63" s="15"/>
-      <c r="F63" s="20"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
@@ -3079,13 +3056,13 @@
         <v>64</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E64" s="15"/>
-      <c r="F64" s="20"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
@@ -3095,13 +3072,13 @@
         <v>65</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E65" s="15"/>
-      <c r="F65" s="20"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
@@ -3111,13 +3088,13 @@
         <v>66</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E66" s="15"/>
-      <c r="F66" s="20"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
@@ -3127,13 +3104,13 @@
         <v>67</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E67" s="15"/>
-      <c r="F67" s="20"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
@@ -3143,13 +3120,13 @@
         <v>68</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E68" s="15"/>
-      <c r="F68" s="20"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
@@ -3159,13 +3136,13 @@
         <v>69</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="15"/>
-      <c r="F69" s="20"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
@@ -3175,13 +3152,13 @@
         <v>70</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E70" s="15"/>
-      <c r="F70" s="20"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
@@ -3191,13 +3168,13 @@
         <v>71</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="20"/>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
@@ -3207,13 +3184,13 @@
         <v>72</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E72" s="15"/>
-      <c r="F72" s="20"/>
+      <c r="E72" s="13"/>
+      <c r="F72" s="13"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
@@ -3223,13 +3200,13 @@
         <v>73</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E73" s="15"/>
-      <c r="F73" s="20"/>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
@@ -3239,13 +3216,13 @@
         <v>74</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E74" s="15"/>
-      <c r="F74" s="20"/>
+      <c r="E74" s="13"/>
+      <c r="F74" s="13"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
@@ -3255,13 +3232,13 @@
         <v>75</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E75" s="15"/>
-      <c r="F75" s="20"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
@@ -3271,13 +3248,13 @@
         <v>76</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="20"/>
+      <c r="E76" s="13"/>
+      <c r="F76" s="13"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
@@ -3287,13 +3264,13 @@
         <v>77</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E77" s="15"/>
-      <c r="F77" s="20"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
@@ -3303,13 +3280,13 @@
         <v>78</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="20"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
@@ -3319,13 +3296,13 @@
         <v>79</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E79" s="15"/>
-      <c r="F79" s="20"/>
+      <c r="E79" s="13"/>
+      <c r="F79" s="13"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
@@ -3335,13 +3312,13 @@
         <v>80</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E80" s="15"/>
-      <c r="F80" s="20"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="13"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
@@ -3351,13 +3328,13 @@
         <v>81</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E81" s="15"/>
-      <c r="F81" s="20"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="13"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
@@ -3367,13 +3344,13 @@
         <v>82</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E82" s="15"/>
-      <c r="F82" s="20"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
@@ -3383,13 +3360,13 @@
         <v>83</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E83" s="15"/>
-      <c r="F83" s="20"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="13"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
@@ -3399,13 +3376,13 @@
         <v>84</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E84" s="15"/>
-      <c r="F84" s="20"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
@@ -3415,13 +3392,13 @@
         <v>85</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E85" s="15"/>
-      <c r="F85" s="20"/>
+      <c r="E85" s="13"/>
+      <c r="F85" s="13"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
@@ -3431,13 +3408,13 @@
         <v>86</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E86" s="15"/>
-      <c r="F86" s="20"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
@@ -3447,13 +3424,13 @@
         <v>87</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E87" s="15"/>
-      <c r="F87" s="20"/>
+      <c r="E87" s="13"/>
+      <c r="F87" s="13"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
@@ -3463,13 +3440,13 @@
         <v>88</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E88" s="15"/>
-      <c r="F88" s="20"/>
+      <c r="E88" s="13"/>
+      <c r="F88" s="13"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
@@ -3479,13 +3456,13 @@
         <v>89</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E89" s="15"/>
-      <c r="F89" s="20"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
@@ -3495,13 +3472,13 @@
         <v>90</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E90" s="15"/>
-      <c r="F90" s="20"/>
+      <c r="E90" s="13"/>
+      <c r="F90" s="13"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
@@ -3511,13 +3488,13 @@
         <v>91</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E91" s="15"/>
-      <c r="F91" s="20"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
@@ -3527,13 +3504,13 @@
         <v>92</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E92" s="15"/>
-      <c r="F92" s="20"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="13"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
@@ -3543,13 +3520,13 @@
         <v>93</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E93" s="15"/>
-      <c r="F93" s="20"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
@@ -3559,13 +3536,13 @@
         <v>94</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E94" s="15"/>
-      <c r="F94" s="20"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
@@ -3575,13 +3552,13 @@
         <v>95</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E95" s="15"/>
-      <c r="F95" s="20"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
@@ -3591,13 +3568,13 @@
         <v>96</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E96" s="15"/>
-      <c r="F96" s="20"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
@@ -3607,13 +3584,13 @@
         <v>97</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E97" s="15"/>
-      <c r="F97" s="20"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
@@ -3623,13 +3600,13 @@
         <v>98</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E98" s="15"/>
-      <c r="F98" s="20"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
@@ -3639,13 +3616,13 @@
         <v>99</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E99" s="15"/>
-      <c r="F99" s="20"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
@@ -3655,13 +3632,13 @@
         <v>100</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E100" s="15"/>
-      <c r="F100" s="20"/>
+      <c r="E100" s="13"/>
+      <c r="F100" s="13"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
@@ -3671,13 +3648,13 @@
         <v>101</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E101" s="15"/>
-      <c r="F101" s="20"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
@@ -3687,13 +3664,13 @@
         <v>104</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E102" s="15"/>
-      <c r="F102" s="20"/>
+      <c r="E102" s="13"/>
+      <c r="F102" s="13"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
@@ -3703,13 +3680,13 @@
         <v>105</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E103" s="15"/>
-      <c r="F103" s="20"/>
+      <c r="E103" s="13"/>
+      <c r="F103" s="13"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
@@ -3719,13 +3696,13 @@
         <v>106</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E104" s="15"/>
-      <c r="F104" s="20"/>
+      <c r="E104" s="13"/>
+      <c r="F104" s="13"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
@@ -3735,13 +3712,13 @@
         <v>107</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E105" s="15"/>
-      <c r="F105" s="20"/>
+      <c r="E105" s="13"/>
+      <c r="F105" s="13"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
@@ -3751,13 +3728,13 @@
         <v>108</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E106" s="15"/>
-      <c r="F106" s="20"/>
+      <c r="E106" s="13"/>
+      <c r="F106" s="13"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
@@ -3767,13 +3744,13 @@
         <v>109</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E107" s="15"/>
-      <c r="F107" s="20"/>
+      <c r="E107" s="13"/>
+      <c r="F107" s="13"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
@@ -3783,13 +3760,13 @@
         <v>110</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="20"/>
+      <c r="E108" s="13"/>
+      <c r="F108" s="13"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
@@ -3799,13 +3776,13 @@
         <v>111</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E109" s="15"/>
-      <c r="F109" s="20"/>
+      <c r="E109" s="13"/>
+      <c r="F109" s="13"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
@@ -3815,13 +3792,13 @@
         <v>112</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="20"/>
+      <c r="E110" s="13"/>
+      <c r="F110" s="13"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
@@ -3831,13 +3808,13 @@
         <v>113</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E111" s="15"/>
-      <c r="F111" s="20"/>
+      <c r="E111" s="13"/>
+      <c r="F111" s="13"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
@@ -3847,13 +3824,13 @@
         <v>114</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E112" s="15"/>
-      <c r="F112" s="20"/>
+      <c r="E112" s="13"/>
+      <c r="F112" s="13"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
@@ -3863,13 +3840,13 @@
         <v>115</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E113" s="15"/>
-      <c r="F113" s="20"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="13"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
@@ -3879,13 +3856,13 @@
         <v>116</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E114" s="15"/>
-      <c r="F114" s="20"/>
+      <c r="E114" s="13"/>
+      <c r="F114" s="13"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
@@ -3895,13 +3872,13 @@
         <v>117</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D115" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E115" s="15"/>
-      <c r="F115" s="20"/>
+      <c r="E115" s="13"/>
+      <c r="F115" s="13"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
@@ -3911,13 +3888,13 @@
         <v>118</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E116" s="15"/>
-      <c r="F116" s="20"/>
+      <c r="E116" s="13"/>
+      <c r="F116" s="13"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
@@ -3927,13 +3904,13 @@
         <v>119</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E117" s="15"/>
-      <c r="F117" s="20"/>
+      <c r="E117" s="13"/>
+      <c r="F117" s="13"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
@@ -3943,13 +3920,13 @@
         <v>120</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D118" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E118" s="15"/>
-      <c r="F118" s="20"/>
+      <c r="E118" s="13"/>
+      <c r="F118" s="13"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
@@ -3959,13 +3936,13 @@
         <v>121</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E119" s="15"/>
-      <c r="F119" s="20"/>
+      <c r="E119" s="13"/>
+      <c r="F119" s="13"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
@@ -3975,13 +3952,13 @@
         <v>122</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E120" s="15"/>
-      <c r="F120" s="20"/>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
@@ -3991,13 +3968,13 @@
         <v>123</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E121" s="15"/>
-      <c r="F121" s="20"/>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
@@ -4007,13 +3984,13 @@
         <v>124</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E122" s="15"/>
-      <c r="F122" s="20"/>
+      <c r="E122" s="13"/>
+      <c r="F122" s="13"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
@@ -4023,13 +4000,13 @@
         <v>125</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E123" s="15"/>
-      <c r="F123" s="20"/>
+      <c r="E123" s="13"/>
+      <c r="F123" s="13"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
@@ -4039,13 +4016,13 @@
         <v>126</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E124" s="15"/>
-      <c r="F124" s="20"/>
+      <c r="E124" s="13"/>
+      <c r="F124" s="13"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
@@ -4055,13 +4032,13 @@
         <v>127</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D125" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="E125" s="15"/>
-      <c r="F125" s="20"/>
+        <v>188</v>
+      </c>
+      <c r="D125" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="E125" s="13"/>
+      <c r="F125" s="13"/>
     </row>
     <row r="126" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
@@ -4071,15 +4048,15 @@
         <v>128</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D126" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="E126" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="F126" s="20"/>
+        <v>188</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="F126" s="13"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
@@ -4089,13 +4066,13 @@
         <v>129</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E127" s="15"/>
-      <c r="F127" s="20"/>
+      <c r="E127" s="13"/>
+      <c r="F127" s="13"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
@@ -4105,13 +4082,13 @@
         <v>130</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E128" s="15"/>
-      <c r="F128" s="20"/>
+      <c r="E128" s="13"/>
+      <c r="F128" s="13"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
@@ -4121,13 +4098,13 @@
         <v>131</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E129" s="15"/>
-      <c r="F129" s="20"/>
+      <c r="E129" s="13"/>
+      <c r="F129" s="13"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
@@ -4137,13 +4114,13 @@
         <v>132</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E130" s="15"/>
-      <c r="F130" s="20"/>
+      <c r="E130" s="13"/>
+      <c r="F130" s="13"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
@@ -4153,13 +4130,13 @@
         <v>133</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E131" s="15"/>
-      <c r="F131" s="20"/>
+      <c r="E131" s="13"/>
+      <c r="F131" s="13"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
@@ -4169,13 +4146,13 @@
         <v>134</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E132" s="15"/>
-      <c r="F132" s="20"/>
+      <c r="E132" s="13"/>
+      <c r="F132" s="13"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
@@ -4185,13 +4162,13 @@
         <v>135</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E133" s="15"/>
-      <c r="F133" s="20"/>
+      <c r="E133" s="13"/>
+      <c r="F133" s="13"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
@@ -4201,13 +4178,13 @@
         <v>136</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E134" s="15"/>
-      <c r="F134" s="20"/>
+      <c r="E134" s="13"/>
+      <c r="F134" s="13"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
@@ -4217,13 +4194,13 @@
         <v>137</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E135" s="15"/>
-      <c r="F135" s="20"/>
+      <c r="E135" s="13"/>
+      <c r="F135" s="13"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
@@ -4233,13 +4210,13 @@
         <v>138</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E136" s="15"/>
-      <c r="F136" s="20"/>
+      <c r="E136" s="13"/>
+      <c r="F136" s="13"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
@@ -4249,13 +4226,13 @@
         <v>139</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E137" s="15"/>
-      <c r="F137" s="20"/>
+      <c r="E137" s="13"/>
+      <c r="F137" s="13"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
@@ -4265,13 +4242,13 @@
         <v>140</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E138" s="15"/>
-      <c r="F138" s="20"/>
+      <c r="E138" s="13"/>
+      <c r="F138" s="13"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
@@ -4281,13 +4258,13 @@
         <v>141</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E139" s="15"/>
-      <c r="F139" s="20"/>
+      <c r="E139" s="13"/>
+      <c r="F139" s="13"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
@@ -4297,13 +4274,13 @@
         <v>142</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E140" s="15"/>
-      <c r="F140" s="20"/>
+      <c r="E140" s="13"/>
+      <c r="F140" s="13"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
@@ -4313,13 +4290,13 @@
         <v>143</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E141" s="15"/>
-      <c r="F141" s="20"/>
+      <c r="E141" s="13"/>
+      <c r="F141" s="13"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
@@ -4329,13 +4306,13 @@
         <v>144</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E142" s="15"/>
-      <c r="F142" s="20"/>
+      <c r="E142" s="13"/>
+      <c r="F142" s="13"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
@@ -4345,13 +4322,13 @@
         <v>145</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E143" s="15"/>
-      <c r="F143" s="20"/>
+      <c r="E143" s="13"/>
+      <c r="F143" s="13"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
@@ -4361,13 +4338,13 @@
         <v>146</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E144" s="15"/>
-      <c r="F144" s="20"/>
+      <c r="E144" s="13"/>
+      <c r="F144" s="13"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
@@ -4377,13 +4354,13 @@
         <v>147</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E145" s="15"/>
-      <c r="F145" s="20"/>
+      <c r="E145" s="13"/>
+      <c r="F145" s="13"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
@@ -4393,13 +4370,13 @@
         <v>148</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E146" s="15"/>
-      <c r="F146" s="20"/>
+      <c r="E146" s="13"/>
+      <c r="F146" s="13"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
@@ -4409,13 +4386,13 @@
         <v>149</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E147" s="15"/>
-      <c r="F147" s="20"/>
+      <c r="E147" s="13"/>
+      <c r="F147" s="13"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
@@ -4425,13 +4402,13 @@
         <v>150</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E148" s="15"/>
-      <c r="F148" s="20"/>
+      <c r="E148" s="13"/>
+      <c r="F148" s="13"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
@@ -4441,13 +4418,13 @@
         <v>151</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E149" s="15"/>
-      <c r="F149" s="20"/>
+      <c r="E149" s="13"/>
+      <c r="F149" s="13"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
@@ -4457,13 +4434,13 @@
         <v>152</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E150" s="15"/>
-      <c r="F150" s="20"/>
+      <c r="E150" s="13"/>
+      <c r="F150" s="13"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
@@ -4473,13 +4450,13 @@
         <v>153</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E151" s="15"/>
-      <c r="F151" s="20"/>
+      <c r="E151" s="13"/>
+      <c r="F151" s="13"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
@@ -4489,13 +4466,13 @@
         <v>154</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E152" s="15"/>
-      <c r="F152" s="20"/>
+      <c r="E152" s="13"/>
+      <c r="F152" s="13"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
@@ -4505,13 +4482,13 @@
         <v>155</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E153" s="15"/>
-      <c r="F153" s="20"/>
+      <c r="E153" s="13"/>
+      <c r="F153" s="13"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
@@ -4521,13 +4498,13 @@
         <v>156</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E154" s="15"/>
-      <c r="F154" s="20"/>
+      <c r="E154" s="13"/>
+      <c r="F154" s="13"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
@@ -4537,13 +4514,13 @@
         <v>157</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E155" s="15"/>
-      <c r="F155" s="20"/>
+      <c r="E155" s="13"/>
+      <c r="F155" s="13"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
@@ -4553,13 +4530,13 @@
         <v>158</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E156" s="15"/>
-      <c r="F156" s="20"/>
+      <c r="E156" s="13"/>
+      <c r="F156" s="13"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
@@ -4569,13 +4546,13 @@
         <v>159</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E157" s="15"/>
-      <c r="F157" s="20"/>
+      <c r="E157" s="13"/>
+      <c r="F157" s="13"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
@@ -4585,13 +4562,13 @@
         <v>160</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E158" s="15"/>
-      <c r="F158" s="20"/>
+      <c r="E158" s="13"/>
+      <c r="F158" s="13"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
@@ -4601,13 +4578,13 @@
         <v>161</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E159" s="15"/>
-      <c r="F159" s="20"/>
+      <c r="E159" s="13"/>
+      <c r="F159" s="13"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
@@ -4617,13 +4594,13 @@
         <v>162</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E160" s="15"/>
-      <c r="F160" s="20"/>
+      <c r="E160" s="13"/>
+      <c r="F160" s="13"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
@@ -4633,13 +4610,13 @@
         <v>163</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E161" s="15"/>
-      <c r="F161" s="20"/>
+      <c r="E161" s="13"/>
+      <c r="F161" s="13"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
@@ -4649,13 +4626,13 @@
         <v>164</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E162" s="15"/>
-      <c r="F162" s="20"/>
+      <c r="E162" s="13"/>
+      <c r="F162" s="13"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
@@ -4665,13 +4642,13 @@
         <v>165</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E163" s="15"/>
-      <c r="F163" s="20"/>
+      <c r="E163" s="13"/>
+      <c r="F163" s="13"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
@@ -4681,13 +4658,13 @@
         <v>166</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E164" s="15"/>
-      <c r="F164" s="20"/>
+      <c r="E164" s="13"/>
+      <c r="F164" s="13"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
@@ -4697,13 +4674,13 @@
         <v>167</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E165" s="15"/>
-      <c r="F165" s="20"/>
+      <c r="E165" s="13"/>
+      <c r="F165" s="13"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
@@ -4713,13 +4690,13 @@
         <v>168</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E166" s="15"/>
-      <c r="F166" s="20"/>
+      <c r="E166" s="13"/>
+      <c r="F166" s="13"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
@@ -4729,13 +4706,13 @@
         <v>169</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E167" s="15"/>
-      <c r="F167" s="20"/>
+      <c r="E167" s="13"/>
+      <c r="F167" s="13"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
@@ -4745,13 +4722,13 @@
         <v>170</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E168" s="15"/>
-      <c r="F168" s="20"/>
+      <c r="E168" s="13"/>
+      <c r="F168" s="13"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
@@ -4761,13 +4738,13 @@
         <v>171</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="15"/>
-      <c r="F169" s="20"/>
+      <c r="E169" s="13"/>
+      <c r="F169" s="13"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
@@ -4777,13 +4754,13 @@
         <v>172</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E170" s="15"/>
-      <c r="F170" s="20"/>
+      <c r="E170" s="13"/>
+      <c r="F170" s="13"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
@@ -4793,13 +4770,13 @@
         <v>173</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E171" s="15"/>
-      <c r="F171" s="20"/>
+      <c r="E171" s="13"/>
+      <c r="F171" s="13"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
@@ -4809,13 +4786,13 @@
         <v>174</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E172" s="15"/>
-      <c r="F172" s="20"/>
+      <c r="E172" s="13"/>
+      <c r="F172" s="13"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
@@ -4825,13 +4802,13 @@
         <v>175</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E173" s="15"/>
-      <c r="F173" s="20"/>
+      <c r="E173" s="13"/>
+      <c r="F173" s="13"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
@@ -4841,13 +4818,13 @@
         <v>176</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E174" s="15"/>
-      <c r="F174" s="20"/>
+      <c r="E174" s="13"/>
+      <c r="F174" s="13"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
@@ -4857,13 +4834,13 @@
         <v>177</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E175" s="15"/>
-      <c r="F175" s="20"/>
+      <c r="E175" s="13"/>
+      <c r="F175" s="13"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
@@ -4873,13 +4850,13 @@
         <v>178</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E176" s="15"/>
-      <c r="F176" s="20"/>
+      <c r="E176" s="13"/>
+      <c r="F176" s="13"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
@@ -4889,13 +4866,13 @@
         <v>179</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E177" s="15"/>
-      <c r="F177" s="20"/>
+      <c r="E177" s="13"/>
+      <c r="F177" s="13"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
@@ -4905,13 +4882,13 @@
         <v>180</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E178" s="15"/>
-      <c r="F178" s="20"/>
+      <c r="E178" s="13"/>
+      <c r="F178" s="13"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
@@ -4921,13 +4898,13 @@
         <v>181</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E179" s="15"/>
-      <c r="F179" s="20"/>
+      <c r="E179" s="13"/>
+      <c r="F179" s="13"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
@@ -4937,13 +4914,13 @@
         <v>182</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E180" s="15"/>
-      <c r="F180" s="20"/>
+      <c r="E180" s="13"/>
+      <c r="F180" s="13"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
@@ -4953,11 +4930,11 @@
         <v>183</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D181" s="13"/>
-      <c r="E181" s="21"/>
-      <c r="F181" s="20"/>
+        <v>189</v>
+      </c>
+      <c r="D181" s="11"/>
+      <c r="E181" s="18"/>
+      <c r="F181" s="13"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
@@ -4967,144 +4944,144 @@
         <v>184</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E182" s="15"/>
-      <c r="F182" s="20"/>
+      <c r="E182" s="13"/>
+      <c r="F182" s="13"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>182</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E183" s="15"/>
-      <c r="F183" s="20"/>
+      <c r="E183" s="13"/>
+      <c r="F183" s="13"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>183</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E184" s="15"/>
-      <c r="F184" s="20"/>
+      <c r="E184" s="13"/>
+      <c r="F184" s="13"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>184</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E185" s="15"/>
-      <c r="F185" s="20"/>
+      <c r="E185" s="13"/>
+      <c r="F185" s="13"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>185</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E186" s="15"/>
-      <c r="F186" s="20"/>
+      <c r="E186" s="13"/>
+      <c r="F186" s="13"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>186</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E187" s="15"/>
-      <c r="F187" s="20"/>
+      <c r="E187" s="13"/>
+      <c r="F187" s="13"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>187</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E188" s="15"/>
-      <c r="F188" s="20"/>
+      <c r="E188" s="13"/>
+      <c r="F188" s="13"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>188</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E189" s="15"/>
-      <c r="F189" s="20"/>
+      <c r="E189" s="13"/>
+      <c r="F189" s="13"/>
     </row>
     <row r="190" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>189</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E190" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="F190" s="26" t="s">
-        <v>478</v>
+      <c r="E190" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="F190" s="23" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5112,1164 +5089,1164 @@
         <v>190</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E191" s="15"/>
-      <c r="F191" s="20"/>
+      <c r="E191" s="13"/>
+      <c r="F191" s="13"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>191</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E192" s="15"/>
-      <c r="F192" s="20"/>
+      <c r="E192" s="13"/>
+      <c r="F192" s="13"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>192</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E193" s="15"/>
-      <c r="F193" s="20"/>
+      <c r="E193" s="13"/>
+      <c r="F193" s="13"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>193</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D194" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E194" s="15"/>
-      <c r="F194" s="20"/>
+      <c r="E194" s="13"/>
+      <c r="F194" s="13"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>194</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E195" s="15"/>
-      <c r="F195" s="20"/>
+      <c r="E195" s="13"/>
+      <c r="F195" s="13"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>195</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D196" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E196" s="15"/>
-      <c r="F196" s="20"/>
+      <c r="E196" s="13"/>
+      <c r="F196" s="13"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>196</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E197" s="15"/>
-      <c r="F197" s="20"/>
+      <c r="E197" s="13"/>
+      <c r="F197" s="13"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>197</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D198" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E198" s="15"/>
-      <c r="F198" s="20"/>
+      <c r="E198" s="13"/>
+      <c r="F198" s="13"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>198</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E199" s="15"/>
-      <c r="F199" s="20"/>
+      <c r="E199" s="13"/>
+      <c r="F199" s="13"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
         <v>199</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D200" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E200" s="15"/>
-      <c r="F200" s="20"/>
+      <c r="E200" s="13"/>
+      <c r="F200" s="13"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>200</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E201" s="15"/>
-      <c r="F201" s="20"/>
+      <c r="E201" s="13"/>
+      <c r="F201" s="13"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>201</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D202" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E202" s="15"/>
-      <c r="F202" s="20"/>
+      <c r="E202" s="13"/>
+      <c r="F202" s="13"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
         <v>202</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E203" s="15"/>
-      <c r="F203" s="20"/>
+      <c r="E203" s="13"/>
+      <c r="F203" s="13"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
         <v>203</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D204" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E204" s="15"/>
-      <c r="F204" s="20"/>
+      <c r="E204" s="13"/>
+      <c r="F204" s="13"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
         <v>204</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E205" s="15"/>
-      <c r="F205" s="20"/>
+      <c r="E205" s="13"/>
+      <c r="F205" s="13"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
         <v>205</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D206" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E206" s="15"/>
-      <c r="F206" s="20"/>
+      <c r="E206" s="13"/>
+      <c r="F206" s="13"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
         <v>206</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E207" s="15"/>
-      <c r="F207" s="20"/>
+      <c r="E207" s="13"/>
+      <c r="F207" s="13"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
         <v>207</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D208" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E208" s="15"/>
-      <c r="F208" s="20"/>
+      <c r="E208" s="13"/>
+      <c r="F208" s="13"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
         <v>208</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E209" s="15"/>
-      <c r="F209" s="20"/>
+      <c r="E209" s="13"/>
+      <c r="F209" s="13"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
         <v>209</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D210" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E210" s="15"/>
-      <c r="F210" s="20"/>
+      <c r="E210" s="13"/>
+      <c r="F210" s="13"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
         <v>210</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E211" s="15"/>
-      <c r="F211" s="20"/>
+      <c r="E211" s="13"/>
+      <c r="F211" s="13"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
         <v>211</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D212" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E212" s="15"/>
-      <c r="F212" s="20"/>
+      <c r="E212" s="13"/>
+      <c r="F212" s="13"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
         <v>212</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E213" s="15"/>
-      <c r="F213" s="20"/>
+      <c r="E213" s="13"/>
+      <c r="F213" s="13"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>213</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D214" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E214" s="15"/>
-      <c r="F214" s="20"/>
+      <c r="E214" s="13"/>
+      <c r="F214" s="13"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>214</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E215" s="15"/>
-      <c r="F215" s="20"/>
+      <c r="E215" s="13"/>
+      <c r="F215" s="13"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>215</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D216" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E216" s="15"/>
-      <c r="F216" s="20"/>
+      <c r="E216" s="13"/>
+      <c r="F216" s="13"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>216</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E217" s="15"/>
-      <c r="F217" s="20"/>
+      <c r="E217" s="13"/>
+      <c r="F217" s="13"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>217</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D218" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E218" s="15"/>
-      <c r="F218" s="20"/>
+      <c r="E218" s="13"/>
+      <c r="F218" s="13"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>218</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E219" s="15"/>
-      <c r="F219" s="20"/>
+      <c r="E219" s="13"/>
+      <c r="F219" s="13"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
         <v>219</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D220" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E220" s="15"/>
-      <c r="F220" s="20"/>
+      <c r="E220" s="13"/>
+      <c r="F220" s="13"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>220</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E221" s="15"/>
-      <c r="F221" s="20"/>
+      <c r="E221" s="13"/>
+      <c r="F221" s="13"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>221</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D222" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E222" s="15"/>
-      <c r="F222" s="20"/>
+      <c r="E222" s="13"/>
+      <c r="F222" s="13"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>222</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D223" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E223" s="15"/>
-      <c r="F223" s="20"/>
+      <c r="E223" s="13"/>
+      <c r="F223" s="13"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>223</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D224" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E224" s="15"/>
-      <c r="F224" s="20"/>
+      <c r="E224" s="13"/>
+      <c r="F224" s="13"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>224</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E225" s="15"/>
-      <c r="F225" s="20"/>
+      <c r="E225" s="13"/>
+      <c r="F225" s="13"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>225</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D226" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E226" s="15"/>
-      <c r="F226" s="20"/>
+      <c r="E226" s="13"/>
+      <c r="F226" s="13"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>226</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D227" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E227" s="15"/>
-      <c r="F227" s="20"/>
+      <c r="E227" s="13"/>
+      <c r="F227" s="13"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>227</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D228" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E228" s="15"/>
-      <c r="F228" s="20"/>
+      <c r="E228" s="13"/>
+      <c r="F228" s="13"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>228</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D229" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E229" s="15"/>
-      <c r="F229" s="20"/>
+      <c r="E229" s="13"/>
+      <c r="F229" s="13"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>229</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E230" s="15"/>
-      <c r="F230" s="20"/>
+      <c r="E230" s="13"/>
+      <c r="F230" s="13"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>230</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D231" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E231" s="15"/>
-      <c r="F231" s="20"/>
+      <c r="E231" s="13"/>
+      <c r="F231" s="13"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>231</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D232" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E232" s="15"/>
-      <c r="F232" s="20"/>
+      <c r="E232" s="13"/>
+      <c r="F232" s="13"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>232</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D233" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E233" s="15"/>
-      <c r="F233" s="20"/>
+      <c r="E233" s="13"/>
+      <c r="F233" s="13"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>233</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C234" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D234" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E234" s="15"/>
-      <c r="F234" s="20"/>
+      <c r="E234" s="13"/>
+      <c r="F234" s="13"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>234</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D235" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E235" s="15"/>
-      <c r="F235" s="20"/>
+      <c r="E235" s="13"/>
+      <c r="F235" s="13"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>235</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D236" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E236" s="15"/>
-      <c r="F236" s="20"/>
+      <c r="E236" s="13"/>
+      <c r="F236" s="13"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>236</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D237" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E237" s="15"/>
-      <c r="F237" s="20"/>
+      <c r="E237" s="13"/>
+      <c r="F237" s="13"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>237</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D238" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E238" s="15"/>
-      <c r="F238" s="20"/>
+      <c r="E238" s="13"/>
+      <c r="F238" s="13"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>238</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D239" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E239" s="15"/>
-      <c r="F239" s="20"/>
+      <c r="E239" s="13"/>
+      <c r="F239" s="13"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>239</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C240" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D240" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E240" s="15"/>
-      <c r="F240" s="20"/>
+      <c r="E240" s="13"/>
+      <c r="F240" s="13"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>240</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D241" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E241" s="15"/>
-      <c r="F241" s="20"/>
+      <c r="E241" s="13"/>
+      <c r="F241" s="13"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>241</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D242" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E242" s="15"/>
-      <c r="F242" s="20"/>
+      <c r="E242" s="13"/>
+      <c r="F242" s="13"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>242</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D243" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E243" s="15"/>
-      <c r="F243" s="20"/>
+      <c r="E243" s="13"/>
+      <c r="F243" s="13"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>243</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D244" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E244" s="15"/>
-      <c r="F244" s="20"/>
+      <c r="E244" s="13"/>
+      <c r="F244" s="13"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>244</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D245" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E245" s="15"/>
-      <c r="F245" s="20"/>
+      <c r="E245" s="13"/>
+      <c r="F245" s="13"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>245</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D246" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E246" s="15"/>
-      <c r="F246" s="20"/>
+      <c r="E246" s="13"/>
+      <c r="F246" s="13"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>246</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D247" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E247" s="15"/>
-      <c r="F247" s="20"/>
+      <c r="E247" s="13"/>
+      <c r="F247" s="13"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>247</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D248" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E248" s="15"/>
-      <c r="F248" s="20"/>
+      <c r="E248" s="13"/>
+      <c r="F248" s="13"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>248</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D249" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E249" s="15"/>
-      <c r="F249" s="20"/>
+      <c r="E249" s="13"/>
+      <c r="F249" s="13"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>249</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D250" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E250" s="15"/>
-      <c r="F250" s="20"/>
+      <c r="E250" s="13"/>
+      <c r="F250" s="13"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>250</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D251" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E251" s="15"/>
-      <c r="F251" s="20"/>
+      <c r="E251" s="13"/>
+      <c r="F251" s="13"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>251</v>
       </c>
       <c r="B252" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D252" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E252" s="15"/>
-      <c r="F252" s="20"/>
+      <c r="E252" s="13"/>
+      <c r="F252" s="13"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>252</v>
       </c>
       <c r="B253" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D253" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E253" s="15"/>
-      <c r="F253" s="20"/>
+      <c r="E253" s="13"/>
+      <c r="F253" s="13"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>253</v>
       </c>
       <c r="B254" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D254" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E254" s="15"/>
-      <c r="F254" s="20"/>
+      <c r="E254" s="13"/>
+      <c r="F254" s="13"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>254</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E255" s="15"/>
-      <c r="F255" s="20"/>
+      <c r="E255" s="13"/>
+      <c r="F255" s="13"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>255</v>
       </c>
       <c r="B256" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D256" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E256" s="15"/>
-      <c r="F256" s="20"/>
+      <c r="E256" s="13"/>
+      <c r="F256" s="13"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>256</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D257" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E257" s="15"/>
-      <c r="F257" s="20"/>
+      <c r="E257" s="13"/>
+      <c r="F257" s="13"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>257</v>
       </c>
       <c r="B258" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D258" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E258" s="15"/>
-      <c r="F258" s="20"/>
+      <c r="E258" s="13"/>
+      <c r="F258" s="13"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>258</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D259" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E259" s="15"/>
-      <c r="F259" s="20"/>
+      <c r="E259" s="13"/>
+      <c r="F259" s="13"/>
     </row>
     <row r="260" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>259</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D260" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E260" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="F260" s="20"/>
+      <c r="E260" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="F260" s="13"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>260</v>
       </c>
       <c r="B261" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D261" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E261" s="15"/>
-      <c r="F261" s="20"/>
+      <c r="E261" s="13"/>
+      <c r="F261" s="13"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>261</v>
       </c>
       <c r="B262" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C262" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="C262" s="6" t="s">
-        <v>274</v>
-      </c>
       <c r="D262" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E262" s="15"/>
-      <c r="F262" s="20"/>
+      <c r="E262" s="13"/>
+      <c r="F262" s="13"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>262</v>
       </c>
       <c r="B263" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D263" s="4" t="s">
         <v>103</v>
@@ -6282,10 +6259,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D264" s="4" t="s">
         <v>103</v>
@@ -6298,10 +6275,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -6312,10 +6289,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D266" s="4" t="s">
         <v>103</v>
@@ -6328,10 +6305,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D267" s="4" t="s">
         <v>103</v>
@@ -6344,10 +6321,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -6358,10 +6335,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D269" s="4" t="s">
         <v>103</v>
@@ -6374,10 +6351,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
@@ -6388,10 +6365,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
@@ -6402,16 +6379,16 @@
         <v>271</v>
       </c>
       <c r="B272" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C272" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="D272" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E272" s="4" t="s">
         <v>475</v>
-      </c>
-      <c r="D272" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E272" s="4" t="s">
-        <v>477</v>
       </c>
       <c r="F272" s="4"/>
     </row>
@@ -6420,10 +6397,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
@@ -6434,10 +6411,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
@@ -6448,10 +6425,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
@@ -6462,10 +6439,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
@@ -6476,10 +6453,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D277" s="4" t="s">
         <v>103</v>
@@ -6492,10 +6469,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
@@ -6506,10 +6483,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
@@ -6520,10 +6497,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
@@ -6534,10 +6511,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D281" s="4" t="s">
         <v>103</v>
@@ -6550,10 +6527,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D282" s="4" t="s">
         <v>103</v>
@@ -6566,10 +6543,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
@@ -6580,10 +6557,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
@@ -6594,10 +6571,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
@@ -6608,10 +6585,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
@@ -6622,10 +6599,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
@@ -6636,10 +6613,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
@@ -6650,10 +6627,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
@@ -6664,10 +6641,10 @@
         <v>289</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D290" s="4" t="s">
         <v>103</v>
@@ -6680,10 +6657,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
@@ -6694,10 +6671,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
@@ -6708,10 +6685,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
@@ -6722,10 +6699,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
@@ -6736,10 +6713,10 @@
         <v>294</v>
       </c>
       <c r="B295" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D295" s="4" t="s">
         <v>103</v>
@@ -6752,10 +6729,10 @@
         <v>295</v>
       </c>
       <c r="B296" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
@@ -6766,10 +6743,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
@@ -6780,10 +6757,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D298" s="4" t="s">
         <v>103</v>
@@ -6796,10 +6773,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D299" s="4" t="s">
         <v>103</v>
@@ -6812,10 +6789,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
@@ -6826,10 +6803,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
@@ -6840,10 +6817,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D302" s="4" t="s">
         <v>103</v>
@@ -6856,10 +6833,10 @@
         <v>302</v>
       </c>
       <c r="B303" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D303" s="4" t="s">
         <v>103</v>
@@ -6872,10 +6849,10 @@
         <v>303</v>
       </c>
       <c r="B304" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D304" s="4" t="s">
         <v>103</v>
@@ -6888,10 +6865,10 @@
         <v>304</v>
       </c>
       <c r="B305" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D305" s="4" t="s">
         <v>103</v>
@@ -6904,10 +6881,10 @@
         <v>305</v>
       </c>
       <c r="B306" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D306" s="4" t="s">
         <v>103</v>
@@ -6920,10 +6897,10 @@
         <v>306</v>
       </c>
       <c r="B307" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D307" s="4" t="s">
         <v>103</v>
@@ -6936,10 +6913,10 @@
         <v>307</v>
       </c>
       <c r="B308" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
@@ -6950,10 +6927,10 @@
         <v>308</v>
       </c>
       <c r="B309" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>103</v>
@@ -6966,10 +6943,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>103</v>
@@ -6982,10 +6959,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>103</v>
@@ -6998,10 +6975,10 @@
         <v>311</v>
       </c>
       <c r="B312" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>103</v>
@@ -7014,10 +6991,10 @@
         <v>312</v>
       </c>
       <c r="B313" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
@@ -7028,10 +7005,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>103</v>
@@ -7044,10 +7021,10 @@
         <v>314</v>
       </c>
       <c r="B315" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>103</v>
@@ -7060,10 +7037,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>103</v>
@@ -7076,10 +7053,10 @@
         <v>316</v>
       </c>
       <c r="B317" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>103</v>
@@ -7092,10 +7069,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
@@ -7106,10 +7083,10 @@
         <v>318</v>
       </c>
       <c r="B319" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>103</v>
@@ -7122,10 +7099,10 @@
         <v>319</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
@@ -7136,12 +7113,14 @@
         <v>320</v>
       </c>
       <c r="B321" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D321" s="4"/>
+        <v>474</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E321" s="4"/>
       <c r="F321" s="4"/>
     </row>
@@ -7150,10 +7129,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>103</v>
@@ -7166,10 +7145,10 @@
         <v>322</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>103</v>
@@ -7182,10 +7161,10 @@
         <v>323</v>
       </c>
       <c r="B324" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>103</v>
@@ -7198,10 +7177,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>103</v>
@@ -7214,10 +7193,10 @@
         <v>325</v>
       </c>
       <c r="B326" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -7228,10 +7207,10 @@
         <v>326</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
@@ -7242,10 +7221,10 @@
         <v>327</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>103</v>
@@ -7258,10 +7237,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>103</v>
@@ -7274,10 +7253,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
@@ -7288,10 +7267,10 @@
         <v>330</v>
       </c>
       <c r="B331" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
@@ -7302,10 +7281,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
@@ -7316,10 +7295,10 @@
         <v>332</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>103</v>
@@ -7332,10 +7311,10 @@
         <v>333</v>
       </c>
       <c r="B334" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
@@ -7346,10 +7325,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -7360,10 +7339,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>103</v>
@@ -7376,10 +7355,10 @@
         <v>336</v>
       </c>
       <c r="B337" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>103</v>
@@ -7392,10 +7371,10 @@
         <v>337</v>
       </c>
       <c r="B338" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>103</v>
@@ -7408,10 +7387,10 @@
         <v>338</v>
       </c>
       <c r="B339" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>103</v>
@@ -7424,10 +7403,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>103</v>
@@ -7440,10 +7419,10 @@
         <v>340</v>
       </c>
       <c r="B341" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
@@ -7454,10 +7433,10 @@
         <v>341</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
@@ -7468,10 +7447,10 @@
         <v>342</v>
       </c>
       <c r="B343" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>103</v>
@@ -7484,10 +7463,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>103</v>
@@ -7500,10 +7479,10 @@
         <v>344</v>
       </c>
       <c r="B345" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>103</v>
@@ -7516,10 +7495,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>103</v>
@@ -7532,10 +7511,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C347" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
@@ -7546,10 +7525,10 @@
         <v>347</v>
       </c>
       <c r="B348" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>103</v>
@@ -7562,10 +7541,10 @@
         <v>348</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>103</v>
@@ -7578,10 +7557,10 @@
         <v>349</v>
       </c>
       <c r="B350" s="6" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C350" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>103</v>
@@ -7594,10 +7573,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C351" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
@@ -7608,10 +7587,10 @@
         <v>351</v>
       </c>
       <c r="B352" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C352" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
@@ -7622,10 +7601,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C353" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>103</v>
@@ -7638,10 +7617,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C354" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>103</v>
@@ -7654,10 +7633,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>103</v>
@@ -7670,10 +7649,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C356" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>103</v>
@@ -7686,10 +7665,10 @@
         <v>356</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C357" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>103</v>
@@ -7702,10 +7681,10 @@
         <v>357</v>
       </c>
       <c r="B358" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C358" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>103</v>
@@ -7718,10 +7697,10 @@
         <v>358</v>
       </c>
       <c r="B359" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C359" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>103</v>
@@ -7734,10 +7713,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C360" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>103</v>
@@ -7750,10 +7729,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C361" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>103</v>
@@ -7766,10 +7745,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="6" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C362" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>103</v>
@@ -7782,10 +7761,10 @@
         <v>362</v>
       </c>
       <c r="B363" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C363" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
@@ -7796,10 +7775,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
@@ -7810,10 +7789,10 @@
         <v>364</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>103</v>
@@ -7826,10 +7805,10 @@
         <v>365</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
@@ -7840,10 +7819,10 @@
         <v>366</v>
       </c>
       <c r="B367" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
@@ -7854,10 +7833,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="6" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
@@ -7868,10 +7847,10 @@
         <v>368</v>
       </c>
       <c r="B369" s="6" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
@@ -7882,10 +7861,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
@@ -7896,10 +7875,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="6" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
@@ -7910,10 +7889,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
@@ -7924,10 +7903,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
@@ -7938,10 +7917,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
@@ -7952,10 +7931,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
@@ -7966,10 +7945,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
@@ -7980,10 +7959,10 @@
         <v>376</v>
       </c>
       <c r="B377" s="6" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -7994,10 +7973,10 @@
         <v>377</v>
       </c>
       <c r="B378" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
@@ -8008,10 +7987,10 @@
         <v>378</v>
       </c>
       <c r="B379" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
@@ -8022,10 +8001,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
@@ -8036,10 +8015,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
@@ -8050,10 +8029,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
@@ -8064,10 +8043,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
@@ -8078,10 +8057,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
@@ -8092,10 +8071,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="6" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
@@ -8106,10 +8085,10 @@
         <v>385</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
@@ -8120,10 +8099,10 @@
         <v>386</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
@@ -8134,10 +8113,10 @@
         <v>387</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
@@ -8148,10 +8127,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
@@ -8162,10 +8141,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
@@ -8176,10 +8155,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
@@ -8190,10 +8169,10 @@
         <v>391</v>
       </c>
       <c r="B392" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -8204,10 +8183,10 @@
         <v>392</v>
       </c>
       <c r="B393" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>103</v>
@@ -8220,10 +8199,10 @@
         <v>393</v>
       </c>
       <c r="B394" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -8234,10 +8213,10 @@
         <v>394</v>
       </c>
       <c r="B395" s="6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -8248,10 +8227,10 @@
         <v>395</v>
       </c>
       <c r="B396" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -8262,10 +8241,10 @@
         <v>396</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -8276,10 +8255,10 @@
         <v>397</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -8290,10 +8269,10 @@
         <v>398</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>103</v>
@@ -8306,10 +8285,10 @@
         <v>399</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>103</v>
@@ -8322,10 +8301,10 @@
         <v>400</v>
       </c>
       <c r="B401" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
@@ -8336,10 +8315,10 @@
         <v>401</v>
       </c>
       <c r="B402" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
@@ -8350,10 +8329,10 @@
         <v>402</v>
       </c>
       <c r="B403" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>103</v>
@@ -8366,10 +8345,10 @@
         <v>403</v>
       </c>
       <c r="B404" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>103</v>
@@ -8382,13 +8361,15 @@
         <v>404</v>
       </c>
       <c r="B405" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D405" s="4"/>
-      <c r="E405" s="21"/>
+        <v>474</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E405" s="18"/>
       <c r="F405" s="4"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -8396,12 +8377,14 @@
         <v>405</v>
       </c>
       <c r="B406" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D406" s="4"/>
+        <v>474</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E406" s="4"/>
       <c r="F406" s="4"/>
     </row>
@@ -8410,10 +8393,10 @@
         <v>406</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>103</v>
@@ -8426,10 +8409,10 @@
         <v>407</v>
       </c>
       <c r="B408" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
@@ -8440,10 +8423,10 @@
         <v>408</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
@@ -8454,10 +8437,10 @@
         <v>409</v>
       </c>
       <c r="B410" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>103</v>
@@ -8470,10 +8453,10 @@
         <v>410</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
@@ -8484,10 +8467,10 @@
         <v>411</v>
       </c>
       <c r="B412" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>103</v>
@@ -8500,10 +8483,10 @@
         <v>412</v>
       </c>
       <c r="B413" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
@@ -8514,10 +8497,10 @@
         <v>413</v>
       </c>
       <c r="B414" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>103</v>
@@ -8530,10 +8513,10 @@
         <v>414</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
@@ -8544,12 +8527,14 @@
         <v>415</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D416" s="4"/>
+        <v>474</v>
+      </c>
+      <c r="D416" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E416" s="4"/>
       <c r="F416" s="4"/>
     </row>
@@ -8558,10 +8543,10 @@
         <v>416</v>
       </c>
       <c r="B417" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
@@ -8572,10 +8557,10 @@
         <v>417</v>
       </c>
       <c r="B418" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
@@ -8586,10 +8571,10 @@
         <v>418</v>
       </c>
       <c r="B419" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
@@ -8600,10 +8585,10 @@
         <v>419</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
@@ -8614,10 +8599,10 @@
         <v>420</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
@@ -8628,10 +8613,10 @@
         <v>421</v>
       </c>
       <c r="B422" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
@@ -8642,10 +8627,10 @@
         <v>422</v>
       </c>
       <c r="B423" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
@@ -8656,10 +8641,10 @@
         <v>423</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -8670,10 +8655,10 @@
         <v>424</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
@@ -8684,10 +8669,10 @@
         <v>425</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
@@ -8698,10 +8683,10 @@
         <v>426</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
@@ -8712,10 +8697,10 @@
         <v>427</v>
       </c>
       <c r="B428" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
@@ -8726,10 +8711,10 @@
         <v>428</v>
       </c>
       <c r="B429" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
@@ -8740,10 +8725,10 @@
         <v>429</v>
       </c>
       <c r="B430" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>103</v>
@@ -8756,10 +8741,10 @@
         <v>430</v>
       </c>
       <c r="B431" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -8770,10 +8755,10 @@
         <v>431</v>
       </c>
       <c r="B432" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -8784,10 +8769,10 @@
         <v>432</v>
       </c>
       <c r="B433" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -8798,10 +8783,10 @@
         <v>433</v>
       </c>
       <c r="B434" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
@@ -8812,10 +8797,10 @@
         <v>434</v>
       </c>
       <c r="B435" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -8826,10 +8811,10 @@
         <v>435</v>
       </c>
       <c r="B436" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -8840,10 +8825,10 @@
         <v>436</v>
       </c>
       <c r="B437" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -8854,12 +8839,14 @@
         <v>437</v>
       </c>
       <c r="B438" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C438" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D438" s="4"/>
+        <v>474</v>
+      </c>
+      <c r="D438" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E438" s="4"/>
       <c r="F438" s="4"/>
     </row>
@@ -8868,12 +8855,14 @@
         <v>438</v>
       </c>
       <c r="B439" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C439" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D439" s="4"/>
+        <v>474</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E439" s="4"/>
       <c r="F439" s="4"/>
     </row>
@@ -8882,10 +8871,10 @@
         <v>439</v>
       </c>
       <c r="B440" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C440" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
@@ -8896,10 +8885,10 @@
         <v>440</v>
       </c>
       <c r="B441" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C441" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
@@ -8910,10 +8899,10 @@
         <v>441</v>
       </c>
       <c r="B442" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C442" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
@@ -8924,12 +8913,14 @@
         <v>442</v>
       </c>
       <c r="B443" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C443" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D443" s="4"/>
+        <v>474</v>
+      </c>
+      <c r="D443" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E443" s="4"/>
       <c r="F443" s="4"/>
     </row>
@@ -8938,12 +8929,14 @@
         <v>443</v>
       </c>
       <c r="B444" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C444" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D444" s="4"/>
+        <v>474</v>
+      </c>
+      <c r="D444" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E444" s="4"/>
       <c r="F444" s="4"/>
     </row>
@@ -8952,10 +8945,10 @@
         <v>444</v>
       </c>
       <c r="B445" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C445" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
@@ -8966,10 +8959,10 @@
         <v>445</v>
       </c>
       <c r="B446" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C446" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
@@ -8980,10 +8973,10 @@
         <v>446</v>
       </c>
       <c r="B447" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C447" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
@@ -8994,10 +8987,10 @@
         <v>447</v>
       </c>
       <c r="B448" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C448" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
@@ -9008,10 +9001,10 @@
         <v>448</v>
       </c>
       <c r="B449" s="6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C449" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
@@ -9022,10 +9015,10 @@
         <v>449</v>
       </c>
       <c r="B450" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C450" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
@@ -9036,10 +9029,10 @@
         <v>450</v>
       </c>
       <c r="B451" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C451" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>103</v>
@@ -9052,10 +9045,10 @@
         <v>451</v>
       </c>
       <c r="B452" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C452" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
@@ -9066,12 +9059,14 @@
         <v>452</v>
       </c>
       <c r="B453" s="6" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C453" s="6" t="s">
-        <v>475</v>
-      </c>
-      <c r="D453" s="4"/>
+        <v>474</v>
+      </c>
+      <c r="D453" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E453" s="4"/>
       <c r="F453" s="4"/>
     </row>
@@ -9080,10 +9075,10 @@
         <v>453</v>
       </c>
       <c r="B454" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C454" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
@@ -9094,10 +9089,10 @@
         <v>454</v>
       </c>
       <c r="B455" s="6" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C455" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
@@ -9108,10 +9103,10 @@
         <v>455</v>
       </c>
       <c r="B456" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C456" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
@@ -9122,10 +9117,10 @@
         <v>456</v>
       </c>
       <c r="B457" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>103</v>
@@ -9138,10 +9133,10 @@
         <v>457</v>
       </c>
       <c r="B458" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C458" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>103</v>
@@ -9154,10 +9149,10 @@
         <v>458</v>
       </c>
       <c r="B459" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C459" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>103</v>
@@ -9170,10 +9165,10 @@
         <v>459</v>
       </c>
       <c r="B460" s="6" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
@@ -9184,10 +9179,10 @@
         <v>460</v>
       </c>
       <c r="B461" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
@@ -9198,13 +9193,13 @@
         <v>461</v>
       </c>
       <c r="B462" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C462" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D462" s="4" t="s">
-        <v>476</v>
+        <v>103</v>
       </c>
       <c r="E462" s="4"/>
       <c r="F462" s="4"/>
@@ -9213,156 +9208,171 @@
       <c r="A463" s="4">
         <v>462</v>
       </c>
-      <c r="B463" s="24" t="s">
-        <v>479</v>
-      </c>
-      <c r="C463" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D463" s="25"/>
-      <c r="E463" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F463" s="20"/>
+      <c r="B463" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C463" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D463" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E463" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F463" s="13"/>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
         <v>463</v>
       </c>
-      <c r="B464" s="24" t="s">
-        <v>480</v>
-      </c>
-      <c r="C464" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D464" s="25"/>
-      <c r="E464" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F464" s="20"/>
+      <c r="B464" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="C464" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D464" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E464" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F464" s="13"/>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
         <v>464</v>
       </c>
-      <c r="B465" s="24" t="s">
-        <v>481</v>
-      </c>
-      <c r="C465" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D465" s="25"/>
-      <c r="E465" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F465" s="20"/>
+      <c r="B465" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="C465" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D465" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E465" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F465" s="13"/>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
         <v>465</v>
       </c>
-      <c r="B466" s="24" t="s">
-        <v>482</v>
-      </c>
-      <c r="C466" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D466" s="25"/>
-      <c r="E466" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F466" s="20"/>
+      <c r="B466" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="C466" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D466" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E466" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F466" s="13"/>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
         <v>466</v>
       </c>
-      <c r="B467" s="24" t="s">
-        <v>483</v>
-      </c>
-      <c r="C467" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D467" s="25"/>
-      <c r="E467" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F467" s="20"/>
+      <c r="B467" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C467" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D467" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E467" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F467" s="13"/>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="4">
         <v>467</v>
       </c>
-      <c r="B468" s="24" t="s">
-        <v>484</v>
-      </c>
-      <c r="C468" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D468" s="25"/>
-      <c r="E468" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F468" s="20"/>
+      <c r="B468" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="C468" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D468" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E468" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F468" s="13"/>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
         <v>468</v>
       </c>
-      <c r="B469" s="24" t="s">
+      <c r="B469" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C469" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="C469" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D469" s="25"/>
-      <c r="E469" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F469" s="20"/>
+      <c r="D469" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E469" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F469" s="13"/>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="4">
         <v>469</v>
       </c>
-      <c r="B470" s="24" t="s">
+      <c r="B470" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="C470" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D470" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E470" s="13" t="s">
         <v>486</v>
       </c>
-      <c r="C470" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D470" s="25"/>
-      <c r="E470" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F470" s="20"/>
+      <c r="F470" s="13"/>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
         <v>470</v>
       </c>
-      <c r="B471" s="24" t="s">
-        <v>487</v>
-      </c>
-      <c r="C471" s="24" t="s">
-        <v>488</v>
-      </c>
-      <c r="D471" s="25"/>
-      <c r="E471" s="15" t="s">
-        <v>489</v>
-      </c>
-      <c r="F471" s="20"/>
+      <c r="B471" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="C471" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D471" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E471" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="F471" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E471" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>
-  <conditionalFormatting sqref="E272">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576 B1:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5 B1:B1048576 G1:G1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06DBB788-4138-4F7C-B9D0-B8EFA3C6BEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6AAEB7-5729-49F6-97E6-46708D01C773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6AAEB7-5729-49F6-97E6-46708D01C773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0933C2B1-0852-4E30-80AC-BB7F12982E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0933C2B1-0852-4E30-80AC-BB7F12982E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370980F6-D391-4948-A73F-EFE2A1A253D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="492">
   <si>
     <t>STT</t>
   </si>
@@ -1596,7 +1596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1628,9 +1628,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1644,12 +1641,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1659,6 +1650,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1998,11 +1990,11 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="10" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" style="22" customWidth="1"/>
-    <col min="3" max="3" width="15" style="22" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="15" style="19" customWidth="1"/>
     <col min="4" max="4" width="22.7109375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="30.42578125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" style="12" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="29.7109375" style="11" customWidth="1"/>
     <col min="7" max="7" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2019,7 +2011,7 @@
       <c r="D1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>192</v>
       </c>
     </row>
@@ -2036,8 +2028,10 @@
       <c r="D2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="21"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="18" t="s">
+        <v>401</v>
+      </c>
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2053,8 +2047,10 @@
       <c r="D3" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="21"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="18" t="s">
+        <v>394</v>
+      </c>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2070,8 +2066,10 @@
       <c r="D4" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="21"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="18" t="s">
+        <v>420</v>
+      </c>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2087,8 +2085,10 @@
       <c r="D5" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="21"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="18" t="s">
+        <v>432</v>
+      </c>
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2104,8 +2104,10 @@
       <c r="D6" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="21"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="18" t="s">
+        <v>378</v>
+      </c>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2121,8 +2123,10 @@
       <c r="D7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="21"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="18" t="s">
+        <v>406</v>
+      </c>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2138,8 +2142,10 @@
       <c r="D8" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="21"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="18" t="s">
+        <v>379</v>
+      </c>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2155,8 +2161,10 @@
       <c r="D9" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="21"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="18" t="s">
+        <v>464</v>
+      </c>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2172,8 +2180,10 @@
       <c r="D10" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="21"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="18" t="s">
+        <v>443</v>
+      </c>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2189,8 +2199,10 @@
       <c r="D11" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="21"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="18" t="s">
+        <v>398</v>
+      </c>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2206,8 +2218,10 @@
       <c r="D12" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="21"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="18" t="s">
+        <v>396</v>
+      </c>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2223,8 +2237,10 @@
       <c r="D13" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="21"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="18" t="s">
+        <v>439</v>
+      </c>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2240,10 +2256,12 @@
       <c r="D14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="F14" s="21"/>
+      <c r="F14" s="18" t="s">
+        <v>389</v>
+      </c>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2259,8 +2277,10 @@
       <c r="D15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="21"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="18" t="s">
+        <v>472</v>
+      </c>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2276,8 +2296,10 @@
       <c r="D16" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="21"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="18" t="s">
+        <v>447</v>
+      </c>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2293,8 +2315,10 @@
       <c r="D17" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="21"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="18" t="s">
+        <v>461</v>
+      </c>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2310,8 +2334,10 @@
       <c r="D18" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="21"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="18" t="s">
+        <v>473</v>
+      </c>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2327,8 +2353,10 @@
       <c r="D19" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="21"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="18" t="s">
+        <v>423</v>
+      </c>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2344,8 +2372,10 @@
       <c r="D20" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="21"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="18" t="s">
+        <v>376</v>
+      </c>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2361,8 +2391,10 @@
       <c r="D21" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="21"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="18" t="s">
+        <v>449</v>
+      </c>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2378,8 +2410,10 @@
       <c r="D22" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="20"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="21" t="s">
+        <v>410</v>
+      </c>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2395,8 +2429,10 @@
       <c r="D23" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="20"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="21" t="s">
+        <v>466</v>
+      </c>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2412,8 +2448,10 @@
       <c r="D24" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="20"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="21" t="s">
+        <v>390</v>
+      </c>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2429,8 +2467,10 @@
       <c r="D25" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="20"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="21" t="s">
+        <v>457</v>
+      </c>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2446,8 +2486,10 @@
       <c r="D26" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="20"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="21" t="s">
+        <v>382</v>
+      </c>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2463,8 +2505,10 @@
       <c r="D27" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="20"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="21" t="s">
+        <v>183</v>
+      </c>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2480,8 +2524,10 @@
       <c r="D28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="20"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="21" t="s">
+        <v>459</v>
+      </c>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2497,8 +2543,10 @@
       <c r="D29" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="20"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="21" t="s">
+        <v>393</v>
+      </c>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2514,8 +2562,10 @@
       <c r="D30" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="20"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="21" t="s">
+        <v>399</v>
+      </c>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2531,8 +2581,10 @@
       <c r="D31" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="20"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="21" t="s">
+        <v>402</v>
+      </c>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2548,8 +2600,10 @@
       <c r="D32" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="20"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="21" t="s">
+        <v>384</v>
+      </c>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2565,8 +2619,10 @@
       <c r="D33" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="20"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="21" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -2581,8 +2637,10 @@
       <c r="D34" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="20"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="21" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -2597,8 +2655,10 @@
       <c r="D35" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="20"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="21" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -2613,8 +2673,10 @@
       <c r="D36" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="20"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="21" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -2629,8 +2691,10 @@
       <c r="D37" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="20"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="21" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -2645,8 +2709,10 @@
       <c r="D38" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="20"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="21" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
@@ -2661,8 +2727,10 @@
       <c r="D39" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="20"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="21" t="s">
+        <v>383</v>
+      </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
@@ -2677,8 +2745,10 @@
       <c r="D40" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="19"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="21" t="s">
+        <v>375</v>
+      </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
@@ -2693,8 +2763,10 @@
       <c r="D41" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="19"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="21" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
@@ -2709,8 +2781,10 @@
       <c r="D42" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="21" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
@@ -2725,8 +2799,10 @@
       <c r="D43" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="21" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
@@ -2741,8 +2817,10 @@
       <c r="D44" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="21" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
@@ -2757,8 +2835,10 @@
       <c r="D45" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="21" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
@@ -2773,8 +2853,10 @@
       <c r="D46" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="21" t="s">
+        <v>404</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
@@ -2789,8 +2871,10 @@
       <c r="D47" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="21" t="s">
+        <v>385</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
@@ -2805,8 +2889,10 @@
       <c r="D48" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="21" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
@@ -2821,8 +2907,10 @@
       <c r="D49" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="21" t="s">
+        <v>392</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
@@ -2837,8 +2925,10 @@
       <c r="D50" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="21" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
@@ -2853,8 +2943,10 @@
       <c r="D51" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="21" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
@@ -2869,8 +2961,8 @@
       <c r="D52" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
@@ -2885,8 +2977,8 @@
       <c r="D53" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
@@ -2901,8 +2993,8 @@
       <c r="D54" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
@@ -2917,8 +3009,8 @@
       <c r="D55" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
@@ -2933,8 +3025,8 @@
       <c r="D56" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
@@ -2949,8 +3041,8 @@
       <c r="D57" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
@@ -2965,8 +3057,8 @@
       <c r="D58" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
@@ -2981,8 +3073,8 @@
       <c r="D59" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
@@ -2997,8 +3089,8 @@
       <c r="D60" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
@@ -3013,8 +3105,8 @@
       <c r="D61" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
@@ -3029,8 +3121,8 @@
       <c r="D62" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
@@ -3045,8 +3137,8 @@
       <c r="D63" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
@@ -3061,8 +3153,8 @@
       <c r="D64" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
@@ -3077,8 +3169,8 @@
       <c r="D65" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
@@ -3093,8 +3185,8 @@
       <c r="D66" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
@@ -3109,8 +3201,8 @@
       <c r="D67" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
@@ -3125,8 +3217,8 @@
       <c r="D68" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
@@ -3141,8 +3233,8 @@
       <c r="D69" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
@@ -3157,8 +3249,8 @@
       <c r="D70" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
@@ -3173,8 +3265,8 @@
       <c r="D71" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
@@ -3189,8 +3281,8 @@
       <c r="D72" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
@@ -3205,8 +3297,8 @@
       <c r="D73" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
@@ -3221,8 +3313,8 @@
       <c r="D74" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
@@ -3237,8 +3329,8 @@
       <c r="D75" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="4">
@@ -3253,8 +3345,8 @@
       <c r="D76" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
@@ -3269,8 +3361,8 @@
       <c r="D77" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
@@ -3285,8 +3377,8 @@
       <c r="D78" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
@@ -3301,8 +3393,8 @@
       <c r="D79" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
@@ -3317,8 +3409,8 @@
       <c r="D80" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
@@ -3333,8 +3425,8 @@
       <c r="D81" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
@@ -3349,8 +3441,8 @@
       <c r="D82" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
@@ -3365,8 +3457,8 @@
       <c r="D83" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
@@ -3381,8 +3473,8 @@
       <c r="D84" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
@@ -3397,8 +3489,8 @@
       <c r="D85" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
@@ -3413,8 +3505,8 @@
       <c r="D86" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
@@ -3429,8 +3521,8 @@
       <c r="D87" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
@@ -3445,8 +3537,8 @@
       <c r="D88" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="4">
@@ -3461,8 +3553,8 @@
       <c r="D89" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
@@ -3477,8 +3569,8 @@
       <c r="D90" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
@@ -3493,8 +3585,8 @@
       <c r="D91" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
@@ -3509,8 +3601,8 @@
       <c r="D92" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
@@ -3525,8 +3617,8 @@
       <c r="D93" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
@@ -3541,8 +3633,8 @@
       <c r="D94" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
@@ -3557,8 +3649,8 @@
       <c r="D95" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
@@ -3573,8 +3665,8 @@
       <c r="D96" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
@@ -3589,8 +3681,8 @@
       <c r="D97" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
@@ -3605,8 +3697,8 @@
       <c r="D98" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
@@ -3621,8 +3713,8 @@
       <c r="D99" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
@@ -3637,8 +3729,8 @@
       <c r="D100" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
@@ -3653,8 +3745,8 @@
       <c r="D101" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
@@ -3669,8 +3761,8 @@
       <c r="D102" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="12"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
@@ -3685,8 +3777,8 @@
       <c r="D103" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
@@ -3701,8 +3793,8 @@
       <c r="D104" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="12"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
@@ -3717,8 +3809,8 @@
       <c r="D105" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E105" s="13"/>
-      <c r="F105" s="13"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="12"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
@@ -3733,8 +3825,8 @@
       <c r="D106" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
@@ -3749,8 +3841,8 @@
       <c r="D107" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="12"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
@@ -3765,8 +3857,8 @@
       <c r="D108" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
@@ -3781,8 +3873,8 @@
       <c r="D109" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E109" s="13"/>
-      <c r="F109" s="13"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="12"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
@@ -3797,8 +3889,8 @@
       <c r="D110" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E110" s="13"/>
-      <c r="F110" s="13"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="12"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
@@ -3813,8 +3905,8 @@
       <c r="D111" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E111" s="13"/>
-      <c r="F111" s="13"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="12"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
@@ -3829,8 +3921,8 @@
       <c r="D112" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="12"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
@@ -3845,8 +3937,8 @@
       <c r="D113" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="12"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
@@ -3861,8 +3953,8 @@
       <c r="D114" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="12"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
@@ -3877,8 +3969,8 @@
       <c r="D115" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E115" s="13"/>
-      <c r="F115" s="13"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
@@ -3893,8 +3985,8 @@
       <c r="D116" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E116" s="13"/>
-      <c r="F116" s="13"/>
+      <c r="E116" s="12"/>
+      <c r="F116" s="12"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
@@ -3909,8 +4001,8 @@
       <c r="D117" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E117" s="13"/>
-      <c r="F117" s="13"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
@@ -3925,8 +4017,8 @@
       <c r="D118" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E118" s="13"/>
-      <c r="F118" s="13"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
@@ -3941,8 +4033,8 @@
       <c r="D119" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E119" s="13"/>
-      <c r="F119" s="13"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
@@ -3957,8 +4049,8 @@
       <c r="D120" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
@@ -3973,8 +4065,8 @@
       <c r="D121" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E121" s="13"/>
-      <c r="F121" s="13"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
@@ -3989,8 +4081,8 @@
       <c r="D122" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
@@ -4005,8 +4097,8 @@
       <c r="D123" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E123" s="13"/>
-      <c r="F123" s="13"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
@@ -4021,8 +4113,8 @@
       <c r="D124" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E124" s="13"/>
-      <c r="F124" s="13"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
@@ -4034,11 +4126,11 @@
       <c r="C125" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D125" s="16" t="s">
+      <c r="D125" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="E125" s="13"/>
-      <c r="F125" s="13"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
     </row>
     <row r="126" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
@@ -4053,10 +4145,10 @@
       <c r="D126" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E126" s="15" t="s">
+      <c r="E126" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="F126" s="13"/>
+      <c r="F126" s="12"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
@@ -4071,8 +4163,8 @@
       <c r="D127" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E127" s="13"/>
-      <c r="F127" s="13"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
@@ -4087,8 +4179,8 @@
       <c r="D128" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E128" s="13"/>
-      <c r="F128" s="13"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="12"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
@@ -4103,8 +4195,8 @@
       <c r="D129" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E129" s="13"/>
-      <c r="F129" s="13"/>
+      <c r="E129" s="12"/>
+      <c r="F129" s="12"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
@@ -4119,8 +4211,8 @@
       <c r="D130" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E130" s="13"/>
-      <c r="F130" s="13"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
@@ -4135,8 +4227,8 @@
       <c r="D131" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E131" s="13"/>
-      <c r="F131" s="13"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
@@ -4151,8 +4243,8 @@
       <c r="D132" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E132" s="13"/>
-      <c r="F132" s="13"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
@@ -4167,8 +4259,8 @@
       <c r="D133" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E133" s="13"/>
-      <c r="F133" s="13"/>
+      <c r="E133" s="12"/>
+      <c r="F133" s="12"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
@@ -4183,8 +4275,8 @@
       <c r="D134" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E134" s="13"/>
-      <c r="F134" s="13"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="12"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
@@ -4199,8 +4291,8 @@
       <c r="D135" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E135" s="13"/>
-      <c r="F135" s="13"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="12"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
@@ -4215,8 +4307,8 @@
       <c r="D136" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E136" s="13"/>
-      <c r="F136" s="13"/>
+      <c r="E136" s="12"/>
+      <c r="F136" s="12"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
@@ -4231,8 +4323,8 @@
       <c r="D137" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E137" s="13"/>
-      <c r="F137" s="13"/>
+      <c r="E137" s="12"/>
+      <c r="F137" s="12"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
@@ -4247,8 +4339,8 @@
       <c r="D138" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E138" s="13"/>
-      <c r="F138" s="13"/>
+      <c r="E138" s="12"/>
+      <c r="F138" s="12"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="4">
@@ -4263,8 +4355,8 @@
       <c r="D139" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E139" s="13"/>
-      <c r="F139" s="13"/>
+      <c r="E139" s="12"/>
+      <c r="F139" s="12"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="4">
@@ -4279,8 +4371,8 @@
       <c r="D140" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E140" s="13"/>
-      <c r="F140" s="13"/>
+      <c r="E140" s="12"/>
+      <c r="F140" s="12"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="4">
@@ -4295,8 +4387,8 @@
       <c r="D141" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E141" s="13"/>
-      <c r="F141" s="13"/>
+      <c r="E141" s="12"/>
+      <c r="F141" s="12"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="4">
@@ -4311,8 +4403,8 @@
       <c r="D142" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E142" s="13"/>
-      <c r="F142" s="13"/>
+      <c r="E142" s="12"/>
+      <c r="F142" s="12"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="4">
@@ -4327,8 +4419,8 @@
       <c r="D143" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E143" s="13"/>
-      <c r="F143" s="13"/>
+      <c r="E143" s="12"/>
+      <c r="F143" s="12"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="4">
@@ -4343,8 +4435,8 @@
       <c r="D144" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E144" s="13"/>
-      <c r="F144" s="13"/>
+      <c r="E144" s="12"/>
+      <c r="F144" s="12"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="4">
@@ -4359,8 +4451,8 @@
       <c r="D145" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E145" s="13"/>
-      <c r="F145" s="13"/>
+      <c r="E145" s="12"/>
+      <c r="F145" s="12"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="4">
@@ -4375,8 +4467,8 @@
       <c r="D146" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E146" s="13"/>
-      <c r="F146" s="13"/>
+      <c r="E146" s="12"/>
+      <c r="F146" s="12"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
@@ -4391,8 +4483,8 @@
       <c r="D147" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E147" s="13"/>
-      <c r="F147" s="13"/>
+      <c r="E147" s="12"/>
+      <c r="F147" s="12"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
@@ -4407,8 +4499,8 @@
       <c r="D148" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E148" s="13"/>
-      <c r="F148" s="13"/>
+      <c r="E148" s="12"/>
+      <c r="F148" s="12"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
@@ -4423,8 +4515,8 @@
       <c r="D149" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E149" s="13"/>
-      <c r="F149" s="13"/>
+      <c r="E149" s="12"/>
+      <c r="F149" s="12"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
@@ -4439,8 +4531,8 @@
       <c r="D150" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E150" s="13"/>
-      <c r="F150" s="13"/>
+      <c r="E150" s="12"/>
+      <c r="F150" s="12"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
@@ -4455,8 +4547,8 @@
       <c r="D151" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E151" s="13"/>
-      <c r="F151" s="13"/>
+      <c r="E151" s="12"/>
+      <c r="F151" s="12"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
@@ -4471,8 +4563,8 @@
       <c r="D152" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E152" s="13"/>
-      <c r="F152" s="13"/>
+      <c r="E152" s="12"/>
+      <c r="F152" s="12"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="4">
@@ -4487,8 +4579,8 @@
       <c r="D153" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E153" s="13"/>
-      <c r="F153" s="13"/>
+      <c r="E153" s="12"/>
+      <c r="F153" s="12"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
@@ -4503,8 +4595,8 @@
       <c r="D154" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E154" s="13"/>
-      <c r="F154" s="13"/>
+      <c r="E154" s="12"/>
+      <c r="F154" s="12"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
@@ -4519,8 +4611,8 @@
       <c r="D155" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E155" s="13"/>
-      <c r="F155" s="13"/>
+      <c r="E155" s="12"/>
+      <c r="F155" s="12"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
@@ -4535,8 +4627,8 @@
       <c r="D156" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E156" s="13"/>
-      <c r="F156" s="13"/>
+      <c r="E156" s="12"/>
+      <c r="F156" s="12"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
@@ -4551,8 +4643,8 @@
       <c r="D157" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E157" s="13"/>
-      <c r="F157" s="13"/>
+      <c r="E157" s="12"/>
+      <c r="F157" s="12"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
@@ -4567,8 +4659,8 @@
       <c r="D158" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E158" s="13"/>
-      <c r="F158" s="13"/>
+      <c r="E158" s="12"/>
+      <c r="F158" s="12"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
@@ -4583,8 +4675,8 @@
       <c r="D159" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E159" s="13"/>
-      <c r="F159" s="13"/>
+      <c r="E159" s="12"/>
+      <c r="F159" s="12"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
@@ -4599,8 +4691,8 @@
       <c r="D160" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E160" s="13"/>
-      <c r="F160" s="13"/>
+      <c r="E160" s="12"/>
+      <c r="F160" s="12"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
@@ -4615,8 +4707,8 @@
       <c r="D161" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E161" s="13"/>
-      <c r="F161" s="13"/>
+      <c r="E161" s="12"/>
+      <c r="F161" s="12"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
@@ -4631,8 +4723,8 @@
       <c r="D162" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E162" s="13"/>
-      <c r="F162" s="13"/>
+      <c r="E162" s="12"/>
+      <c r="F162" s="12"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
@@ -4647,8 +4739,8 @@
       <c r="D163" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E163" s="13"/>
-      <c r="F163" s="13"/>
+      <c r="E163" s="12"/>
+      <c r="F163" s="12"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
@@ -4663,8 +4755,8 @@
       <c r="D164" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E164" s="13"/>
-      <c r="F164" s="13"/>
+      <c r="E164" s="12"/>
+      <c r="F164" s="12"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
@@ -4679,8 +4771,8 @@
       <c r="D165" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E165" s="13"/>
-      <c r="F165" s="13"/>
+      <c r="E165" s="12"/>
+      <c r="F165" s="12"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
@@ -4695,8 +4787,8 @@
       <c r="D166" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E166" s="13"/>
-      <c r="F166" s="13"/>
+      <c r="E166" s="12"/>
+      <c r="F166" s="12"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
@@ -4711,8 +4803,8 @@
       <c r="D167" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E167" s="13"/>
-      <c r="F167" s="13"/>
+      <c r="E167" s="12"/>
+      <c r="F167" s="12"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
@@ -4727,8 +4819,8 @@
       <c r="D168" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E168" s="13"/>
-      <c r="F168" s="13"/>
+      <c r="E168" s="12"/>
+      <c r="F168" s="12"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
@@ -4743,8 +4835,8 @@
       <c r="D169" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E169" s="13"/>
-      <c r="F169" s="13"/>
+      <c r="E169" s="12"/>
+      <c r="F169" s="12"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
@@ -4759,8 +4851,8 @@
       <c r="D170" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E170" s="13"/>
-      <c r="F170" s="13"/>
+      <c r="E170" s="12"/>
+      <c r="F170" s="12"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
@@ -4775,8 +4867,8 @@
       <c r="D171" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E171" s="13"/>
-      <c r="F171" s="13"/>
+      <c r="E171" s="12"/>
+      <c r="F171" s="12"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
@@ -4791,8 +4883,8 @@
       <c r="D172" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E172" s="13"/>
-      <c r="F172" s="13"/>
+      <c r="E172" s="12"/>
+      <c r="F172" s="12"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
@@ -4807,8 +4899,8 @@
       <c r="D173" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E173" s="13"/>
-      <c r="F173" s="13"/>
+      <c r="E173" s="12"/>
+      <c r="F173" s="12"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
@@ -4823,8 +4915,8 @@
       <c r="D174" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E174" s="13"/>
-      <c r="F174" s="13"/>
+      <c r="E174" s="12"/>
+      <c r="F174" s="12"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
@@ -4839,8 +4931,8 @@
       <c r="D175" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E175" s="13"/>
-      <c r="F175" s="13"/>
+      <c r="E175" s="12"/>
+      <c r="F175" s="12"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
@@ -4855,8 +4947,8 @@
       <c r="D176" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E176" s="13"/>
-      <c r="F176" s="13"/>
+      <c r="E176" s="12"/>
+      <c r="F176" s="12"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
@@ -4871,8 +4963,8 @@
       <c r="D177" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E177" s="13"/>
-      <c r="F177" s="13"/>
+      <c r="E177" s="12"/>
+      <c r="F177" s="12"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
@@ -4887,8 +4979,8 @@
       <c r="D178" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E178" s="13"/>
-      <c r="F178" s="13"/>
+      <c r="E178" s="12"/>
+      <c r="F178" s="12"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
@@ -4903,8 +4995,8 @@
       <c r="D179" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E179" s="13"/>
-      <c r="F179" s="13"/>
+      <c r="E179" s="12"/>
+      <c r="F179" s="12"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
@@ -4919,8 +5011,8 @@
       <c r="D180" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E180" s="13"/>
-      <c r="F180" s="13"/>
+      <c r="E180" s="12"/>
+      <c r="F180" s="12"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
@@ -4932,9 +5024,11 @@
       <c r="C181" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D181" s="11"/>
-      <c r="E181" s="18"/>
-      <c r="F181" s="13"/>
+      <c r="D181" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E181" s="17"/>
+      <c r="F181" s="12"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
@@ -4949,8 +5043,8 @@
       <c r="D182" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E182" s="13"/>
-      <c r="F182" s="13"/>
+      <c r="E182" s="12"/>
+      <c r="F182" s="12"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
@@ -4965,8 +5059,8 @@
       <c r="D183" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E183" s="13"/>
-      <c r="F183" s="13"/>
+      <c r="E183" s="12"/>
+      <c r="F183" s="12"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
@@ -4981,8 +5075,8 @@
       <c r="D184" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E184" s="13"/>
-      <c r="F184" s="13"/>
+      <c r="E184" s="12"/>
+      <c r="F184" s="12"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
@@ -4997,8 +5091,8 @@
       <c r="D185" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E185" s="13"/>
-      <c r="F185" s="13"/>
+      <c r="E185" s="12"/>
+      <c r="F185" s="12"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
@@ -5013,8 +5107,8 @@
       <c r="D186" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E186" s="13"/>
-      <c r="F186" s="13"/>
+      <c r="E186" s="12"/>
+      <c r="F186" s="12"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
@@ -5029,8 +5123,8 @@
       <c r="D187" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E187" s="13"/>
-      <c r="F187" s="13"/>
+      <c r="E187" s="12"/>
+      <c r="F187" s="12"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
@@ -5045,8 +5139,8 @@
       <c r="D188" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E188" s="13"/>
-      <c r="F188" s="13"/>
+      <c r="E188" s="12"/>
+      <c r="F188" s="12"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
@@ -5061,8 +5155,8 @@
       <c r="D189" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E189" s="13"/>
-      <c r="F189" s="13"/>
+      <c r="E189" s="12"/>
+      <c r="F189" s="12"/>
     </row>
     <row r="190" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
@@ -5077,10 +5171,10 @@
       <c r="D190" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E190" s="15" t="s">
+      <c r="E190" s="14" t="s">
         <v>489</v>
       </c>
-      <c r="F190" s="23" t="s">
+      <c r="F190" s="20" t="s">
         <v>476</v>
       </c>
     </row>
@@ -5097,8 +5191,8 @@
       <c r="D191" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E191" s="13"/>
-      <c r="F191" s="13"/>
+      <c r="E191" s="12"/>
+      <c r="F191" s="12"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
@@ -5113,8 +5207,8 @@
       <c r="D192" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E192" s="13"/>
-      <c r="F192" s="13"/>
+      <c r="E192" s="12"/>
+      <c r="F192" s="12"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
@@ -5129,8 +5223,8 @@
       <c r="D193" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E193" s="13"/>
-      <c r="F193" s="13"/>
+      <c r="E193" s="12"/>
+      <c r="F193" s="12"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
@@ -5145,8 +5239,8 @@
       <c r="D194" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E194" s="13"/>
-      <c r="F194" s="13"/>
+      <c r="E194" s="12"/>
+      <c r="F194" s="12"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
@@ -5161,8 +5255,8 @@
       <c r="D195" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E195" s="13"/>
-      <c r="F195" s="13"/>
+      <c r="E195" s="12"/>
+      <c r="F195" s="12"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
@@ -5177,8 +5271,8 @@
       <c r="D196" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E196" s="13"/>
-      <c r="F196" s="13"/>
+      <c r="E196" s="12"/>
+      <c r="F196" s="12"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
@@ -5193,8 +5287,8 @@
       <c r="D197" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E197" s="13"/>
-      <c r="F197" s="13"/>
+      <c r="E197" s="12"/>
+      <c r="F197" s="12"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
@@ -5209,8 +5303,8 @@
       <c r="D198" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E198" s="13"/>
-      <c r="F198" s="13"/>
+      <c r="E198" s="12"/>
+      <c r="F198" s="12"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
@@ -5225,8 +5319,8 @@
       <c r="D199" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E199" s="13"/>
-      <c r="F199" s="13"/>
+      <c r="E199" s="12"/>
+      <c r="F199" s="12"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
@@ -5241,8 +5335,8 @@
       <c r="D200" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E200" s="13"/>
-      <c r="F200" s="13"/>
+      <c r="E200" s="12"/>
+      <c r="F200" s="12"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
@@ -5257,8 +5351,8 @@
       <c r="D201" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E201" s="13"/>
-      <c r="F201" s="13"/>
+      <c r="E201" s="12"/>
+      <c r="F201" s="12"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
@@ -5273,8 +5367,8 @@
       <c r="D202" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E202" s="13"/>
-      <c r="F202" s="13"/>
+      <c r="E202" s="12"/>
+      <c r="F202" s="12"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="4">
@@ -5289,8 +5383,8 @@
       <c r="D203" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E203" s="13"/>
-      <c r="F203" s="13"/>
+      <c r="E203" s="12"/>
+      <c r="F203" s="12"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="4">
@@ -5305,8 +5399,8 @@
       <c r="D204" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E204" s="13"/>
-      <c r="F204" s="13"/>
+      <c r="E204" s="12"/>
+      <c r="F204" s="12"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="4">
@@ -5321,8 +5415,8 @@
       <c r="D205" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E205" s="13"/>
-      <c r="F205" s="13"/>
+      <c r="E205" s="12"/>
+      <c r="F205" s="12"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="4">
@@ -5337,8 +5431,8 @@
       <c r="D206" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E206" s="13"/>
-      <c r="F206" s="13"/>
+      <c r="E206" s="12"/>
+      <c r="F206" s="12"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="4">
@@ -5353,8 +5447,8 @@
       <c r="D207" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E207" s="13"/>
-      <c r="F207" s="13"/>
+      <c r="E207" s="12"/>
+      <c r="F207" s="12"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="4">
@@ -5369,8 +5463,8 @@
       <c r="D208" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E208" s="13"/>
-      <c r="F208" s="13"/>
+      <c r="E208" s="12"/>
+      <c r="F208" s="12"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="4">
@@ -5385,8 +5479,8 @@
       <c r="D209" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E209" s="13"/>
-      <c r="F209" s="13"/>
+      <c r="E209" s="12"/>
+      <c r="F209" s="12"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="4">
@@ -5401,8 +5495,8 @@
       <c r="D210" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E210" s="13"/>
-      <c r="F210" s="13"/>
+      <c r="E210" s="12"/>
+      <c r="F210" s="12"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="4">
@@ -5417,8 +5511,8 @@
       <c r="D211" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E211" s="13"/>
-      <c r="F211" s="13"/>
+      <c r="E211" s="12"/>
+      <c r="F211" s="12"/>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="4">
@@ -5433,8 +5527,8 @@
       <c r="D212" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E212" s="13"/>
-      <c r="F212" s="13"/>
+      <c r="E212" s="12"/>
+      <c r="F212" s="12"/>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="4">
@@ -5449,8 +5543,8 @@
       <c r="D213" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E213" s="13"/>
-      <c r="F213" s="13"/>
+      <c r="E213" s="12"/>
+      <c r="F213" s="12"/>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
@@ -5465,8 +5559,8 @@
       <c r="D214" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E214" s="13"/>
-      <c r="F214" s="13"/>
+      <c r="E214" s="12"/>
+      <c r="F214" s="12"/>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
@@ -5481,8 +5575,8 @@
       <c r="D215" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E215" s="13"/>
-      <c r="F215" s="13"/>
+      <c r="E215" s="12"/>
+      <c r="F215" s="12"/>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
@@ -5497,8 +5591,8 @@
       <c r="D216" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E216" s="13"/>
-      <c r="F216" s="13"/>
+      <c r="E216" s="12"/>
+      <c r="F216" s="12"/>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
@@ -5513,8 +5607,8 @@
       <c r="D217" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E217" s="13"/>
-      <c r="F217" s="13"/>
+      <c r="E217" s="12"/>
+      <c r="F217" s="12"/>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
@@ -5529,8 +5623,8 @@
       <c r="D218" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E218" s="13"/>
-      <c r="F218" s="13"/>
+      <c r="E218" s="12"/>
+      <c r="F218" s="12"/>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
@@ -5545,8 +5639,8 @@
       <c r="D219" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E219" s="13"/>
-      <c r="F219" s="13"/>
+      <c r="E219" s="12"/>
+      <c r="F219" s="12"/>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="4">
@@ -5561,8 +5655,8 @@
       <c r="D220" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E220" s="13"/>
-      <c r="F220" s="13"/>
+      <c r="E220" s="12"/>
+      <c r="F220" s="12"/>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
@@ -5577,8 +5671,8 @@
       <c r="D221" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E221" s="13"/>
-      <c r="F221" s="13"/>
+      <c r="E221" s="12"/>
+      <c r="F221" s="12"/>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
@@ -5593,8 +5687,8 @@
       <c r="D222" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E222" s="13"/>
-      <c r="F222" s="13"/>
+      <c r="E222" s="12"/>
+      <c r="F222" s="12"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
@@ -5609,8 +5703,8 @@
       <c r="D223" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E223" s="13"/>
-      <c r="F223" s="13"/>
+      <c r="E223" s="12"/>
+      <c r="F223" s="12"/>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
@@ -5625,8 +5719,8 @@
       <c r="D224" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E224" s="13"/>
-      <c r="F224" s="13"/>
+      <c r="E224" s="12"/>
+      <c r="F224" s="12"/>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
@@ -5641,8 +5735,8 @@
       <c r="D225" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E225" s="13"/>
-      <c r="F225" s="13"/>
+      <c r="E225" s="12"/>
+      <c r="F225" s="12"/>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
@@ -5657,8 +5751,8 @@
       <c r="D226" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E226" s="13"/>
-      <c r="F226" s="13"/>
+      <c r="E226" s="12"/>
+      <c r="F226" s="12"/>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
@@ -5673,8 +5767,8 @@
       <c r="D227" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E227" s="13"/>
-      <c r="F227" s="13"/>
+      <c r="E227" s="12"/>
+      <c r="F227" s="12"/>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
@@ -5689,8 +5783,8 @@
       <c r="D228" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E228" s="13"/>
-      <c r="F228" s="13"/>
+      <c r="E228" s="12"/>
+      <c r="F228" s="12"/>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
@@ -5705,8 +5799,8 @@
       <c r="D229" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E229" s="13"/>
-      <c r="F229" s="13"/>
+      <c r="E229" s="12"/>
+      <c r="F229" s="12"/>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
@@ -5721,8 +5815,8 @@
       <c r="D230" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E230" s="13"/>
-      <c r="F230" s="13"/>
+      <c r="E230" s="12"/>
+      <c r="F230" s="12"/>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
@@ -5737,8 +5831,8 @@
       <c r="D231" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E231" s="13"/>
-      <c r="F231" s="13"/>
+      <c r="E231" s="12"/>
+      <c r="F231" s="12"/>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
@@ -5753,8 +5847,8 @@
       <c r="D232" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E232" s="13"/>
-      <c r="F232" s="13"/>
+      <c r="E232" s="12"/>
+      <c r="F232" s="12"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
@@ -5769,8 +5863,8 @@
       <c r="D233" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E233" s="13"/>
-      <c r="F233" s="13"/>
+      <c r="E233" s="12"/>
+      <c r="F233" s="12"/>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
@@ -5785,8 +5879,8 @@
       <c r="D234" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E234" s="13"/>
-      <c r="F234" s="13"/>
+      <c r="E234" s="12"/>
+      <c r="F234" s="12"/>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
@@ -5801,8 +5895,8 @@
       <c r="D235" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E235" s="13"/>
-      <c r="F235" s="13"/>
+      <c r="E235" s="12"/>
+      <c r="F235" s="12"/>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
@@ -5817,8 +5911,8 @@
       <c r="D236" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E236" s="13"/>
-      <c r="F236" s="13"/>
+      <c r="E236" s="12"/>
+      <c r="F236" s="12"/>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
@@ -5833,8 +5927,8 @@
       <c r="D237" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E237" s="13"/>
-      <c r="F237" s="13"/>
+      <c r="E237" s="12"/>
+      <c r="F237" s="12"/>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
@@ -5849,8 +5943,8 @@
       <c r="D238" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E238" s="13"/>
-      <c r="F238" s="13"/>
+      <c r="E238" s="12"/>
+      <c r="F238" s="12"/>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
@@ -5865,8 +5959,8 @@
       <c r="D239" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E239" s="13"/>
-      <c r="F239" s="13"/>
+      <c r="E239" s="12"/>
+      <c r="F239" s="12"/>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
@@ -5881,8 +5975,8 @@
       <c r="D240" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E240" s="13"/>
-      <c r="F240" s="13"/>
+      <c r="E240" s="12"/>
+      <c r="F240" s="12"/>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
@@ -5897,8 +5991,8 @@
       <c r="D241" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E241" s="13"/>
-      <c r="F241" s="13"/>
+      <c r="E241" s="12"/>
+      <c r="F241" s="12"/>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
@@ -5913,8 +6007,8 @@
       <c r="D242" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E242" s="13"/>
-      <c r="F242" s="13"/>
+      <c r="E242" s="12"/>
+      <c r="F242" s="12"/>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
@@ -5929,8 +6023,8 @@
       <c r="D243" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E243" s="13"/>
-      <c r="F243" s="13"/>
+      <c r="E243" s="12"/>
+      <c r="F243" s="12"/>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
@@ -5945,8 +6039,8 @@
       <c r="D244" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E244" s="13"/>
-      <c r="F244" s="13"/>
+      <c r="E244" s="12"/>
+      <c r="F244" s="12"/>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
@@ -5961,8 +6055,8 @@
       <c r="D245" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E245" s="13"/>
-      <c r="F245" s="13"/>
+      <c r="E245" s="12"/>
+      <c r="F245" s="12"/>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
@@ -5977,8 +6071,8 @@
       <c r="D246" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E246" s="13"/>
-      <c r="F246" s="13"/>
+      <c r="E246" s="12"/>
+      <c r="F246" s="12"/>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
@@ -5993,8 +6087,8 @@
       <c r="D247" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E247" s="13"/>
-      <c r="F247" s="13"/>
+      <c r="E247" s="12"/>
+      <c r="F247" s="12"/>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
@@ -6009,8 +6103,8 @@
       <c r="D248" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E248" s="13"/>
-      <c r="F248" s="13"/>
+      <c r="E248" s="12"/>
+      <c r="F248" s="12"/>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
@@ -6025,8 +6119,8 @@
       <c r="D249" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E249" s="13"/>
-      <c r="F249" s="13"/>
+      <c r="E249" s="12"/>
+      <c r="F249" s="12"/>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
@@ -6041,8 +6135,8 @@
       <c r="D250" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E250" s="13"/>
-      <c r="F250" s="13"/>
+      <c r="E250" s="12"/>
+      <c r="F250" s="12"/>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
@@ -6057,8 +6151,8 @@
       <c r="D251" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E251" s="13"/>
-      <c r="F251" s="13"/>
+      <c r="E251" s="12"/>
+      <c r="F251" s="12"/>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
@@ -6073,8 +6167,8 @@
       <c r="D252" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E252" s="13"/>
-      <c r="F252" s="13"/>
+      <c r="E252" s="12"/>
+      <c r="F252" s="12"/>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
@@ -6089,8 +6183,8 @@
       <c r="D253" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E253" s="13"/>
-      <c r="F253" s="13"/>
+      <c r="E253" s="12"/>
+      <c r="F253" s="12"/>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
@@ -6105,8 +6199,8 @@
       <c r="D254" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E254" s="13"/>
-      <c r="F254" s="13"/>
+      <c r="E254" s="12"/>
+      <c r="F254" s="12"/>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
@@ -6121,8 +6215,8 @@
       <c r="D255" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E255" s="13"/>
-      <c r="F255" s="13"/>
+      <c r="E255" s="12"/>
+      <c r="F255" s="12"/>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
@@ -6137,8 +6231,8 @@
       <c r="D256" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E256" s="13"/>
-      <c r="F256" s="13"/>
+      <c r="E256" s="12"/>
+      <c r="F256" s="12"/>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
@@ -6153,8 +6247,8 @@
       <c r="D257" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E257" s="13"/>
-      <c r="F257" s="13"/>
+      <c r="E257" s="12"/>
+      <c r="F257" s="12"/>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
@@ -6169,8 +6263,8 @@
       <c r="D258" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E258" s="13"/>
-      <c r="F258" s="13"/>
+      <c r="E258" s="12"/>
+      <c r="F258" s="12"/>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
@@ -6185,8 +6279,8 @@
       <c r="D259" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E259" s="13"/>
-      <c r="F259" s="13"/>
+      <c r="E259" s="12"/>
+      <c r="F259" s="12"/>
     </row>
     <row r="260" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
@@ -6201,10 +6295,10 @@
       <c r="D260" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E260" s="15" t="s">
+      <c r="E260" s="14" t="s">
         <v>488</v>
       </c>
-      <c r="F260" s="13"/>
+      <c r="F260" s="12"/>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
@@ -6219,8 +6313,8 @@
       <c r="D261" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E261" s="13"/>
-      <c r="F261" s="13"/>
+      <c r="E261" s="12"/>
+      <c r="F261" s="12"/>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
@@ -6235,8 +6329,8 @@
       <c r="D262" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E262" s="13"/>
-      <c r="F262" s="13"/>
+      <c r="E262" s="12"/>
+      <c r="F262" s="12"/>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
@@ -7766,7 +7860,9 @@
       <c r="C363" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D363" s="4"/>
+      <c r="D363" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E363" s="4"/>
       <c r="F363" s="4"/>
     </row>
@@ -7780,7 +7876,9 @@
       <c r="C364" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D364" s="4"/>
+      <c r="D364" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E364" s="4"/>
       <c r="F364" s="4"/>
     </row>
@@ -7810,7 +7908,9 @@
       <c r="C366" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D366" s="4"/>
+      <c r="D366" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E366" s="4"/>
       <c r="F366" s="4"/>
     </row>
@@ -7824,7 +7924,9 @@
       <c r="C367" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D367" s="4"/>
+      <c r="D367" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E367" s="4"/>
       <c r="F367" s="4"/>
     </row>
@@ -7838,7 +7940,9 @@
       <c r="C368" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D368" s="4"/>
+      <c r="D368" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E368" s="4"/>
       <c r="F368" s="4"/>
     </row>
@@ -7852,7 +7956,9 @@
       <c r="C369" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D369" s="4"/>
+      <c r="D369" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E369" s="4"/>
       <c r="F369" s="4"/>
     </row>
@@ -7866,7 +7972,9 @@
       <c r="C370" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D370" s="4"/>
+      <c r="D370" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E370" s="4"/>
       <c r="F370" s="4"/>
     </row>
@@ -7880,7 +7988,9 @@
       <c r="C371" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D371" s="4"/>
+      <c r="D371" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E371" s="4"/>
       <c r="F371" s="4"/>
     </row>
@@ -7894,7 +8004,9 @@
       <c r="C372" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D372" s="4"/>
+      <c r="D372" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E372" s="4"/>
       <c r="F372" s="4"/>
     </row>
@@ -7908,7 +8020,9 @@
       <c r="C373" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D373" s="4"/>
+      <c r="D373" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E373" s="4"/>
       <c r="F373" s="4"/>
     </row>
@@ -7950,7 +8064,9 @@
       <c r="C376" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D376" s="4"/>
+      <c r="D376" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E376" s="4"/>
       <c r="F376" s="4"/>
     </row>
@@ -7964,7 +8080,9 @@
       <c r="C377" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D377" s="4"/>
+      <c r="D377" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E377" s="4"/>
       <c r="F377" s="4"/>
     </row>
@@ -7978,7 +8096,9 @@
       <c r="C378" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D378" s="4"/>
+      <c r="D378" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E378" s="4"/>
       <c r="F378" s="4"/>
     </row>
@@ -8006,7 +8126,9 @@
       <c r="C380" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D380" s="4"/>
+      <c r="D380" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E380" s="4"/>
       <c r="F380" s="4"/>
     </row>
@@ -8020,7 +8142,9 @@
       <c r="C381" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D381" s="4"/>
+      <c r="D381" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E381" s="4"/>
       <c r="F381" s="4"/>
     </row>
@@ -8034,7 +8158,9 @@
       <c r="C382" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D382" s="4"/>
+      <c r="D382" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E382" s="4"/>
       <c r="F382" s="4"/>
     </row>
@@ -8062,7 +8188,9 @@
       <c r="C384" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D384" s="4"/>
+      <c r="D384" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E384" s="4"/>
       <c r="F384" s="4"/>
     </row>
@@ -8090,7 +8218,9 @@
       <c r="C386" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D386" s="4"/>
+      <c r="D386" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E386" s="4"/>
       <c r="F386" s="4"/>
     </row>
@@ -8104,7 +8234,9 @@
       <c r="C387" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D387" s="4"/>
+      <c r="D387" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E387" s="4"/>
       <c r="F387" s="4"/>
     </row>
@@ -8132,7 +8264,9 @@
       <c r="C389" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D389" s="4"/>
+      <c r="D389" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E389" s="4"/>
       <c r="F389" s="4"/>
     </row>
@@ -8146,7 +8280,9 @@
       <c r="C390" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D390" s="4"/>
+      <c r="D390" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E390" s="4"/>
       <c r="F390" s="4"/>
     </row>
@@ -8160,7 +8296,9 @@
       <c r="C391" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D391" s="4"/>
+      <c r="D391" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E391" s="4"/>
       <c r="F391" s="4"/>
     </row>
@@ -8174,7 +8312,9 @@
       <c r="C392" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D392" s="4"/>
+      <c r="D392" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E392" s="4"/>
       <c r="F392" s="4"/>
     </row>
@@ -8204,7 +8344,9 @@
       <c r="C394" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D394" s="4"/>
+      <c r="D394" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E394" s="4"/>
       <c r="F394" s="4"/>
     </row>
@@ -8260,7 +8402,9 @@
       <c r="C398" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D398" s="4"/>
+      <c r="D398" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E398" s="4"/>
       <c r="F398" s="4"/>
     </row>
@@ -8369,7 +8513,7 @@
       <c r="D405" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E405" s="18"/>
+      <c r="E405" s="17"/>
       <c r="F405" s="4"/>
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
@@ -8414,7 +8558,9 @@
       <c r="C408" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D408" s="4"/>
+      <c r="D408" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E408" s="4"/>
       <c r="F408" s="4"/>
     </row>
@@ -8458,7 +8604,9 @@
       <c r="C411" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D411" s="4"/>
+      <c r="D411" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E411" s="4"/>
       <c r="F411" s="4"/>
     </row>
@@ -8548,7 +8696,9 @@
       <c r="C417" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D417" s="4"/>
+      <c r="D417" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E417" s="4"/>
       <c r="F417" s="4"/>
     </row>
@@ -8590,7 +8740,9 @@
       <c r="C420" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D420" s="4"/>
+      <c r="D420" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E420" s="4"/>
       <c r="F420" s="4"/>
     </row>
@@ -8674,7 +8826,9 @@
       <c r="C426" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D426" s="4"/>
+      <c r="D426" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E426" s="4"/>
       <c r="F426" s="4"/>
     </row>
@@ -8688,7 +8842,9 @@
       <c r="C427" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D427" s="4"/>
+      <c r="D427" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E427" s="4"/>
       <c r="F427" s="4"/>
     </row>
@@ -8702,7 +8858,9 @@
       <c r="C428" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D428" s="4"/>
+      <c r="D428" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E428" s="4"/>
       <c r="F428" s="4"/>
     </row>
@@ -8716,7 +8874,9 @@
       <c r="C429" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D429" s="4"/>
+      <c r="D429" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E429" s="4"/>
       <c r="F429" s="4"/>
     </row>
@@ -8746,7 +8906,9 @@
       <c r="C431" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D431" s="4"/>
+      <c r="D431" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E431" s="4"/>
       <c r="F431" s="4"/>
     </row>
@@ -8802,7 +8964,9 @@
       <c r="C435" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D435" s="4"/>
+      <c r="D435" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E435" s="4"/>
       <c r="F435" s="4"/>
     </row>
@@ -8816,7 +8980,9 @@
       <c r="C436" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D436" s="4"/>
+      <c r="D436" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E436" s="4"/>
       <c r="F436" s="4"/>
     </row>
@@ -8830,7 +8996,9 @@
       <c r="C437" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D437" s="4"/>
+      <c r="D437" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E437" s="4"/>
       <c r="F437" s="4"/>
     </row>
@@ -8950,7 +9118,9 @@
       <c r="C445" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D445" s="4"/>
+      <c r="D445" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E445" s="4"/>
       <c r="F445" s="4"/>
     </row>
@@ -8964,7 +9134,9 @@
       <c r="C446" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D446" s="4"/>
+      <c r="D446" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E446" s="4"/>
       <c r="F446" s="4"/>
     </row>
@@ -8978,7 +9150,9 @@
       <c r="C447" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D447" s="4"/>
+      <c r="D447" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E447" s="4"/>
       <c r="F447" s="4"/>
     </row>
@@ -8992,7 +9166,9 @@
       <c r="C448" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D448" s="4"/>
+      <c r="D448" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E448" s="4"/>
       <c r="F448" s="4"/>
     </row>
@@ -9006,7 +9182,9 @@
       <c r="C449" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D449" s="4"/>
+      <c r="D449" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E449" s="4"/>
       <c r="F449" s="4"/>
     </row>
@@ -9020,7 +9198,9 @@
       <c r="C450" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D450" s="4"/>
+      <c r="D450" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E450" s="4"/>
       <c r="F450" s="4"/>
     </row>
@@ -9050,7 +9230,9 @@
       <c r="C452" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D452" s="4"/>
+      <c r="D452" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E452" s="4"/>
       <c r="F452" s="4"/>
     </row>
@@ -9080,7 +9262,9 @@
       <c r="C454" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D454" s="4"/>
+      <c r="D454" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E454" s="4"/>
       <c r="F454" s="4"/>
     </row>
@@ -9094,7 +9278,9 @@
       <c r="C455" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D455" s="4"/>
+      <c r="D455" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E455" s="4"/>
       <c r="F455" s="4"/>
     </row>
@@ -9108,7 +9294,9 @@
       <c r="C456" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D456" s="4"/>
+      <c r="D456" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E456" s="4"/>
       <c r="F456" s="4"/>
     </row>
@@ -9170,7 +9358,9 @@
       <c r="C460" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D460" s="4"/>
+      <c r="D460" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E460" s="4"/>
       <c r="F460" s="4"/>
     </row>
@@ -9184,7 +9374,9 @@
       <c r="C461" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D461" s="4"/>
+      <c r="D461" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E461" s="4"/>
       <c r="F461" s="4"/>
     </row>
@@ -9217,10 +9409,10 @@
       <c r="D463" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E463" s="13" t="s">
+      <c r="E463" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F463" s="13"/>
+      <c r="F463" s="12"/>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="4">
@@ -9235,10 +9427,10 @@
       <c r="D464" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E464" s="13" t="s">
+      <c r="E464" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F464" s="13"/>
+      <c r="F464" s="12"/>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="4">
@@ -9253,10 +9445,10 @@
       <c r="D465" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E465" s="13" t="s">
+      <c r="E465" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F465" s="13"/>
+      <c r="F465" s="12"/>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="4">
@@ -9271,10 +9463,10 @@
       <c r="D466" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E466" s="13" t="s">
+      <c r="E466" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F466" s="13"/>
+      <c r="F466" s="12"/>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="4">
@@ -9289,10 +9481,10 @@
       <c r="D467" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E467" s="13" t="s">
+      <c r="E467" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F467" s="13"/>
+      <c r="F467" s="12"/>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="4">
@@ -9307,10 +9499,10 @@
       <c r="D468" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E468" s="13" t="s">
+      <c r="E468" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F468" s="13"/>
+      <c r="F468" s="12"/>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="4">
@@ -9325,10 +9517,10 @@
       <c r="D469" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E469" s="13" t="s">
+      <c r="E469" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F469" s="13"/>
+      <c r="F469" s="12"/>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="4">
@@ -9343,16 +9535,16 @@
       <c r="D470" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E470" s="13" t="s">
+      <c r="E470" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F470" s="13"/>
+      <c r="F470" s="12"/>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="4">
         <v>470</v>
       </c>
-      <c r="B471" s="21" t="s">
+      <c r="B471" s="18" t="s">
         <v>491</v>
       </c>
       <c r="C471" s="6" t="s">
@@ -9361,10 +9553,10 @@
       <c r="D471" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E471" s="13" t="s">
+      <c r="E471" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="F471" s="13"/>
+      <c r="F471" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E471" xr:uid="{6F4CE4C5-33C3-485C-9EF7-1623C4B890AF}"/>

--- a/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
+++ b/5. Other/Danh sách VNSH03 nhận từ X-Force.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\5. Other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370980F6-D391-4948-A73F-EFE2A1A253D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED418AA-D3D8-43FC-876E-92CE1B15061A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DE03BF13-5A63-4E6D-9BDA-D95C0EEDDB32}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="492">
   <si>
     <t>STT</t>
   </si>
@@ -2029,9 +2029,7 @@
         <v>103</v>
       </c>
       <c r="E2" s="12"/>
-      <c r="F2" s="18" t="s">
-        <v>401</v>
-      </c>
+      <c r="F2" s="18"/>
       <c r="G2" s="9"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -2048,9 +2046,7 @@
         <v>103</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="18" t="s">
-        <v>394</v>
-      </c>
+      <c r="F3" s="18"/>
       <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2067,9 +2063,7 @@
         <v>103</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="18" t="s">
-        <v>420</v>
-      </c>
+      <c r="F4" s="18"/>
       <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2086,9 +2080,7 @@
         <v>103</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="18" t="s">
-        <v>432</v>
-      </c>
+      <c r="F5" s="18"/>
       <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2105,9 +2097,7 @@
         <v>103</v>
       </c>
       <c r="E6" s="12"/>
-      <c r="F6" s="18" t="s">
-        <v>378</v>
-      </c>
+      <c r="F6" s="18"/>
       <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -2124,9 +2114,7 @@
         <v>103</v>
       </c>
       <c r="E7" s="12"/>
-      <c r="F7" s="18" t="s">
-        <v>406</v>
-      </c>
+      <c r="F7" s="18"/>
       <c r="G7" s="9"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -2143,9 +2131,7 @@
         <v>103</v>
       </c>
       <c r="E8" s="12"/>
-      <c r="F8" s="18" t="s">
-        <v>379</v>
-      </c>
+      <c r="F8" s="18"/>
       <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -2162,9 +2148,7 @@
         <v>103</v>
       </c>
       <c r="E9" s="12"/>
-      <c r="F9" s="18" t="s">
-        <v>464</v>
-      </c>
+      <c r="F9" s="18"/>
       <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -2181,9 +2165,7 @@
         <v>103</v>
       </c>
       <c r="E10" s="12"/>
-      <c r="F10" s="18" t="s">
-        <v>443</v>
-      </c>
+      <c r="F10" s="18"/>
       <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -2200,9 +2182,7 @@
         <v>103</v>
       </c>
       <c r="E11" s="12"/>
-      <c r="F11" s="18" t="s">
-        <v>398</v>
-      </c>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2219,9 +2199,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="12"/>
-      <c r="F12" s="18" t="s">
-        <v>396</v>
-      </c>
+      <c r="F12" s="18"/>
       <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2238,9 +2216,7 @@
         <v>103</v>
       </c>
       <c r="E13" s="12"/>
-      <c r="F13" s="18" t="s">
-        <v>439</v>
-      </c>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
     </row>
     <row r="14" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -2259,9 +2235,7 @@
       <c r="E14" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="F14" s="18" t="s">
-        <v>389</v>
-      </c>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -2278,9 +2252,7 @@
         <v>103</v>
       </c>
       <c r="E15" s="12"/>
-      <c r="F15" s="18" t="s">
-        <v>472</v>
-      </c>
+      <c r="F15" s="18"/>
       <c r="G15" s="9"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2297,9 +2269,7 @@
         <v>103</v>
       </c>
       <c r="E16" s="12"/>
-      <c r="F16" s="18" t="s">
-        <v>447</v>
-      </c>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -2316,9 +2286,7 @@
         <v>103</v>
       </c>
       <c r="E17" s="12"/>
-      <c r="F17" s="18" t="s">
-        <v>461</v>
-      </c>
+      <c r="F17" s="18"/>
       <c r="G17" s="9"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -2335,9 +2303,7 @@
         <v>103</v>
       </c>
       <c r="E18" s="12"/>
-      <c r="F18" s="18" t="s">
-        <v>473</v>
-      </c>
+      <c r="F18" s="18"/>
       <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2354,9 +2320,7 @@
         <v>103</v>
       </c>
       <c r="E19" s="12"/>
-      <c r="F19" s="18" t="s">
-        <v>423</v>
-      </c>
+      <c r="F19" s="18"/>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2373,9 +2337,7 @@
         <v>103</v>
       </c>
       <c r="E20" s="12"/>
-      <c r="F20" s="18" t="s">
-        <v>376</v>
-      </c>
+      <c r="F20" s="18"/>
       <c r="G20" s="9"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -2392,9 +2354,7 @@
         <v>103</v>
       </c>
       <c r="E21" s="12"/>
-      <c r="F21" s="18" t="s">
-        <v>449</v>
-      </c>
+      <c r="F21" s="18"/>
       <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -2411,9 +2371,7 @@
         <v>103</v>
       </c>
       <c r="E22" s="12"/>
-      <c r="F22" s="21" t="s">
-        <v>410</v>
-      </c>
+      <c r="F22" s="21"/>
       <c r="G22" s="9"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -2430,9 +2388,7 @@
         <v>103</v>
       </c>
       <c r="E23" s="12"/>
-      <c r="F23" s="21" t="s">
-        <v>466</v>
-      </c>
+      <c r="F23" s="21"/>
       <c r="G23" s="9"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -2449,9 +2405,7 @@
         <v>103</v>
       </c>
       <c r="E24" s="12"/>
-      <c r="F24" s="21" t="s">
-        <v>390</v>
-      </c>
+      <c r="F24" s="21"/>
       <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2468,9 +2422,7 @@
         <v>103</v>
       </c>
       <c r="E25" s="12"/>
-      <c r="F25" s="21" t="s">
-        <v>457</v>
-      </c>
+      <c r="F25" s="21"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2487,9 +2439,7 @@
         <v>103</v>
       </c>
       <c r="E26" s="12"/>
-      <c r="F26" s="21" t="s">
-        <v>382</v>
-      </c>
+      <c r="F26" s="21"/>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2506,9 +2456,7 @@
         <v>103</v>
       </c>
       <c r="E27" s="12"/>
-      <c r="F27" s="21" t="s">
-        <v>183</v>
-      </c>
+      <c r="F27" s="21"/>
       <c r="G27" s="10"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2525,9 +2473,7 @@
         <v>103</v>
       </c>
       <c r="E28" s="12"/>
-      <c r="F28" s="21" t="s">
-        <v>459</v>
-      </c>
+      <c r="F28" s="21"/>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2544,9 +2490,7 @@
         <v>103</v>
       </c>
       <c r="E29" s="12"/>
-      <c r="F29" s="21" t="s">
-        <v>393</v>
-      </c>
+      <c r="F29" s="21"/>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -2563,9 +2507,7 @@
         <v>103</v>
       </c>
       <c r="E30" s="12"/>
-      <c r="F30" s="21" t="s">
-        <v>399</v>
-      </c>
+      <c r="F30" s="21"/>
       <c r="G30" s="10"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2582,9 +2524,7 @@
         <v>103</v>
       </c>
       <c r="E31" s="12"/>
-      <c r="F31" s="21" t="s">
-        <v>402</v>
-      </c>
+      <c r="F31" s="21"/>
       <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -2601,9 +2541,7 @@
         <v>103</v>
       </c>
       <c r="E32" s="12"/>
-      <c r="F32" s="21" t="s">
-        <v>384</v>
-      </c>
+      <c r="F32" s="21"/>
       <c r="G32" s="10"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2620,9 +2558,7 @@
         <v>103</v>
       </c>
       <c r="E33" s="12"/>
-      <c r="F33" s="21" t="s">
-        <v>381</v>
-      </c>
+      <c r="F33" s="21"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
@@ -2638,9 +2574,7 @@
         <v>103</v>
       </c>
       <c r="E34" s="12"/>
-      <c r="F34" s="21" t="s">
-        <v>462</v>
-      </c>
+      <c r="F34" s="21"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
@@ -2656,9 +2590,7 @@
         <v>103</v>
       </c>
       <c r="E35" s="12"/>
-      <c r="F35" s="21" t="s">
-        <v>438</v>
-      </c>
+      <c r="F35" s="21"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
@@ -2674,9 +2606,7 @@
         <v>103</v>
       </c>
       <c r="E36" s="12"/>
-      <c r="F36" s="21" t="s">
-        <v>403</v>
-      </c>
+      <c r="F36" s="21"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
@@ -2692,9 +2622,7 @@
         <v>103</v>
       </c>
       <c r="E37" s="12"/>
-      <c r="F37" s="21" t="s">
-        <v>468</v>
-      </c>
+      <c r="F37" s="21"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
@@ -2710,9 +2638,7 @@
         <v>103</v>
       </c>
       <c r="E38" s="12"/>
-      <c r="F38" s="21" t="s">
-        <v>388</v>
-      </c>
+      <c r="F38" s="21"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
@@ -2728,9 +2654,7 @@
         <v>103</v>
       </c>
       <c r="E39" s="12"/>
-      <c r="F39" s="21" t="s">
-        <v>383</v>
-      </c>
+      <c r="F39" s="21"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
@@ -2746,9 +2670,7 @@
         <v>103</v>
       </c>
       <c r="E40" s="12"/>
-      <c r="F40" s="21" t="s">
-        <v>375</v>
-      </c>
+      <c r="F40" s="21"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
@@ -2764,9 +2686,7 @@
         <v>103</v>
       </c>
       <c r="E41" s="12"/>
-      <c r="F41" s="21" t="s">
-        <v>429</v>
-      </c>
+      <c r="F41" s="21"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
@@ -2782,9 +2702,7 @@
         <v>103</v>
       </c>
       <c r="E42" s="12"/>
-      <c r="F42" s="21" t="s">
-        <v>458</v>
-      </c>
+      <c r="F42" s="21"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
@@ -2800,9 +2718,7 @@
         <v>103</v>
       </c>
       <c r="E43" s="12"/>
-      <c r="F43" s="21" t="s">
-        <v>467</v>
-      </c>
+      <c r="F43" s="21"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
@@ -2818,9 +2734,7 @@
         <v>103</v>
       </c>
       <c r="E44" s="12"/>
-      <c r="F44" s="21" t="s">
-        <v>440</v>
-      </c>
+      <c r="F44" s="21"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
@@ -2836,9 +2750,7 @@
         <v>103</v>
       </c>
       <c r="E45" s="12"/>
-      <c r="F45" s="21" t="s">
-        <v>380</v>
-      </c>
+      <c r="F45" s="21"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
@@ -2854,9 +2766,7 @@
         <v>103</v>
       </c>
       <c r="E46" s="12"/>
-      <c r="F46" s="21" t="s">
-        <v>404</v>
-      </c>
+      <c r="F46" s="21"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
@@ -2872,9 +2782,7 @@
         <v>103</v>
       </c>
       <c r="E47" s="12"/>
-      <c r="F47" s="21" t="s">
-        <v>385</v>
-      </c>
+      <c r="F47" s="21"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
@@ -2890,9 +2798,7 @@
         <v>103</v>
       </c>
       <c r="E48" s="12"/>
-      <c r="F48" s="21" t="s">
-        <v>448</v>
-      </c>
+      <c r="F48" s="21"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
@@ -2908,9 +2814,7 @@
         <v>103</v>
       </c>
       <c r="E49" s="12"/>
-      <c r="F49" s="21" t="s">
-        <v>392</v>
-      </c>
+      <c r="F49" s="21"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
@@ -2926,9 +2830,7 @@
         <v>103</v>
       </c>
       <c r="E50" s="12"/>
-      <c r="F50" s="21" t="s">
-        <v>441</v>
-      </c>
+      <c r="F50" s="21"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
@@ -2944,9 +2846,7 @@
         <v>103</v>
       </c>
       <c r="E51" s="12"/>
-      <c r="F51" s="21" t="s">
-        <v>460</v>
-      </c>
+      <c r="F51" s="21"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
@@ -8036,7 +7936,9 @@
       <c r="C374" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D374" s="4"/>
+      <c r="D374" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E374" s="4"/>
       <c r="F374" s="4"/>
     </row>
@@ -8050,7 +7952,9 @@
       <c r="C375" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D375" s="4"/>
+      <c r="D375" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E375" s="4"/>
       <c r="F375" s="4"/>
     </row>
@@ -8112,7 +8016,9 @@
       <c r="C379" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D379" s="4"/>
+      <c r="D379" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E379" s="4"/>
       <c r="F379" s="4"/>
     </row>
@@ -8174,7 +8080,9 @@
       <c r="C383" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D383" s="4"/>
+      <c r="D383" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E383" s="4"/>
       <c r="F383" s="4"/>
     </row>
@@ -8204,7 +8112,9 @@
       <c r="C385" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D385" s="4"/>
+      <c r="D385" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E385" s="4"/>
       <c r="F385" s="4"/>
     </row>
@@ -8250,7 +8160,9 @@
       <c r="C388" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D388" s="4"/>
+      <c r="D388" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E388" s="4"/>
       <c r="F388" s="4"/>
     </row>
@@ -8360,7 +8272,9 @@
       <c r="C395" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D395" s="4"/>
+      <c r="D395" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E395" s="4"/>
       <c r="F395" s="4"/>
     </row>
@@ -8374,7 +8288,9 @@
       <c r="C396" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D396" s="4"/>
+      <c r="D396" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E396" s="4"/>
       <c r="F396" s="4"/>
     </row>
@@ -8388,7 +8304,9 @@
       <c r="C397" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D397" s="4"/>
+      <c r="D397" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E397" s="4"/>
       <c r="F397" s="4"/>
     </row>
@@ -8450,7 +8368,9 @@
       <c r="C401" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D401" s="4"/>
+      <c r="D401" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E401" s="4"/>
       <c r="F401" s="4"/>
     </row>
@@ -8464,7 +8384,9 @@
       <c r="C402" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D402" s="4"/>
+      <c r="D402" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E402" s="4"/>
       <c r="F402" s="4"/>
     </row>
@@ -8574,7 +8496,9 @@
       <c r="C409" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D409" s="4"/>
+      <c r="D409" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E409" s="4"/>
       <c r="F409" s="4"/>
     </row>
@@ -8636,7 +8560,9 @@
       <c r="C413" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D413" s="4"/>
+      <c r="D413" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E413" s="4"/>
       <c r="F413" s="4"/>
     </row>
@@ -8666,7 +8592,9 @@
       <c r="C415" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D415" s="4"/>
+      <c r="D415" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E415" s="4"/>
       <c r="F415" s="4"/>
     </row>
@@ -8712,7 +8640,9 @@
       <c r="C418" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D418" s="4"/>
+      <c r="D418" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E418" s="4"/>
       <c r="F418" s="4"/>
     </row>
@@ -8726,7 +8656,9 @@
       <c r="C419" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D419" s="4"/>
+      <c r="D419" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E419" s="4"/>
       <c r="F419" s="4"/>
     </row>
@@ -8756,7 +8688,9 @@
       <c r="C421" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D421" s="4"/>
+      <c r="D421" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E421" s="4"/>
       <c r="F421" s="4"/>
     </row>
@@ -8770,7 +8704,9 @@
       <c r="C422" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D422" s="4"/>
+      <c r="D422" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E422" s="4"/>
       <c r="F422" s="4"/>
     </row>
@@ -8784,7 +8720,9 @@
       <c r="C423" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D423" s="4"/>
+      <c r="D423" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E423" s="4"/>
       <c r="F423" s="4"/>
     </row>
@@ -8798,7 +8736,9 @@
       <c r="C424" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D424" s="4"/>
+      <c r="D424" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E424" s="4"/>
       <c r="F424" s="4"/>
     </row>
@@ -8812,7 +8752,9 @@
       <c r="C425" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D425" s="4"/>
+      <c r="D425" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E425" s="4"/>
       <c r="F425" s="4"/>
     </row>
@@ -8922,7 +8864,9 @@
       <c r="C432" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D432" s="4"/>
+      <c r="D432" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E432" s="4"/>
       <c r="F432" s="4"/>
     </row>
@@ -8936,7 +8880,9 @@
       <c r="C433" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D433" s="4"/>
+      <c r="D433" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E433" s="4"/>
       <c r="F433" s="4"/>
     </row>
@@ -8950,7 +8896,9 @@
       <c r="C434" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D434" s="4"/>
+      <c r="D434" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E434" s="4"/>
       <c r="F434" s="4"/>
     </row>
@@ -9044,7 +8992,9 @@
       <c r="C440" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D440" s="4"/>
+      <c r="D440" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E440" s="4"/>
       <c r="F440" s="4"/>
     </row>
@@ -9058,7 +9008,9 @@
       <c r="C441" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D441" s="4"/>
+      <c r="D441" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E441" s="4"/>
       <c r="F441" s="4"/>
     </row>
@@ -9072,7 +9024,9 @@
       <c r="C442" s="6" t="s">
         <v>474</v>
       </c>
-      <c r="D442" s="4"/>
+      <c r="D442" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="E442" s="4"/>
       <c r="F442" s="4"/>
     </row>
